--- a/datos/CV_PF.xlsx
+++ b/datos/CV_PF.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df502c28020c5b60/Documentos/GIM/Proteccion Familiar/Estrategia/Estrategia 2026/3.Estrategia Comercial 2026/Dash board/Archivos 18032026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://funerariaimchile-my.sharepoint.com/personal/anais_gonzalez_funerariaim_cl/Documents/Dashboard_Control Diario de Ventas/Archivos diarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{02C78619-7F02-45F9-BEE5-00EEA7E7CAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{693F19A8-94C1-4275-8FFA-02E95D8F7DD5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF6F809D-2ED1-4770-811E-EBB475309F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ParamQuery Pro" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2226" uniqueCount="677">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -208,129 +208,132 @@
     <t>2</t>
   </si>
   <si>
+    <t>ACTIVO VALIDADO</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO SOLUCIÓN TOTAL ADULTO MAYOR</t>
+  </si>
+  <si>
+    <t>ADULTO MAYOR SOLUCIÓN TOTAL</t>
+  </si>
+  <si>
+    <t>SIN DATOS</t>
+  </si>
+  <si>
+    <t>UPAGO</t>
+  </si>
+  <si>
+    <t>3729</t>
+  </si>
+  <si>
+    <t>10084099-5</t>
+  </si>
+  <si>
+    <t>MAUREIRA CARRERA AMANDA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>11/08/1966</t>
+  </si>
+  <si>
+    <t>Pirque</t>
+  </si>
+  <si>
+    <t>120 - Pirque - Cordillera -CP</t>
+  </si>
+  <si>
+    <t>990407886</t>
+  </si>
+  <si>
+    <t>cmaureiracarrera1966@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>Diego Alejandro Vasquez Flores</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>2300000</t>
+  </si>
+  <si>
+    <t>1932773</t>
+  </si>
+  <si>
+    <t>0.12</t>
+  </si>
+  <si>
+    <t>285000</t>
+  </si>
+  <si>
+    <t>2015000</t>
+  </si>
+  <si>
+    <t>33583</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO ADULTO MAYOR</t>
+  </si>
+  <si>
+    <t>ADULTO MAYOR</t>
+  </si>
+  <si>
+    <t>3734</t>
+  </si>
+  <si>
+    <t>5404340-6</t>
+  </si>
+  <si>
+    <t>GONZALEZ GALLEGOS BORIS HERNAN</t>
+  </si>
+  <si>
+    <t>28/07/1945</t>
+  </si>
+  <si>
+    <t>Puente Alto</t>
+  </si>
+  <si>
+    <t>598 - Puente Alto - Cordillera -CP</t>
+  </si>
+  <si>
+    <t>993966776</t>
+  </si>
+  <si>
+    <t>borisgonzalezgallegos77@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>09/02/2026</t>
+  </si>
+  <si>
+    <t>ASDREYM CAROLINA GUILLEN VALDES</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>1700000</t>
+  </si>
+  <si>
+    <t>1428571</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>340000</t>
+  </si>
+  <si>
+    <t>1360000</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>113333</t>
+  </si>
+  <si>
     <t>ACTIVO PEND VALIDAR</t>
   </si>
   <si>
-    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO SOLUCIÓN TOTAL ADULTO MAYOR</t>
-  </si>
-  <si>
-    <t>ADULTO MAYOR SOLUCIÓN TOTAL</t>
-  </si>
-  <si>
-    <t>SIN DATOS</t>
-  </si>
-  <si>
-    <t>UPAGO</t>
-  </si>
-  <si>
-    <t>3729</t>
-  </si>
-  <si>
-    <t>10084099-5</t>
-  </si>
-  <si>
-    <t>MAUREIRA CARRERA AMANDA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>11/08/1966</t>
-  </si>
-  <si>
-    <t>Pirque</t>
-  </si>
-  <si>
-    <t>120 - Pirque - Cordillera -CP</t>
-  </si>
-  <si>
-    <t>990407886</t>
-  </si>
-  <si>
-    <t>cmaureiracarrera1966@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>Diego Alejandro Vasquez Flores</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>2300000</t>
-  </si>
-  <si>
-    <t>1932773</t>
-  </si>
-  <si>
-    <t>0.12</t>
-  </si>
-  <si>
-    <t>285000</t>
-  </si>
-  <si>
-    <t>2015000</t>
-  </si>
-  <si>
-    <t>33583</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO ADULTO MAYOR</t>
-  </si>
-  <si>
-    <t>ADULTO MAYOR</t>
-  </si>
-  <si>
-    <t>3734</t>
-  </si>
-  <si>
-    <t>5404340-6</t>
-  </si>
-  <si>
-    <t>GONZALEZ GALLEGOS BORIS HERNAN</t>
-  </si>
-  <si>
-    <t>28/07/1945</t>
-  </si>
-  <si>
-    <t>Puente Alto</t>
-  </si>
-  <si>
-    <t>598 - Puente Alto - Cordillera -CP</t>
-  </si>
-  <si>
-    <t>993966776</t>
-  </si>
-  <si>
-    <t>borisgonzalezgallegos77@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>09/02/2026</t>
-  </si>
-  <si>
-    <t>ASDREYM CAROLINA GUILLEN VALDES</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>1700000</t>
-  </si>
-  <si>
-    <t>1428571</t>
-  </si>
-  <si>
-    <t>0.2</t>
-  </si>
-  <si>
-    <t>340000</t>
-  </si>
-  <si>
-    <t>1360000</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>113333</t>
-  </si>
-  <si>
     <t>SERVICIO FUNERARIO RAICES DE VIDA ADULTO MAYOR</t>
   </si>
   <si>
@@ -439,7 +442,7 @@
     <t>joseedelfin@hotmail.com; ; ; ;</t>
   </si>
   <si>
-    <t>RODOLFO SANTANA BASAEZ</t>
+    <t>Camilo Jesus Medel Rojas</t>
   </si>
   <si>
     <t>Luis Alberto Osores   Osores</t>
@@ -502,9 +505,6 @@
     <t>normaayala982@gmail.com; ; ; ;</t>
   </si>
   <si>
-    <t>Camilo Jesus Medel Rojas</t>
-  </si>
-  <si>
     <t>Francesca Nicole Sanchez pacheco</t>
   </si>
   <si>
@@ -583,9 +583,6 @@
     <t>440000</t>
   </si>
   <si>
-    <t>ACTIVO VALIDADO</t>
-  </si>
-  <si>
     <t>SERVICIO FUNERARIO TESOROS DEL ALMA PERSONAL</t>
   </si>
   <si>
@@ -1213,7 +1210,7 @@
     <t>949508704</t>
   </si>
   <si>
-    <t>camilosalinas89@gmqil.com; ; ; ;</t>
+    <t>camilo.salinas89@gmail.com; ; ; ;</t>
   </si>
   <si>
     <t>GABRIELA DEL CARMEN ROJAS QUEZADA</t>
@@ -1222,6 +1219,9 @@
     <t>Margarita Cristina Rojas Quezada</t>
   </si>
   <si>
+    <t>2511562</t>
+  </si>
+  <si>
     <t>53438</t>
   </si>
   <si>
@@ -1627,10 +1627,10 @@
     <t>157 - Providencia - Santiago -CP</t>
   </si>
   <si>
-    <t>096709222</t>
-  </si>
-  <si>
-    <t>lorerebodellobb@gmail.com; ; ; ;</t>
+    <t>996709222</t>
+  </si>
+  <si>
+    <t>lorerebolledow@gmail.com; ; ; ;</t>
   </si>
   <si>
     <t>XIMENA DEL CARMEN LOPEZ ROZAS</t>
@@ -1750,15 +1750,12 @@
     <t>978588716</t>
   </si>
   <si>
-    <t>fefy_2802@hotmail.comn; ; ; ;</t>
+    <t>fefy_2802@hotmail.com; ; ; ;</t>
   </si>
   <si>
     <t>CATALINA PATRICIA CABRERA  HORMAZABAL</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>1760000</t>
   </si>
   <si>
@@ -1771,7 +1768,7 @@
     <t>1584000</t>
   </si>
   <si>
-    <t>52800</t>
+    <t>132000</t>
   </si>
   <si>
     <t>3921</t>
@@ -1841,6 +1838,219 @@
   </si>
   <si>
     <t>3923</t>
+  </si>
+  <si>
+    <t>6580393-3</t>
+  </si>
+  <si>
+    <t>MUÑOZ ARAYA MARIA ANGELICA</t>
+  </si>
+  <si>
+    <t>10/02/1951</t>
+  </si>
+  <si>
+    <t>185 - Quilicura - Santiago -CP</t>
+  </si>
+  <si>
+    <t>942906579</t>
+  </si>
+  <si>
+    <t>angelucamunoz0185@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>19/03/2026</t>
+  </si>
+  <si>
+    <t>Dennisse alondra ramirez osorio</t>
+  </si>
+  <si>
+    <t>265000</t>
+  </si>
+  <si>
+    <t>2120000</t>
+  </si>
+  <si>
+    <t>58889</t>
+  </si>
+  <si>
+    <t>3932</t>
+  </si>
+  <si>
+    <t>11721969-0</t>
+  </si>
+  <si>
+    <t>REYES SUAREZ MÓNICA ANDREA</t>
+  </si>
+  <si>
+    <t>19/07/1971</t>
+  </si>
+  <si>
+    <t>374 - San Bernardo - Maipo -CP</t>
+  </si>
+  <si>
+    <t>988282016</t>
+  </si>
+  <si>
+    <t>monicaareyessuarez@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>FRANCISCA ANDREA DELGADO LOYOLA</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>1820000</t>
+  </si>
+  <si>
+    <t>30847</t>
+  </si>
+  <si>
+    <t>3937</t>
+  </si>
+  <si>
+    <t>17577317-7</t>
+  </si>
+  <si>
+    <t>SALDES ALVAREZ CAROLINA DE JESUS</t>
+  </si>
+  <si>
+    <t>27/07/1990</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>4251 - San Miguel - Santiago -CP</t>
+  </si>
+  <si>
+    <t>958637867</t>
+  </si>
+  <si>
+    <t>saldescarito@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>Gabriela katalina Arcos Sanchez</t>
+  </si>
+  <si>
+    <t>2242500</t>
+  </si>
+  <si>
+    <t>1884454</t>
+  </si>
+  <si>
+    <t>3950</t>
+  </si>
+  <si>
+    <t>5357234-0</t>
+  </si>
+  <si>
+    <t>SEPULVEDA RUIZ NESTOR MANUEL</t>
+  </si>
+  <si>
+    <t>25/11/1951</t>
+  </si>
+  <si>
+    <t>731 - Maipú - Santiago -CP</t>
+  </si>
+  <si>
+    <t>988035602</t>
+  </si>
+  <si>
+    <t>nestor.sepulveda.ruiz@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>EDIXON MANUEL BASTIDAS VASQUEZ</t>
+  </si>
+  <si>
+    <t>5000000</t>
+  </si>
+  <si>
+    <t>4201681</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO TESOROS DEL ALMA FAMILIAR</t>
+  </si>
+  <si>
+    <t>3956</t>
+  </si>
+  <si>
+    <t>18626228-K</t>
+  </si>
+  <si>
+    <t>FERRADA CALBUN CRITOPHER ANDRES</t>
+  </si>
+  <si>
+    <t>14/11/1993</t>
+  </si>
+  <si>
+    <t>975 - San Miguel - Santiago -CP</t>
+  </si>
+  <si>
+    <t>950056261</t>
+  </si>
+  <si>
+    <t>cferrada@integramundo.cl; ; ; ;</t>
+  </si>
+  <si>
+    <t>21/03/2026</t>
+  </si>
+  <si>
+    <t>2587500</t>
+  </si>
+  <si>
+    <t>2174370</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>388125</t>
+  </si>
+  <si>
+    <t>2199375</t>
+  </si>
+  <si>
+    <t>91641</t>
+  </si>
+  <si>
+    <t>3960</t>
+  </si>
+  <si>
+    <t>27977901-0</t>
+  </si>
+  <si>
+    <t>ESPINOZA DE PEREZ MARLENY DEL CARMEN</t>
+  </si>
+  <si>
+    <t>14/01/1966</t>
+  </si>
+  <si>
+    <t>226 - Quilicura - Santiago -CP</t>
+  </si>
+  <si>
+    <t>967454846</t>
+  </si>
+  <si>
+    <t>marleny66@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>22/03/2026</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>39340</t>
+  </si>
+  <si>
+    <t>3964</t>
   </si>
 </sst>
 </file>
@@ -2701,54 +2911,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AP47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:AP53"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.9296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.73046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="38.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.53125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.53125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="40.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.3984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.06640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.1328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.73046875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.06640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.265625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="63.73046875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="28.46484375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.1328125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="16.73046875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="20.265625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.73046875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="23.06640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="20.73046875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="10" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="9.53125" bestFit="1" customWidth="1"/>
+    <col min="1" max="41" width="8" customWidth="1"/>
+    <col min="42" max="42" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2876,7 +3046,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -3004,7 +3174,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -3132,7 +3302,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -3218,10 +3388,10 @@
         <v>102</v>
       </c>
       <c r="AC4" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="AD4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE4" t="s">
         <v>84</v>
@@ -3257,10 +3427,10 @@
         <v>49</v>
       </c>
       <c r="AP4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -3313,13 +3483,13 @@
         <v>95</v>
       </c>
       <c r="R5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S5" t="s">
         <v>49</v>
       </c>
       <c r="T5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U5" t="s">
         <v>57</v>
@@ -3331,28 +3501,28 @@
         <v>98</v>
       </c>
       <c r="X5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Y5" t="s">
         <v>52</v>
       </c>
       <c r="Z5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA5" t="s">
         <v>101</v>
       </c>
       <c r="AB5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AC5" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="AD5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AF5" t="s">
         <v>65</v>
@@ -3385,10 +3555,10 @@
         <v>49</v>
       </c>
       <c r="AP5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -3396,34 +3566,34 @@
         <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M6" t="s">
         <v>53</v>
@@ -3441,13 +3611,13 @@
         <v>57</v>
       </c>
       <c r="R6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="S6" t="s">
         <v>49</v>
       </c>
       <c r="T6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="U6" t="s">
         <v>57</v>
@@ -3459,28 +3629,28 @@
         <v>60</v>
       </c>
       <c r="X6" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y6" t="s">
         <v>122</v>
       </c>
-      <c r="Y6" t="s">
-        <v>121</v>
-      </c>
       <c r="Z6" t="s">
         <v>49</v>
       </c>
       <c r="AA6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AB6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AC6" t="s">
         <v>62</v>
       </c>
       <c r="AD6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AE6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF6" t="s">
         <v>65</v>
@@ -3513,10 +3683,10 @@
         <v>49</v>
       </c>
       <c r="AP6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -3524,34 +3694,34 @@
         <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s">
         <v>53</v>
@@ -3569,13 +3739,13 @@
         <v>57</v>
       </c>
       <c r="R7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="S7" t="s">
         <v>49</v>
       </c>
       <c r="T7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="U7" t="s">
         <v>57</v>
@@ -3587,28 +3757,28 @@
         <v>60</v>
       </c>
       <c r="X7" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y7" t="s">
         <v>122</v>
       </c>
-      <c r="Y7" t="s">
-        <v>121</v>
-      </c>
       <c r="Z7" t="s">
         <v>49</v>
       </c>
       <c r="AA7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AB7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AC7" t="s">
         <v>62</v>
       </c>
       <c r="AD7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AE7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF7" t="s">
         <v>65</v>
@@ -3641,10 +3811,10 @@
         <v>49</v>
       </c>
       <c r="AP7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -3652,34 +3822,34 @@
         <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M8" t="s">
         <v>53</v>
@@ -3688,10 +3858,10 @@
         <v>54</v>
       </c>
       <c r="O8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q8" t="s">
         <v>57</v>
@@ -3718,13 +3888,13 @@
         <v>96</v>
       </c>
       <c r="Y8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Z8" t="s">
         <v>49</v>
       </c>
       <c r="AA8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AB8" t="s">
         <v>96</v>
@@ -3733,7 +3903,7 @@
         <v>62</v>
       </c>
       <c r="AD8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE8" t="s">
         <v>84</v>
@@ -3769,10 +3939,10 @@
         <v>49</v>
       </c>
       <c r="AP8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -3780,34 +3950,34 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M9" t="s">
         <v>53</v>
@@ -3816,22 +3986,22 @@
         <v>54</v>
       </c>
       <c r="O9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S9" t="s">
         <v>49</v>
       </c>
       <c r="T9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="U9" t="s">
         <v>57</v>
@@ -3840,31 +4010,31 @@
         <v>57</v>
       </c>
       <c r="W9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="X9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Y9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Z9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AA9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AC9" t="s">
         <v>62</v>
       </c>
       <c r="AD9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AE9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF9" t="s">
         <v>65</v>
@@ -3897,10 +4067,10 @@
         <v>49</v>
       </c>
       <c r="AP9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -3908,28 +4078,28 @@
         <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K10" t="s">
         <v>52</v>
@@ -3944,13 +4114,13 @@
         <v>54</v>
       </c>
       <c r="O10" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="P10" t="s">
         <v>161</v>
       </c>
       <c r="Q10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R10" t="s">
         <v>162</v>
@@ -3989,10 +4159,10 @@
         <v>62</v>
       </c>
       <c r="AD10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AF10" t="s">
         <v>65</v>
@@ -4028,7 +4198,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -4114,13 +4284,13 @@
         <v>186</v>
       </c>
       <c r="AC11" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD11" t="s">
         <v>187</v>
       </c>
-      <c r="AD11" t="s">
-        <v>188</v>
-      </c>
       <c r="AE11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AF11" t="s">
         <v>65</v>
@@ -4153,10 +4323,10 @@
         <v>49</v>
       </c>
       <c r="AP11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -4164,28 +4334,28 @@
         <v>43</v>
       </c>
       <c r="C12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" t="s">
         <v>190</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>191</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>192</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>193</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" t="s">
         <v>194</v>
       </c>
-      <c r="H12" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>195</v>
-      </c>
-      <c r="J12" t="s">
-        <v>196</v>
       </c>
       <c r="K12" t="s">
         <v>178</v>
@@ -4203,52 +4373,52 @@
         <v>55</v>
       </c>
       <c r="P12" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q12" t="s">
         <v>197</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>198</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
+        <v>49</v>
+      </c>
+      <c r="T12" t="s">
         <v>199</v>
       </c>
-      <c r="S12" t="s">
-        <v>49</v>
-      </c>
-      <c r="T12" t="s">
+      <c r="U12" t="s">
+        <v>57</v>
+      </c>
+      <c r="V12" t="s">
+        <v>57</v>
+      </c>
+      <c r="W12" t="s">
         <v>200</v>
       </c>
-      <c r="U12" t="s">
-        <v>57</v>
-      </c>
-      <c r="V12" t="s">
-        <v>57</v>
-      </c>
-      <c r="W12" t="s">
+      <c r="X12" t="s">
         <v>201</v>
-      </c>
-      <c r="X12" t="s">
-        <v>202</v>
       </c>
       <c r="Y12" t="s">
         <v>178</v>
       </c>
       <c r="Z12" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA12" t="s">
         <v>203</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AB12" t="s">
         <v>204</v>
       </c>
-      <c r="AB12" t="s">
-        <v>205</v>
-      </c>
       <c r="AC12" t="s">
-        <v>187</v>
+        <v>62</v>
       </c>
       <c r="AD12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AE12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF12" t="s">
         <v>65</v>
@@ -4281,10 +4451,10 @@
         <v>49</v>
       </c>
       <c r="AP12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -4292,28 +4462,28 @@
         <v>43</v>
       </c>
       <c r="C13" t="s">
+        <v>206</v>
+      </c>
+      <c r="D13" t="s">
         <v>207</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>208</v>
-      </c>
-      <c r="E13" t="s">
-        <v>209</v>
       </c>
       <c r="F13" t="s">
         <v>89</v>
       </c>
       <c r="G13" t="s">
+        <v>209</v>
+      </c>
+      <c r="H13" t="s">
         <v>210</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
+        <v>210</v>
+      </c>
+      <c r="J13" t="s">
         <v>211</v>
-      </c>
-      <c r="I13" t="s">
-        <v>211</v>
-      </c>
-      <c r="J13" t="s">
-        <v>212</v>
       </c>
       <c r="K13" t="s">
         <v>178</v>
@@ -4334,16 +4504,16 @@
         <v>75</v>
       </c>
       <c r="Q13" t="s">
+        <v>212</v>
+      </c>
+      <c r="R13" t="s">
         <v>213</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
+        <v>49</v>
+      </c>
+      <c r="T13" t="s">
         <v>214</v>
-      </c>
-      <c r="S13" t="s">
-        <v>49</v>
-      </c>
-      <c r="T13" t="s">
-        <v>215</v>
       </c>
       <c r="U13" t="s">
         <v>57</v>
@@ -4355,22 +4525,22 @@
         <v>164</v>
       </c>
       <c r="X13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Y13" t="s">
         <v>178</v>
       </c>
       <c r="Z13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AA13" t="s">
         <v>179</v>
       </c>
       <c r="AB13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AC13" t="s">
-        <v>187</v>
+        <v>62</v>
       </c>
       <c r="AD13" t="s">
         <v>83</v>
@@ -4409,10 +4579,10 @@
         <v>49</v>
       </c>
       <c r="AP13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -4420,34 +4590,34 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
+        <v>219</v>
+      </c>
+      <c r="D14" t="s">
         <v>220</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>221</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>222</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>223</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" t="s">
         <v>224</v>
       </c>
-      <c r="H14" t="s">
-        <v>49</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>225</v>
-      </c>
-      <c r="J14" t="s">
-        <v>226</v>
       </c>
       <c r="K14" t="s">
         <v>52</v>
       </c>
       <c r="L14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M14" t="s">
         <v>53</v>
@@ -4465,13 +4635,13 @@
         <v>57</v>
       </c>
       <c r="R14" t="s">
+        <v>227</v>
+      </c>
+      <c r="S14" t="s">
+        <v>49</v>
+      </c>
+      <c r="T14" t="s">
         <v>228</v>
-      </c>
-      <c r="S14" t="s">
-        <v>49</v>
-      </c>
-      <c r="T14" t="s">
-        <v>229</v>
       </c>
       <c r="U14" t="s">
         <v>57</v>
@@ -4483,28 +4653,28 @@
         <v>60</v>
       </c>
       <c r="X14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y14" t="s">
+        <v>226</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>203</v>
+      </c>
+      <c r="AB14" t="s">
         <v>227</v>
       </c>
-      <c r="Z14" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>204</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>228</v>
-      </c>
       <c r="AC14" t="s">
-        <v>187</v>
+        <v>62</v>
       </c>
       <c r="AD14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AE14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AF14" t="s">
         <v>65</v>
@@ -4537,10 +4707,10 @@
         <v>49</v>
       </c>
       <c r="AP14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -4548,34 +4718,34 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
+        <v>231</v>
+      </c>
+      <c r="D15" t="s">
         <v>232</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>233</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>234</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>235</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" t="s">
         <v>236</v>
       </c>
-      <c r="H15" t="s">
-        <v>49</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>237</v>
       </c>
-      <c r="J15" t="s">
-        <v>238</v>
-      </c>
       <c r="K15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M15" t="s">
         <v>53</v>
@@ -4584,22 +4754,22 @@
         <v>54</v>
       </c>
       <c r="O15" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="P15" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q15" t="s">
         <v>239</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>240</v>
       </c>
-      <c r="R15" t="s">
+      <c r="S15" t="s">
+        <v>49</v>
+      </c>
+      <c r="T15" t="s">
         <v>241</v>
-      </c>
-      <c r="S15" t="s">
-        <v>49</v>
-      </c>
-      <c r="T15" t="s">
-        <v>242</v>
       </c>
       <c r="U15" t="s">
         <v>57</v>
@@ -4611,28 +4781,28 @@
         <v>164</v>
       </c>
       <c r="X15" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>226</v>
+      </c>
+      <c r="Z15" t="s">
         <v>243</v>
       </c>
-      <c r="Y15" t="s">
-        <v>227</v>
-      </c>
-      <c r="Z15" t="s">
+      <c r="AA15" t="s">
         <v>244</v>
       </c>
-      <c r="AA15" t="s">
+      <c r="AB15" t="s">
         <v>245</v>
       </c>
-      <c r="AB15" t="s">
-        <v>246</v>
-      </c>
       <c r="AC15" t="s">
-        <v>187</v>
+        <v>62</v>
       </c>
       <c r="AD15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AE15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF15" t="s">
         <v>65</v>
@@ -4665,10 +4835,10 @@
         <v>49</v>
       </c>
       <c r="AP15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -4676,34 +4846,34 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
+        <v>247</v>
+      </c>
+      <c r="D16" t="s">
         <v>248</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>249</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>250</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>251</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" t="s">
         <v>252</v>
       </c>
-      <c r="H16" t="s">
-        <v>49</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>253</v>
-      </c>
-      <c r="J16" t="s">
-        <v>254</v>
       </c>
       <c r="K16" t="s">
         <v>177</v>
       </c>
       <c r="L16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M16" t="s">
         <v>53</v>
@@ -4715,52 +4885,52 @@
         <v>55</v>
       </c>
       <c r="P16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q16" t="s">
         <v>76</v>
       </c>
       <c r="R16" t="s">
+        <v>254</v>
+      </c>
+      <c r="S16" t="s">
+        <v>49</v>
+      </c>
+      <c r="T16" t="s">
         <v>255</v>
       </c>
-      <c r="S16" t="s">
-        <v>49</v>
-      </c>
-      <c r="T16" t="s">
+      <c r="U16" t="s">
+        <v>57</v>
+      </c>
+      <c r="V16" t="s">
+        <v>57</v>
+      </c>
+      <c r="W16" t="s">
         <v>256</v>
       </c>
-      <c r="U16" t="s">
-        <v>57</v>
-      </c>
-      <c r="V16" t="s">
-        <v>57</v>
-      </c>
-      <c r="W16" t="s">
+      <c r="X16" t="s">
         <v>257</v>
       </c>
-      <c r="X16" t="s">
+      <c r="Y16" t="s">
+        <v>226</v>
+      </c>
+      <c r="Z16" t="s">
         <v>258</v>
       </c>
-      <c r="Y16" t="s">
-        <v>227</v>
-      </c>
-      <c r="Z16" t="s">
+      <c r="AA16" t="s">
         <v>259</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="AB16" t="s">
         <v>260</v>
       </c>
-      <c r="AB16" t="s">
+      <c r="AC16" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD16" t="s">
         <v>261</v>
       </c>
-      <c r="AC16" t="s">
-        <v>187</v>
-      </c>
-      <c r="AD16" t="s">
+      <c r="AE16" t="s">
         <v>262</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>263</v>
       </c>
       <c r="AF16" t="s">
         <v>65</v>
@@ -4793,10 +4963,10 @@
         <v>49</v>
       </c>
       <c r="AP16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -4804,34 +4974,34 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
+        <v>264</v>
+      </c>
+      <c r="D17" t="s">
         <v>265</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>266</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>267</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>268</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" t="s">
         <v>269</v>
       </c>
-      <c r="H17" t="s">
-        <v>49</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>270</v>
       </c>
-      <c r="J17" t="s">
-        <v>271</v>
-      </c>
       <c r="K17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M17" t="s">
         <v>53</v>
@@ -4846,43 +5016,43 @@
         <v>56</v>
       </c>
       <c r="Q17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R17" t="s">
+        <v>271</v>
+      </c>
+      <c r="S17" t="s">
+        <v>49</v>
+      </c>
+      <c r="T17" t="s">
         <v>272</v>
       </c>
-      <c r="S17" t="s">
-        <v>49</v>
-      </c>
-      <c r="T17" t="s">
+      <c r="U17" t="s">
+        <v>57</v>
+      </c>
+      <c r="V17" t="s">
+        <v>57</v>
+      </c>
+      <c r="W17" t="s">
+        <v>256</v>
+      </c>
+      <c r="X17" t="s">
         <v>273</v>
       </c>
-      <c r="U17" t="s">
-        <v>57</v>
-      </c>
-      <c r="V17" t="s">
-        <v>57</v>
-      </c>
-      <c r="W17" t="s">
-        <v>257</v>
-      </c>
-      <c r="X17" t="s">
+      <c r="Y17" t="s">
+        <v>226</v>
+      </c>
+      <c r="Z17" t="s">
         <v>274</v>
       </c>
-      <c r="Y17" t="s">
-        <v>227</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>275</v>
-      </c>
       <c r="AA17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AB17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AC17" t="s">
-        <v>187</v>
+        <v>62</v>
       </c>
       <c r="AD17" t="s">
         <v>63</v>
@@ -4921,10 +5091,10 @@
         <v>49</v>
       </c>
       <c r="AP17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -4932,34 +5102,34 @@
         <v>43</v>
       </c>
       <c r="C18" t="s">
+        <v>276</v>
+      </c>
+      <c r="D18" t="s">
         <v>277</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>278</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
+        <v>234</v>
+      </c>
+      <c r="G18" t="s">
         <v>279</v>
       </c>
-      <c r="F18" t="s">
-        <v>235</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>280</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
+        <v>280</v>
+      </c>
+      <c r="J18" t="s">
         <v>281</v>
       </c>
-      <c r="I18" t="s">
-        <v>281</v>
-      </c>
-      <c r="J18" t="s">
-        <v>282</v>
-      </c>
       <c r="K18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M18" t="s">
         <v>53</v>
@@ -4974,16 +5144,16 @@
         <v>56</v>
       </c>
       <c r="Q18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R18" t="s">
+        <v>282</v>
+      </c>
+      <c r="S18" t="s">
+        <v>49</v>
+      </c>
+      <c r="T18" t="s">
         <v>283</v>
-      </c>
-      <c r="S18" t="s">
-        <v>49</v>
-      </c>
-      <c r="T18" t="s">
-        <v>284</v>
       </c>
       <c r="U18" t="s">
         <v>57</v>
@@ -4995,28 +5165,28 @@
         <v>164</v>
       </c>
       <c r="X18" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Y18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AA18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AB18" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AC18" t="s">
-        <v>187</v>
+        <v>62</v>
       </c>
       <c r="AD18" t="s">
+        <v>261</v>
+      </c>
+      <c r="AE18" t="s">
         <v>262</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>263</v>
       </c>
       <c r="AF18" t="s">
         <v>65</v>
@@ -5049,10 +5219,10 @@
         <v>49</v>
       </c>
       <c r="AP18" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -5060,34 +5230,34 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
+        <v>286</v>
+      </c>
+      <c r="D19" t="s">
         <v>287</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>288</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>234</v>
+      </c>
+      <c r="G19" t="s">
+        <v>279</v>
+      </c>
+      <c r="H19" t="s">
+        <v>280</v>
+      </c>
+      <c r="I19" t="s">
+        <v>280</v>
+      </c>
+      <c r="J19" t="s">
         <v>289</v>
       </c>
-      <c r="F19" t="s">
-        <v>235</v>
-      </c>
-      <c r="G19" t="s">
-        <v>280</v>
-      </c>
-      <c r="H19" t="s">
-        <v>281</v>
-      </c>
-      <c r="I19" t="s">
-        <v>281</v>
-      </c>
-      <c r="J19" t="s">
-        <v>290</v>
-      </c>
       <c r="K19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M19" t="s">
         <v>53</v>
@@ -5102,49 +5272,49 @@
         <v>56</v>
       </c>
       <c r="Q19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R19" t="s">
+        <v>290</v>
+      </c>
+      <c r="S19" t="s">
+        <v>49</v>
+      </c>
+      <c r="T19" t="s">
         <v>291</v>
       </c>
-      <c r="S19" t="s">
-        <v>49</v>
-      </c>
-      <c r="T19" t="s">
+      <c r="U19" t="s">
+        <v>57</v>
+      </c>
+      <c r="V19" t="s">
+        <v>57</v>
+      </c>
+      <c r="W19" t="s">
+        <v>200</v>
+      </c>
+      <c r="X19" t="s">
         <v>292</v>
       </c>
-      <c r="U19" t="s">
-        <v>57</v>
-      </c>
-      <c r="V19" t="s">
-        <v>57</v>
-      </c>
-      <c r="W19" t="s">
-        <v>201</v>
-      </c>
-      <c r="X19" t="s">
+      <c r="Y19" t="s">
+        <v>226</v>
+      </c>
+      <c r="Z19" t="s">
         <v>293</v>
       </c>
-      <c r="Y19" t="s">
-        <v>227</v>
-      </c>
-      <c r="Z19" t="s">
+      <c r="AA19" t="s">
+        <v>239</v>
+      </c>
+      <c r="AB19" t="s">
         <v>294</v>
       </c>
-      <c r="AA19" t="s">
-        <v>240</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>295</v>
-      </c>
       <c r="AC19" t="s">
-        <v>187</v>
+        <v>62</v>
       </c>
       <c r="AD19" t="s">
+        <v>261</v>
+      </c>
+      <c r="AE19" t="s">
         <v>262</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>263</v>
       </c>
       <c r="AF19" t="s">
         <v>65</v>
@@ -5177,10 +5347,10 @@
         <v>49</v>
       </c>
       <c r="AP19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -5188,34 +5358,34 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
+        <v>296</v>
+      </c>
+      <c r="D20" t="s">
         <v>297</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>298</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>299</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>300</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" t="s">
         <v>301</v>
       </c>
-      <c r="H20" t="s">
-        <v>49</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>302</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>303</v>
       </c>
-      <c r="K20" t="s">
-        <v>304</v>
-      </c>
       <c r="L20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M20" t="s">
         <v>53</v>
@@ -5230,49 +5400,49 @@
         <v>94</v>
       </c>
       <c r="Q20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="S20" t="s">
         <v>49</v>
       </c>
       <c r="T20" t="s">
+        <v>304</v>
+      </c>
+      <c r="U20" t="s">
+        <v>57</v>
+      </c>
+      <c r="V20" t="s">
+        <v>57</v>
+      </c>
+      <c r="W20" t="s">
+        <v>200</v>
+      </c>
+      <c r="X20" t="s">
         <v>305</v>
       </c>
-      <c r="U20" t="s">
-        <v>57</v>
-      </c>
-      <c r="V20" t="s">
-        <v>57</v>
-      </c>
-      <c r="W20" t="s">
-        <v>201</v>
-      </c>
-      <c r="X20" t="s">
+      <c r="Y20" t="s">
+        <v>303</v>
+      </c>
+      <c r="Z20" t="s">
         <v>306</v>
       </c>
-      <c r="Y20" t="s">
-        <v>304</v>
-      </c>
-      <c r="Z20" t="s">
+      <c r="AA20" t="s">
         <v>307</v>
       </c>
-      <c r="AA20" t="s">
+      <c r="AB20" t="s">
         <v>308</v>
       </c>
-      <c r="AB20" t="s">
+      <c r="AC20" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD20" t="s">
         <v>309</v>
       </c>
-      <c r="AC20" t="s">
-        <v>187</v>
-      </c>
-      <c r="AD20" t="s">
+      <c r="AE20" t="s">
         <v>310</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>311</v>
       </c>
       <c r="AF20" t="s">
         <v>65</v>
@@ -5305,10 +5475,10 @@
         <v>49</v>
       </c>
       <c r="AP20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -5316,34 +5486,34 @@
         <v>43</v>
       </c>
       <c r="C21" t="s">
+        <v>312</v>
+      </c>
+      <c r="D21" t="s">
         <v>313</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>314</v>
-      </c>
-      <c r="E21" t="s">
-        <v>315</v>
       </c>
       <c r="F21" t="s">
         <v>89</v>
       </c>
       <c r="G21" t="s">
+        <v>315</v>
+      </c>
+      <c r="H21" t="s">
+        <v>49</v>
+      </c>
+      <c r="I21" t="s">
         <v>316</v>
       </c>
-      <c r="H21" t="s">
-        <v>49</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>317</v>
       </c>
-      <c r="J21" t="s">
-        <v>318</v>
-      </c>
       <c r="K21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M21" t="s">
         <v>53</v>
@@ -5355,52 +5525,52 @@
         <v>55</v>
       </c>
       <c r="P21" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q21" t="s">
         <v>319</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>320</v>
       </c>
-      <c r="R21" t="s">
+      <c r="S21" t="s">
+        <v>49</v>
+      </c>
+      <c r="T21" t="s">
         <v>321</v>
       </c>
-      <c r="S21" t="s">
-        <v>49</v>
-      </c>
-      <c r="T21" t="s">
+      <c r="U21" t="s">
+        <v>57</v>
+      </c>
+      <c r="V21" t="s">
+        <v>57</v>
+      </c>
+      <c r="W21" t="s">
         <v>322</v>
       </c>
-      <c r="U21" t="s">
-        <v>57</v>
-      </c>
-      <c r="V21" t="s">
-        <v>57</v>
-      </c>
-      <c r="W21" t="s">
+      <c r="X21" t="s">
         <v>323</v>
       </c>
-      <c r="X21" t="s">
+      <c r="Y21" t="s">
+        <v>303</v>
+      </c>
+      <c r="Z21" t="s">
         <v>324</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>304</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>325</v>
       </c>
       <c r="AA21" t="s">
         <v>179</v>
       </c>
       <c r="AB21" t="s">
+        <v>325</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD21" t="s">
         <v>326</v>
       </c>
-      <c r="AC21" t="s">
-        <v>187</v>
-      </c>
-      <c r="AD21" t="s">
+      <c r="AE21" t="s">
         <v>327</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>328</v>
       </c>
       <c r="AF21" t="s">
         <v>65</v>
@@ -5433,10 +5603,10 @@
         <v>49</v>
       </c>
       <c r="AP21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -5444,34 +5614,34 @@
         <v>43</v>
       </c>
       <c r="C22" t="s">
+        <v>329</v>
+      </c>
+      <c r="D22" t="s">
         <v>330</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>331</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>332</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>333</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" t="s">
         <v>334</v>
       </c>
-      <c r="H22" t="s">
-        <v>49</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>335</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
+        <v>226</v>
+      </c>
+      <c r="L22" t="s">
         <v>336</v>
-      </c>
-      <c r="K22" t="s">
-        <v>227</v>
-      </c>
-      <c r="L22" t="s">
-        <v>337</v>
       </c>
       <c r="M22" t="s">
         <v>53</v>
@@ -5480,22 +5650,22 @@
         <v>54</v>
       </c>
       <c r="O22" t="s">
+        <v>337</v>
+      </c>
+      <c r="P22" t="s">
         <v>338</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
+        <v>57</v>
+      </c>
+      <c r="R22" t="s">
         <v>339</v>
       </c>
-      <c r="Q22" t="s">
-        <v>57</v>
-      </c>
-      <c r="R22" t="s">
+      <c r="S22" t="s">
+        <v>49</v>
+      </c>
+      <c r="T22" t="s">
         <v>340</v>
-      </c>
-      <c r="S22" t="s">
-        <v>49</v>
-      </c>
-      <c r="T22" t="s">
-        <v>341</v>
       </c>
       <c r="U22" t="s">
         <v>57</v>
@@ -5507,22 +5677,22 @@
         <v>60</v>
       </c>
       <c r="X22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Y22" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Z22" t="s">
         <v>49</v>
       </c>
       <c r="AA22" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AB22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AC22" t="s">
-        <v>187</v>
+        <v>62</v>
       </c>
       <c r="AD22" t="s">
         <v>83</v>
@@ -5561,10 +5731,10 @@
         <v>49</v>
       </c>
       <c r="AP22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -5572,34 +5742,34 @@
         <v>43</v>
       </c>
       <c r="C23" t="s">
+        <v>343</v>
+      </c>
+      <c r="D23" t="s">
         <v>344</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>345</v>
-      </c>
-      <c r="E23" t="s">
-        <v>346</v>
       </c>
       <c r="F23" t="s">
         <v>89</v>
       </c>
       <c r="G23" t="s">
+        <v>346</v>
+      </c>
+      <c r="H23" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" t="s">
         <v>347</v>
       </c>
-      <c r="H23" t="s">
-        <v>49</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>348</v>
       </c>
-      <c r="J23" t="s">
-        <v>349</v>
-      </c>
       <c r="K23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L23" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M23" t="s">
         <v>53</v>
@@ -5611,52 +5781,52 @@
         <v>55</v>
       </c>
       <c r="P23" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q23" t="s">
         <v>76</v>
       </c>
       <c r="R23" t="s">
+        <v>349</v>
+      </c>
+      <c r="S23" t="s">
+        <v>49</v>
+      </c>
+      <c r="T23" t="s">
         <v>350</v>
       </c>
-      <c r="S23" t="s">
-        <v>49</v>
-      </c>
-      <c r="T23" t="s">
+      <c r="U23" t="s">
+        <v>57</v>
+      </c>
+      <c r="V23" t="s">
+        <v>57</v>
+      </c>
+      <c r="W23" t="s">
         <v>351</v>
-      </c>
-      <c r="U23" t="s">
-        <v>57</v>
-      </c>
-      <c r="V23" t="s">
-        <v>57</v>
-      </c>
-      <c r="W23" t="s">
-        <v>352</v>
       </c>
       <c r="X23" t="s">
         <v>165</v>
       </c>
       <c r="Y23" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Z23" t="s">
+        <v>352</v>
+      </c>
+      <c r="AA23" t="s">
         <v>353</v>
       </c>
-      <c r="AA23" t="s">
+      <c r="AB23" t="s">
         <v>354</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>355</v>
       </c>
       <c r="AC23" t="s">
         <v>62</v>
       </c>
       <c r="AD23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AF23" t="s">
         <v>65</v>
@@ -5689,10 +5859,10 @@
         <v>49</v>
       </c>
       <c r="AP23" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -5700,34 +5870,34 @@
         <v>43</v>
       </c>
       <c r="C24" t="s">
+        <v>356</v>
+      </c>
+      <c r="D24" t="s">
         <v>357</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>358</v>
-      </c>
-      <c r="E24" t="s">
-        <v>359</v>
       </c>
       <c r="F24" t="s">
         <v>89</v>
       </c>
       <c r="G24" t="s">
+        <v>359</v>
+      </c>
+      <c r="H24" t="s">
+        <v>49</v>
+      </c>
+      <c r="I24" t="s">
         <v>360</v>
       </c>
-      <c r="H24" t="s">
-        <v>49</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>361</v>
       </c>
-      <c r="J24" t="s">
-        <v>362</v>
-      </c>
       <c r="K24" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L24" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M24" t="s">
         <v>53</v>
@@ -5745,13 +5915,13 @@
         <v>57</v>
       </c>
       <c r="R24" t="s">
+        <v>362</v>
+      </c>
+      <c r="S24" t="s">
+        <v>49</v>
+      </c>
+      <c r="T24" t="s">
         <v>363</v>
-      </c>
-      <c r="S24" t="s">
-        <v>49</v>
-      </c>
-      <c r="T24" t="s">
-        <v>364</v>
       </c>
       <c r="U24" t="s">
         <v>57</v>
@@ -5763,25 +5933,25 @@
         <v>60</v>
       </c>
       <c r="X24" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Y24" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Z24" t="s">
         <v>49</v>
       </c>
       <c r="AA24" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AB24" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AC24" t="s">
-        <v>187</v>
+        <v>62</v>
       </c>
       <c r="AD24" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AE24" t="s">
         <v>64</v>
@@ -5817,10 +5987,10 @@
         <v>49</v>
       </c>
       <c r="AP24" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -5828,34 +5998,34 @@
         <v>43</v>
       </c>
       <c r="C25" t="s">
+        <v>356</v>
+      </c>
+      <c r="D25" t="s">
         <v>357</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>358</v>
-      </c>
-      <c r="E25" t="s">
-        <v>359</v>
       </c>
       <c r="F25" t="s">
         <v>89</v>
       </c>
       <c r="G25" t="s">
+        <v>359</v>
+      </c>
+      <c r="H25" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" t="s">
         <v>360</v>
       </c>
-      <c r="H25" t="s">
-        <v>49</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>361</v>
       </c>
-      <c r="J25" t="s">
-        <v>362</v>
-      </c>
       <c r="K25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M25" t="s">
         <v>53</v>
@@ -5873,13 +6043,13 @@
         <v>57</v>
       </c>
       <c r="R25" t="s">
+        <v>362</v>
+      </c>
+      <c r="S25" t="s">
+        <v>49</v>
+      </c>
+      <c r="T25" t="s">
         <v>363</v>
-      </c>
-      <c r="S25" t="s">
-        <v>49</v>
-      </c>
-      <c r="T25" t="s">
-        <v>364</v>
       </c>
       <c r="U25" t="s">
         <v>57</v>
@@ -5891,25 +6061,25 @@
         <v>60</v>
       </c>
       <c r="X25" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Y25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Z25" t="s">
         <v>49</v>
       </c>
       <c r="AA25" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AB25" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AC25" t="s">
-        <v>187</v>
+        <v>62</v>
       </c>
       <c r="AD25" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AE25" t="s">
         <v>64</v>
@@ -5945,10 +6115,10 @@
         <v>49</v>
       </c>
       <c r="AP25" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -5956,34 +6126,34 @@
         <v>43</v>
       </c>
       <c r="C26" t="s">
+        <v>367</v>
+      </c>
+      <c r="D26" t="s">
         <v>368</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>369</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>370</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>371</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
+        <v>49</v>
+      </c>
+      <c r="I26" t="s">
         <v>372</v>
       </c>
-      <c r="H26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>373</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>374</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>375</v>
-      </c>
-      <c r="L26" t="s">
-        <v>376</v>
       </c>
       <c r="M26" t="s">
         <v>53</v>
@@ -5995,19 +6165,19 @@
         <v>55</v>
       </c>
       <c r="P26" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q26" t="s">
         <v>76</v>
       </c>
       <c r="R26" t="s">
+        <v>377</v>
+      </c>
+      <c r="S26" t="s">
+        <v>49</v>
+      </c>
+      <c r="T26" t="s">
         <v>378</v>
-      </c>
-      <c r="S26" t="s">
-        <v>49</v>
-      </c>
-      <c r="T26" t="s">
-        <v>379</v>
       </c>
       <c r="U26" t="s">
         <v>57</v>
@@ -6019,25 +6189,25 @@
         <v>79</v>
       </c>
       <c r="X26" t="s">
+        <v>379</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>375</v>
+      </c>
+      <c r="Z26" t="s">
         <v>380</v>
       </c>
-      <c r="Y26" t="s">
-        <v>376</v>
-      </c>
-      <c r="Z26" t="s">
+      <c r="AA26" t="s">
         <v>381</v>
       </c>
-      <c r="AA26" t="s">
-        <v>382</v>
-      </c>
       <c r="AB26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AC26" t="s">
         <v>62</v>
       </c>
       <c r="AD26" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AE26" t="s">
         <v>84</v>
@@ -6073,10 +6243,10 @@
         <v>49</v>
       </c>
       <c r="AP26" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -6084,34 +6254,34 @@
         <v>43</v>
       </c>
       <c r="C27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D27" t="s">
         <v>385</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>386</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
+        <v>370</v>
+      </c>
+      <c r="G27" t="s">
+        <v>371</v>
+      </c>
+      <c r="H27" t="s">
+        <v>49</v>
+      </c>
+      <c r="I27" t="s">
         <v>387</v>
       </c>
-      <c r="F27" t="s">
-        <v>371</v>
-      </c>
-      <c r="G27" t="s">
-        <v>372</v>
-      </c>
-      <c r="H27" t="s">
-        <v>49</v>
-      </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>388</v>
       </c>
-      <c r="J27" t="s">
-        <v>389</v>
-      </c>
       <c r="K27" t="s">
+        <v>374</v>
+      </c>
+      <c r="L27" t="s">
         <v>375</v>
-      </c>
-      <c r="L27" t="s">
-        <v>376</v>
       </c>
       <c r="M27" t="s">
         <v>53</v>
@@ -6123,19 +6293,19 @@
         <v>55</v>
       </c>
       <c r="P27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q27" t="s">
         <v>76</v>
       </c>
       <c r="R27" t="s">
+        <v>377</v>
+      </c>
+      <c r="S27" t="s">
+        <v>49</v>
+      </c>
+      <c r="T27" t="s">
         <v>378</v>
-      </c>
-      <c r="S27" t="s">
-        <v>49</v>
-      </c>
-      <c r="T27" t="s">
-        <v>379</v>
       </c>
       <c r="U27" t="s">
         <v>57</v>
@@ -6147,25 +6317,25 @@
         <v>79</v>
       </c>
       <c r="X27" t="s">
+        <v>379</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>375</v>
+      </c>
+      <c r="Z27" t="s">
         <v>380</v>
       </c>
-      <c r="Y27" t="s">
-        <v>376</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>381</v>
-      </c>
       <c r="AA27" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AB27" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AC27" t="s">
         <v>62</v>
       </c>
       <c r="AD27" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AE27" t="s">
         <v>84</v>
@@ -6201,10 +6371,10 @@
         <v>49</v>
       </c>
       <c r="AP27" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -6212,34 +6382,34 @@
         <v>43</v>
       </c>
       <c r="C28" t="s">
+        <v>390</v>
+      </c>
+      <c r="D28" t="s">
         <v>391</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>392</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>393</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>394</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
+        <v>49</v>
+      </c>
+      <c r="I28" t="s">
         <v>395</v>
       </c>
-      <c r="H28" t="s">
-        <v>49</v>
-      </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>396</v>
       </c>
-      <c r="J28" t="s">
-        <v>397</v>
-      </c>
       <c r="K28" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L28" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M28" t="s">
         <v>53</v>
@@ -6248,22 +6418,22 @@
         <v>54</v>
       </c>
       <c r="O28" t="s">
+        <v>397</v>
+      </c>
+      <c r="P28" t="s">
         <v>398</v>
       </c>
-      <c r="P28" t="s">
-        <v>399</v>
-      </c>
       <c r="Q28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R28" t="s">
+        <v>198</v>
+      </c>
+      <c r="S28" t="s">
+        <v>49</v>
+      </c>
+      <c r="T28" t="s">
         <v>199</v>
-      </c>
-      <c r="S28" t="s">
-        <v>49</v>
-      </c>
-      <c r="T28" t="s">
-        <v>200</v>
       </c>
       <c r="U28" t="s">
         <v>57</v>
@@ -6278,13 +6448,13 @@
         <v>80</v>
       </c>
       <c r="Y28" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Z28" t="s">
-        <v>241</v>
+        <v>399</v>
       </c>
       <c r="AA28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AB28" t="s">
         <v>400</v>
@@ -6293,10 +6463,10 @@
         <v>62</v>
       </c>
       <c r="AD28" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AE28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF28" t="s">
         <v>65</v>
@@ -6332,7 +6502,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -6349,7 +6519,7 @@
         <v>404</v>
       </c>
       <c r="F29" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G29" t="s">
         <v>405</v>
@@ -6364,10 +6534,10 @@
         <v>407</v>
       </c>
       <c r="K29" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L29" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M29" t="s">
         <v>53</v>
@@ -6376,7 +6546,7 @@
         <v>54</v>
       </c>
       <c r="O29" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="P29" t="s">
         <v>408</v>
@@ -6385,13 +6555,13 @@
         <v>95</v>
       </c>
       <c r="R29" t="s">
+        <v>349</v>
+      </c>
+      <c r="S29" t="s">
+        <v>49</v>
+      </c>
+      <c r="T29" t="s">
         <v>350</v>
-      </c>
-      <c r="S29" t="s">
-        <v>49</v>
-      </c>
-      <c r="T29" t="s">
-        <v>351</v>
       </c>
       <c r="U29" t="s">
         <v>57</v>
@@ -6406,7 +6576,7 @@
         <v>409</v>
       </c>
       <c r="Y29" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z29" t="s">
         <v>410</v>
@@ -6418,13 +6588,13 @@
         <v>412</v>
       </c>
       <c r="AC29" t="s">
-        <v>187</v>
+        <v>62</v>
       </c>
       <c r="AD29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AF29" t="s">
         <v>65</v>
@@ -6460,7 +6630,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -6528,16 +6698,16 @@
         <v>57</v>
       </c>
       <c r="W30" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="X30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Y30" t="s">
         <v>421</v>
       </c>
       <c r="Z30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AA30" t="s">
         <v>424</v>
@@ -6546,13 +6716,13 @@
         <v>425</v>
       </c>
       <c r="AC30" t="s">
-        <v>187</v>
+        <v>62</v>
       </c>
       <c r="AD30" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AE30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF30" t="s">
         <v>65</v>
@@ -6588,7 +6758,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -6656,16 +6826,16 @@
         <v>57</v>
       </c>
       <c r="W31" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="X31" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Y31" t="s">
         <v>421</v>
       </c>
       <c r="Z31" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AA31" t="s">
         <v>424</v>
@@ -6677,10 +6847,10 @@
         <v>62</v>
       </c>
       <c r="AD31" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AE31" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF31" t="s">
         <v>65</v>
@@ -6716,7 +6886,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -6733,7 +6903,7 @@
         <v>435</v>
       </c>
       <c r="F32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G32" t="s">
         <v>436</v>
@@ -6751,7 +6921,7 @@
         <v>421</v>
       </c>
       <c r="L32" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M32" t="s">
         <v>53</v>
@@ -6760,13 +6930,13 @@
         <v>54</v>
       </c>
       <c r="O32" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="P32" t="s">
         <v>439</v>
       </c>
       <c r="Q32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R32" t="s">
         <v>162</v>
@@ -6790,7 +6960,7 @@
         <v>165</v>
       </c>
       <c r="Y32" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Z32" t="s">
         <v>166</v>
@@ -6802,13 +6972,13 @@
         <v>441</v>
       </c>
       <c r="AC32" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="AD32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AF32" t="s">
         <v>65</v>
@@ -6844,7 +7014,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -6861,7 +7031,7 @@
         <v>445</v>
       </c>
       <c r="F33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G33" t="s">
         <v>446</v>
@@ -6876,10 +7046,10 @@
         <v>448</v>
       </c>
       <c r="K33" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L33" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="M33" t="s">
         <v>53</v>
@@ -6888,7 +7058,7 @@
         <v>54</v>
       </c>
       <c r="O33" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="P33" t="s">
         <v>449</v>
@@ -6918,19 +7088,19 @@
         <v>452</v>
       </c>
       <c r="Y33" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Z33" t="s">
         <v>453</v>
       </c>
       <c r="AA33" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AB33" t="s">
         <v>454</v>
       </c>
       <c r="AC33" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="AD33" t="s">
         <v>455</v>
@@ -6972,7 +7142,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -6989,7 +7159,7 @@
         <v>460</v>
       </c>
       <c r="F34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G34" t="s">
         <v>461</v>
@@ -7016,7 +7186,7 @@
         <v>54</v>
       </c>
       <c r="O34" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="P34" t="s">
         <v>449</v>
@@ -7061,10 +7231,10 @@
         <v>469</v>
       </c>
       <c r="AD34" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AE34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AF34" t="s">
         <v>65</v>
@@ -7100,7 +7270,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -7147,10 +7317,10 @@
         <v>55</v>
       </c>
       <c r="P35" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q35" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R35" t="s">
         <v>479</v>
@@ -7183,13 +7353,13 @@
         <v>440</v>
       </c>
       <c r="AB35" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AC35" t="s">
         <v>469</v>
       </c>
       <c r="AD35" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE35" t="s">
         <v>84</v>
@@ -7228,7 +7398,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>42</v>
       </c>
@@ -7275,10 +7445,10 @@
         <v>55</v>
       </c>
       <c r="P36" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q36" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R36" t="s">
         <v>479</v>
@@ -7311,13 +7481,13 @@
         <v>440</v>
       </c>
       <c r="AB36" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AC36" t="s">
         <v>469</v>
       </c>
       <c r="AD36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE36" t="s">
         <v>84</v>
@@ -7356,7 +7526,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -7373,7 +7543,7 @@
         <v>491</v>
       </c>
       <c r="F37" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G37" t="s">
         <v>492</v>
@@ -7388,7 +7558,7 @@
         <v>494</v>
       </c>
       <c r="K37" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L37" t="s">
         <v>495</v>
@@ -7403,7 +7573,7 @@
         <v>55</v>
       </c>
       <c r="P37" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q37" t="s">
         <v>57</v>
@@ -7448,7 +7618,7 @@
         <v>498</v>
       </c>
       <c r="AE37" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AF37" t="s">
         <v>65</v>
@@ -7484,7 +7654,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -7534,7 +7704,7 @@
         <v>510</v>
       </c>
       <c r="Q38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="R38" t="s">
         <v>482</v>
@@ -7552,7 +7722,7 @@
         <v>57</v>
       </c>
       <c r="W38" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="X38" t="s">
         <v>481</v>
@@ -7576,7 +7746,7 @@
         <v>515</v>
       </c>
       <c r="AE38" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AF38" t="s">
         <v>65</v>
@@ -7612,7 +7782,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -7656,7 +7826,7 @@
         <v>54</v>
       </c>
       <c r="O39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P39" t="s">
         <v>524</v>
@@ -7704,7 +7874,7 @@
         <v>528</v>
       </c>
       <c r="AE39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AF39" t="s">
         <v>65</v>
@@ -7740,7 +7910,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -7784,13 +7954,13 @@
         <v>54</v>
       </c>
       <c r="O40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P40" t="s">
         <v>537</v>
       </c>
       <c r="Q40" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R40" t="s">
         <v>482</v>
@@ -7817,7 +7987,7 @@
         <v>478</v>
       </c>
       <c r="Z40" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AA40" t="s">
         <v>513</v>
@@ -7832,7 +8002,7 @@
         <v>515</v>
       </c>
       <c r="AE40" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AF40" t="s">
         <v>65</v>
@@ -7868,7 +8038,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -7915,13 +8085,13 @@
         <v>55</v>
       </c>
       <c r="P41" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q41" t="s">
         <v>60</v>
       </c>
       <c r="R41" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S41" t="s">
         <v>49</v>
@@ -7936,10 +8106,10 @@
         <v>57</v>
       </c>
       <c r="W41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="X41" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Y41" t="s">
         <v>478</v>
@@ -7954,13 +8124,13 @@
         <v>542</v>
       </c>
       <c r="AC41" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="AD41" t="s">
+        <v>326</v>
+      </c>
+      <c r="AE41" t="s">
         <v>327</v>
-      </c>
-      <c r="AE41" t="s">
-        <v>328</v>
       </c>
       <c r="AF41" t="s">
         <v>65</v>
@@ -7996,7 +8166,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -8013,7 +8183,7 @@
         <v>546</v>
       </c>
       <c r="F42" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G42" t="s">
         <v>547</v>
@@ -8040,10 +8210,10 @@
         <v>54</v>
       </c>
       <c r="O42" t="s">
+        <v>397</v>
+      </c>
+      <c r="P42" t="s">
         <v>398</v>
-      </c>
-      <c r="P42" t="s">
-        <v>399</v>
       </c>
       <c r="Q42" t="s">
         <v>76</v>
@@ -8064,7 +8234,7 @@
         <v>57</v>
       </c>
       <c r="W42" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="X42" t="s">
         <v>552</v>
@@ -8082,13 +8252,13 @@
         <v>554</v>
       </c>
       <c r="AC42" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="AD42" t="s">
+        <v>309</v>
+      </c>
+      <c r="AE42" t="s">
         <v>310</v>
-      </c>
-      <c r="AE42" t="s">
-        <v>311</v>
       </c>
       <c r="AF42" t="s">
         <v>65</v>
@@ -8124,7 +8294,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -8141,7 +8311,7 @@
         <v>558</v>
       </c>
       <c r="F43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G43" t="s">
         <v>461</v>
@@ -8168,13 +8338,13 @@
         <v>54</v>
       </c>
       <c r="O43" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="P43" t="s">
         <v>449</v>
       </c>
       <c r="Q43" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R43" t="s">
         <v>562</v>
@@ -8192,10 +8362,10 @@
         <v>57</v>
       </c>
       <c r="W43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="X43" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Y43" t="s">
         <v>495</v>
@@ -8210,10 +8380,10 @@
         <v>565</v>
       </c>
       <c r="AC43" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="AD43" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AE43" t="s">
         <v>64</v>
@@ -8252,7 +8422,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -8269,7 +8439,7 @@
         <v>460</v>
       </c>
       <c r="F44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G44" t="s">
         <v>461</v>
@@ -8296,7 +8466,7 @@
         <v>54</v>
       </c>
       <c r="O44" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="P44" t="s">
         <v>449</v>
@@ -8341,10 +8511,10 @@
         <v>62</v>
       </c>
       <c r="AD44" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AE44" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AF44" t="s">
         <v>65</v>
@@ -8380,7 +8550,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>42</v>
       </c>
@@ -8397,7 +8567,7 @@
         <v>573</v>
       </c>
       <c r="F45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G45" t="s">
         <v>574</v>
@@ -8424,22 +8594,22 @@
         <v>54</v>
       </c>
       <c r="O45" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="P45" t="s">
         <v>577</v>
       </c>
       <c r="Q45" t="s">
+        <v>95</v>
+      </c>
+      <c r="R45" t="s">
         <v>578</v>
       </c>
-      <c r="R45" t="s">
+      <c r="S45" t="s">
+        <v>49</v>
+      </c>
+      <c r="T45" t="s">
         <v>579</v>
-      </c>
-      <c r="S45" t="s">
-        <v>49</v>
-      </c>
-      <c r="T45" t="s">
-        <v>580</v>
       </c>
       <c r="U45" t="s">
         <v>57</v>
@@ -8451,28 +8621,28 @@
         <v>164</v>
       </c>
       <c r="X45" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Y45" t="s">
         <v>508</v>
       </c>
       <c r="Z45" t="s">
+        <v>581</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>440</v>
+      </c>
+      <c r="AB45" t="s">
         <v>582</v>
-      </c>
-      <c r="AA45" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB45" t="s">
-        <v>583</v>
       </c>
       <c r="AC45" t="s">
         <v>62</v>
       </c>
       <c r="AD45" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AE45" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AF45" t="s">
         <v>65</v>
@@ -8505,10 +8675,10 @@
         <v>49</v>
       </c>
       <c r="AP45" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>42</v>
       </c>
@@ -8516,28 +8686,28 @@
         <v>43</v>
       </c>
       <c r="C46" t="s">
+        <v>584</v>
+      </c>
+      <c r="D46" t="s">
         <v>585</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>586</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
+        <v>157</v>
+      </c>
+      <c r="G46" t="s">
         <v>587</v>
       </c>
-      <c r="F46" t="s">
-        <v>156</v>
-      </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
+        <v>49</v>
+      </c>
+      <c r="I46" t="s">
         <v>588</v>
       </c>
-      <c r="H46" t="s">
-        <v>49</v>
-      </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>589</v>
-      </c>
-      <c r="J46" t="s">
-        <v>590</v>
       </c>
       <c r="K46" t="s">
         <v>567</v>
@@ -8552,55 +8722,55 @@
         <v>54</v>
       </c>
       <c r="O46" t="s">
+        <v>590</v>
+      </c>
+      <c r="P46" t="s">
         <v>591</v>
       </c>
-      <c r="P46" t="s">
+      <c r="Q46" t="s">
+        <v>212</v>
+      </c>
+      <c r="R46" t="s">
         <v>592</v>
       </c>
-      <c r="Q46" t="s">
-        <v>213</v>
-      </c>
-      <c r="R46" t="s">
+      <c r="S46" t="s">
+        <v>49</v>
+      </c>
+      <c r="T46" t="s">
         <v>593</v>
       </c>
-      <c r="S46" t="s">
-        <v>49</v>
-      </c>
-      <c r="T46" t="s">
+      <c r="U46" t="s">
+        <v>57</v>
+      </c>
+      <c r="V46" t="s">
+        <v>57</v>
+      </c>
+      <c r="W46" t="s">
         <v>594</v>
       </c>
-      <c r="U46" t="s">
-        <v>57</v>
-      </c>
-      <c r="V46" t="s">
-        <v>57</v>
-      </c>
-      <c r="W46" t="s">
+      <c r="X46" t="s">
         <v>595</v>
-      </c>
-      <c r="X46" t="s">
-        <v>596</v>
       </c>
       <c r="Y46" t="s">
         <v>567</v>
       </c>
       <c r="Z46" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AA46" t="s">
         <v>61</v>
       </c>
       <c r="AB46" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AC46" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="AD46" t="s">
+        <v>326</v>
+      </c>
+      <c r="AE46" t="s">
         <v>327</v>
-      </c>
-      <c r="AE46" t="s">
-        <v>328</v>
       </c>
       <c r="AF46" t="s">
         <v>65</v>
@@ -8633,10 +8803,10 @@
         <v>49</v>
       </c>
       <c r="AP46" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -8644,28 +8814,28 @@
         <v>500</v>
       </c>
       <c r="C47" t="s">
+        <v>599</v>
+      </c>
+      <c r="D47" t="s">
         <v>600</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>601</v>
-      </c>
-      <c r="E47" t="s">
-        <v>602</v>
       </c>
       <c r="F47" t="s">
         <v>520</v>
       </c>
       <c r="G47" t="s">
+        <v>602</v>
+      </c>
+      <c r="H47" t="s">
+        <v>49</v>
+      </c>
+      <c r="I47" t="s">
         <v>603</v>
       </c>
-      <c r="H47" t="s">
-        <v>49</v>
-      </c>
-      <c r="I47" t="s">
+      <c r="J47" t="s">
         <v>604</v>
-      </c>
-      <c r="J47" t="s">
-        <v>605</v>
       </c>
       <c r="K47" t="s">
         <v>508</v>
@@ -8680,7 +8850,7 @@
         <v>54</v>
       </c>
       <c r="O47" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P47" t="s">
         <v>524</v>
@@ -8728,7 +8898,7 @@
         <v>528</v>
       </c>
       <c r="AE47" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AF47" t="s">
         <v>65</v>
@@ -8761,7 +8931,775 @@
         <v>49</v>
       </c>
       <c r="AP47" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="48" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" t="s">
         <v>606</v>
+      </c>
+      <c r="D48" t="s">
+        <v>607</v>
+      </c>
+      <c r="E48" t="s">
+        <v>608</v>
+      </c>
+      <c r="F48" t="s">
+        <v>157</v>
+      </c>
+      <c r="G48" t="s">
+        <v>609</v>
+      </c>
+      <c r="H48" t="s">
+        <v>610</v>
+      </c>
+      <c r="I48" t="s">
+        <v>610</v>
+      </c>
+      <c r="J48" t="s">
+        <v>611</v>
+      </c>
+      <c r="K48" t="s">
+        <v>612</v>
+      </c>
+      <c r="L48" t="s">
+        <v>612</v>
+      </c>
+      <c r="M48" t="s">
+        <v>53</v>
+      </c>
+      <c r="N48" t="s">
+        <v>54</v>
+      </c>
+      <c r="O48" t="s">
+        <v>337</v>
+      </c>
+      <c r="P48" t="s">
+        <v>613</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>212</v>
+      </c>
+      <c r="R48" t="s">
+        <v>562</v>
+      </c>
+      <c r="S48" t="s">
+        <v>49</v>
+      </c>
+      <c r="T48" t="s">
+        <v>563</v>
+      </c>
+      <c r="U48" t="s">
+        <v>57</v>
+      </c>
+      <c r="V48" t="s">
+        <v>57</v>
+      </c>
+      <c r="W48" t="s">
+        <v>256</v>
+      </c>
+      <c r="X48" t="s">
+        <v>614</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>612</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>615</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>616</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>364</v>
+      </c>
+      <c r="AE48" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF48" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG48" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH48" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ48" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK48" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL48" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM48" t="s">
+        <v>413</v>
+      </c>
+      <c r="AN48" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO48" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP48" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="49" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" t="s">
+        <v>43</v>
+      </c>
+      <c r="C49" t="s">
+        <v>618</v>
+      </c>
+      <c r="D49" t="s">
+        <v>619</v>
+      </c>
+      <c r="E49" t="s">
+        <v>620</v>
+      </c>
+      <c r="F49" t="s">
+        <v>370</v>
+      </c>
+      <c r="G49" t="s">
+        <v>621</v>
+      </c>
+      <c r="H49" t="s">
+        <v>49</v>
+      </c>
+      <c r="I49" t="s">
+        <v>622</v>
+      </c>
+      <c r="J49" t="s">
+        <v>623</v>
+      </c>
+      <c r="K49" t="s">
+        <v>612</v>
+      </c>
+      <c r="L49" t="s">
+        <v>624</v>
+      </c>
+      <c r="M49" t="s">
+        <v>53</v>
+      </c>
+      <c r="N49" t="s">
+        <v>54</v>
+      </c>
+      <c r="O49" t="s">
+        <v>397</v>
+      </c>
+      <c r="P49" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>626</v>
+      </c>
+      <c r="R49" t="s">
+        <v>479</v>
+      </c>
+      <c r="S49" t="s">
+        <v>49</v>
+      </c>
+      <c r="T49" t="s">
+        <v>480</v>
+      </c>
+      <c r="U49" t="s">
+        <v>57</v>
+      </c>
+      <c r="V49" t="s">
+        <v>57</v>
+      </c>
+      <c r="W49" t="s">
+        <v>351</v>
+      </c>
+      <c r="X49" t="s">
+        <v>538</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>624</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>627</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>628</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>104</v>
+      </c>
+      <c r="AE49" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF49" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG49" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH49" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI49" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ49" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK49" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL49" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM49" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN49" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO49" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP49" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="50" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" t="s">
+        <v>43</v>
+      </c>
+      <c r="C50" t="s">
+        <v>630</v>
+      </c>
+      <c r="D50" t="s">
+        <v>631</v>
+      </c>
+      <c r="E50" t="s">
+        <v>632</v>
+      </c>
+      <c r="F50" t="s">
+        <v>633</v>
+      </c>
+      <c r="G50" t="s">
+        <v>634</v>
+      </c>
+      <c r="H50" t="s">
+        <v>635</v>
+      </c>
+      <c r="I50" t="s">
+        <v>635</v>
+      </c>
+      <c r="J50" t="s">
+        <v>636</v>
+      </c>
+      <c r="K50" t="s">
+        <v>624</v>
+      </c>
+      <c r="L50" t="s">
+        <v>624</v>
+      </c>
+      <c r="M50" t="s">
+        <v>53</v>
+      </c>
+      <c r="N50" t="s">
+        <v>54</v>
+      </c>
+      <c r="O50" t="s">
+        <v>337</v>
+      </c>
+      <c r="P50" t="s">
+        <v>637</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>57</v>
+      </c>
+      <c r="R50" t="s">
+        <v>638</v>
+      </c>
+      <c r="S50" t="s">
+        <v>49</v>
+      </c>
+      <c r="T50" t="s">
+        <v>639</v>
+      </c>
+      <c r="U50" t="s">
+        <v>57</v>
+      </c>
+      <c r="V50" t="s">
+        <v>57</v>
+      </c>
+      <c r="W50" t="s">
+        <v>60</v>
+      </c>
+      <c r="X50" t="s">
+        <v>638</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>624</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>244</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>638</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>261</v>
+      </c>
+      <c r="AE50" t="s">
+        <v>262</v>
+      </c>
+      <c r="AF50" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG50" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH50" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI50" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ50" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK50" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL50" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM50" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO50" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP50" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="51" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C51" t="s">
+        <v>641</v>
+      </c>
+      <c r="D51" t="s">
+        <v>642</v>
+      </c>
+      <c r="E51" t="s">
+        <v>643</v>
+      </c>
+      <c r="F51" t="s">
+        <v>234</v>
+      </c>
+      <c r="G51" t="s">
+        <v>644</v>
+      </c>
+      <c r="H51" t="s">
+        <v>645</v>
+      </c>
+      <c r="I51" t="s">
+        <v>645</v>
+      </c>
+      <c r="J51" t="s">
+        <v>646</v>
+      </c>
+      <c r="K51" t="s">
+        <v>421</v>
+      </c>
+      <c r="L51" t="s">
+        <v>478</v>
+      </c>
+      <c r="M51" t="s">
+        <v>53</v>
+      </c>
+      <c r="N51" t="s">
+        <v>54</v>
+      </c>
+      <c r="O51" t="s">
+        <v>55</v>
+      </c>
+      <c r="P51" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>57</v>
+      </c>
+      <c r="R51" t="s">
+        <v>648</v>
+      </c>
+      <c r="S51" t="s">
+        <v>49</v>
+      </c>
+      <c r="T51" t="s">
+        <v>649</v>
+      </c>
+      <c r="U51" t="s">
+        <v>57</v>
+      </c>
+      <c r="V51" t="s">
+        <v>57</v>
+      </c>
+      <c r="W51" t="s">
+        <v>60</v>
+      </c>
+      <c r="X51" t="s">
+        <v>648</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>478</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>650</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>648</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>651</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>327</v>
+      </c>
+      <c r="AF51" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG51" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH51" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI51" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ51" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK51" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL51" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM51" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN51" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO51" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP51" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="52" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" t="s">
+        <v>653</v>
+      </c>
+      <c r="D52" t="s">
+        <v>654</v>
+      </c>
+      <c r="E52" t="s">
+        <v>655</v>
+      </c>
+      <c r="F52" t="s">
+        <v>633</v>
+      </c>
+      <c r="G52" t="s">
+        <v>656</v>
+      </c>
+      <c r="H52" t="s">
+        <v>49</v>
+      </c>
+      <c r="I52" t="s">
+        <v>657</v>
+      </c>
+      <c r="J52" t="s">
+        <v>658</v>
+      </c>
+      <c r="K52" t="s">
+        <v>659</v>
+      </c>
+      <c r="L52" t="s">
+        <v>659</v>
+      </c>
+      <c r="M52" t="s">
+        <v>53</v>
+      </c>
+      <c r="N52" t="s">
+        <v>54</v>
+      </c>
+      <c r="O52" t="s">
+        <v>337</v>
+      </c>
+      <c r="P52" t="s">
+        <v>637</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>239</v>
+      </c>
+      <c r="R52" t="s">
+        <v>660</v>
+      </c>
+      <c r="S52" t="s">
+        <v>49</v>
+      </c>
+      <c r="T52" t="s">
+        <v>661</v>
+      </c>
+      <c r="U52" t="s">
+        <v>57</v>
+      </c>
+      <c r="V52" t="s">
+        <v>57</v>
+      </c>
+      <c r="W52" t="s">
+        <v>662</v>
+      </c>
+      <c r="X52" t="s">
+        <v>663</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>659</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>664</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>307</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>665</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>261</v>
+      </c>
+      <c r="AE52" t="s">
+        <v>262</v>
+      </c>
+      <c r="AF52" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG52" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH52" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI52" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ52" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK52" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL52" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM52" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN52" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO52" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP52" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="53" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>42</v>
+      </c>
+      <c r="B53" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" t="s">
+        <v>667</v>
+      </c>
+      <c r="D53" t="s">
+        <v>668</v>
+      </c>
+      <c r="E53" t="s">
+        <v>669</v>
+      </c>
+      <c r="F53" t="s">
+        <v>157</v>
+      </c>
+      <c r="G53" t="s">
+        <v>670</v>
+      </c>
+      <c r="H53" t="s">
+        <v>49</v>
+      </c>
+      <c r="I53" t="s">
+        <v>671</v>
+      </c>
+      <c r="J53" t="s">
+        <v>672</v>
+      </c>
+      <c r="K53" t="s">
+        <v>612</v>
+      </c>
+      <c r="L53" t="s">
+        <v>673</v>
+      </c>
+      <c r="M53" t="s">
+        <v>53</v>
+      </c>
+      <c r="N53" t="s">
+        <v>54</v>
+      </c>
+      <c r="O53" t="s">
+        <v>55</v>
+      </c>
+      <c r="P53" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>674</v>
+      </c>
+      <c r="R53" t="s">
+        <v>562</v>
+      </c>
+      <c r="S53" t="s">
+        <v>49</v>
+      </c>
+      <c r="T53" t="s">
+        <v>563</v>
+      </c>
+      <c r="U53" t="s">
+        <v>57</v>
+      </c>
+      <c r="V53" t="s">
+        <v>57</v>
+      </c>
+      <c r="W53" t="s">
+        <v>146</v>
+      </c>
+      <c r="X53" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>673</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>203</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>675</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>528</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>262</v>
+      </c>
+      <c r="AF53" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG53" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH53" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI53" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ53" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK53" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL53" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM53" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN53" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO53" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP53" t="s">
+        <v>676</v>
       </c>
     </row>
   </sheetData>

--- a/datos/CV_PF.xlsx
+++ b/datos/CV_PF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://funerariaimchile-my.sharepoint.com/personal/anais_gonzalez_funerariaim_cl/Documents/Dashboard_Control Diario de Ventas/Archivos diarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF6F809D-2ED1-4770-811E-EBB475309F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FEA576D-D88B-4BEE-B0BD-C8C25729F120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2226" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2478" uniqueCount="717">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -2051,6 +2051,126 @@
   </si>
   <si>
     <t>3964</t>
+  </si>
+  <si>
+    <t>4137131-5</t>
+  </si>
+  <si>
+    <t>ARANCIBIA GAMBOA ROBERTO JAIME</t>
+  </si>
+  <si>
+    <t>10/08/1942</t>
+  </si>
+  <si>
+    <t>Pedro Aguirre Cerda</t>
+  </si>
+  <si>
+    <t>6132 - Pedro Aguirre Cerda - Santiago -CP</t>
+  </si>
+  <si>
+    <t>936398005</t>
+  </si>
+  <si>
+    <t>rarancibia430@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>23/03/2026</t>
+  </si>
+  <si>
+    <t>Yohany Margarita Gonzalez Rojas</t>
+  </si>
+  <si>
+    <t>27458</t>
+  </si>
+  <si>
+    <t>3968</t>
+  </si>
+  <si>
+    <t>6155513-7</t>
+  </si>
+  <si>
+    <t>TAMBLEY ROMERO JORGE HERNAN</t>
+  </si>
+  <si>
+    <t>03/09/1952</t>
+  </si>
+  <si>
+    <t>890 - San Miguel - Santiago -CP</t>
+  </si>
+  <si>
+    <t>979572729</t>
+  </si>
+  <si>
+    <t>jhtambleyr@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>360000</t>
+  </si>
+  <si>
+    <t>3976</t>
+  </si>
+  <si>
+    <t>3977</t>
+  </si>
+  <si>
+    <t>257000</t>
+  </si>
+  <si>
+    <t>2308000</t>
+  </si>
+  <si>
+    <t>64111</t>
+  </si>
+  <si>
+    <t>3978</t>
+  </si>
+  <si>
+    <t>8561974-8</t>
+  </si>
+  <si>
+    <t>JIMENEZ GIULIUCCI LEONARDO DE JESUS</t>
+  </si>
+  <si>
+    <t>15/10/1960</t>
+  </si>
+  <si>
+    <t>9471 - La Florida - Santiago -CP</t>
+  </si>
+  <si>
+    <t>974468599</t>
+  </si>
+  <si>
+    <t>leo.jigi@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>1450000</t>
+  </si>
+  <si>
+    <t>1218487</t>
+  </si>
+  <si>
+    <t>3981</t>
+  </si>
+  <si>
+    <t>7545444-9</t>
+  </si>
+  <si>
+    <t>CONTRERAS GONZALEZ MARÍA ANGELICA</t>
+  </si>
+  <si>
+    <t>06/02/1957</t>
+  </si>
+  <si>
+    <t>989100567</t>
+  </si>
+  <si>
+    <t>macggo@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>3994</t>
   </si>
 </sst>
 </file>
@@ -2911,11 +3031,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AP53"/>
+  <dimension ref="A1:AP59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="41" width="8" customWidth="1"/>
-    <col min="42" max="42" width="12" customWidth="1"/>
+    <col min="1" max="42" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.3">
@@ -9276,7 +9395,7 @@
         <v>638</v>
       </c>
       <c r="AC50" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="AD50" t="s">
         <v>261</v>
@@ -9404,7 +9523,7 @@
         <v>648</v>
       </c>
       <c r="AC51" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="AD51" t="s">
         <v>651</v>
@@ -9700,6 +9819,774 @@
       </c>
       <c r="AP53" t="s">
         <v>676</v>
+      </c>
+    </row>
+    <row r="54" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" t="s">
+        <v>43</v>
+      </c>
+      <c r="C54" t="s">
+        <v>677</v>
+      </c>
+      <c r="D54" t="s">
+        <v>678</v>
+      </c>
+      <c r="E54" t="s">
+        <v>679</v>
+      </c>
+      <c r="F54" t="s">
+        <v>680</v>
+      </c>
+      <c r="G54" t="s">
+        <v>681</v>
+      </c>
+      <c r="H54" t="s">
+        <v>49</v>
+      </c>
+      <c r="I54" t="s">
+        <v>682</v>
+      </c>
+      <c r="J54" t="s">
+        <v>683</v>
+      </c>
+      <c r="K54" t="s">
+        <v>659</v>
+      </c>
+      <c r="L54" t="s">
+        <v>684</v>
+      </c>
+      <c r="M54" t="s">
+        <v>53</v>
+      </c>
+      <c r="N54" t="s">
+        <v>54</v>
+      </c>
+      <c r="O54" t="s">
+        <v>397</v>
+      </c>
+      <c r="P54" t="s">
+        <v>685</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>626</v>
+      </c>
+      <c r="R54" t="s">
+        <v>482</v>
+      </c>
+      <c r="S54" t="s">
+        <v>49</v>
+      </c>
+      <c r="T54" t="s">
+        <v>511</v>
+      </c>
+      <c r="U54" t="s">
+        <v>57</v>
+      </c>
+      <c r="V54" t="s">
+        <v>57</v>
+      </c>
+      <c r="W54" t="s">
+        <v>164</v>
+      </c>
+      <c r="X54" t="s">
+        <v>538</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>684</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>349</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>686</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>104</v>
+      </c>
+      <c r="AE54" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF54" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG54" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH54" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI54" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ54" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK54" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL54" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM54" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN54" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO54" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP54" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="55" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55" t="s">
+        <v>688</v>
+      </c>
+      <c r="D55" t="s">
+        <v>689</v>
+      </c>
+      <c r="E55" t="s">
+        <v>690</v>
+      </c>
+      <c r="F55" t="s">
+        <v>633</v>
+      </c>
+      <c r="G55" t="s">
+        <v>691</v>
+      </c>
+      <c r="H55" t="s">
+        <v>692</v>
+      </c>
+      <c r="I55" t="s">
+        <v>692</v>
+      </c>
+      <c r="J55" t="s">
+        <v>693</v>
+      </c>
+      <c r="K55" t="s">
+        <v>684</v>
+      </c>
+      <c r="L55" t="s">
+        <v>684</v>
+      </c>
+      <c r="M55" t="s">
+        <v>53</v>
+      </c>
+      <c r="N55" t="s">
+        <v>54</v>
+      </c>
+      <c r="O55" t="s">
+        <v>55</v>
+      </c>
+      <c r="P55" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>179</v>
+      </c>
+      <c r="R55" t="s">
+        <v>479</v>
+      </c>
+      <c r="S55" t="s">
+        <v>49</v>
+      </c>
+      <c r="T55" t="s">
+        <v>480</v>
+      </c>
+      <c r="U55" t="s">
+        <v>57</v>
+      </c>
+      <c r="V55" t="s">
+        <v>57</v>
+      </c>
+      <c r="W55" t="s">
+        <v>164</v>
+      </c>
+      <c r="X55" t="s">
+        <v>481</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>684</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>482</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>694</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>104</v>
+      </c>
+      <c r="AE55" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF55" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG55" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH55" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI55" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ55" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK55" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL55" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM55" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN55" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO55" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP55" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="56" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" t="s">
+        <v>43</v>
+      </c>
+      <c r="C56" t="s">
+        <v>688</v>
+      </c>
+      <c r="D56" t="s">
+        <v>689</v>
+      </c>
+      <c r="E56" t="s">
+        <v>690</v>
+      </c>
+      <c r="F56" t="s">
+        <v>633</v>
+      </c>
+      <c r="G56" t="s">
+        <v>691</v>
+      </c>
+      <c r="H56" t="s">
+        <v>692</v>
+      </c>
+      <c r="I56" t="s">
+        <v>692</v>
+      </c>
+      <c r="J56" t="s">
+        <v>693</v>
+      </c>
+      <c r="K56" t="s">
+        <v>684</v>
+      </c>
+      <c r="L56" t="s">
+        <v>684</v>
+      </c>
+      <c r="M56" t="s">
+        <v>53</v>
+      </c>
+      <c r="N56" t="s">
+        <v>54</v>
+      </c>
+      <c r="O56" t="s">
+        <v>55</v>
+      </c>
+      <c r="P56" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>179</v>
+      </c>
+      <c r="R56" t="s">
+        <v>479</v>
+      </c>
+      <c r="S56" t="s">
+        <v>49</v>
+      </c>
+      <c r="T56" t="s">
+        <v>480</v>
+      </c>
+      <c r="U56" t="s">
+        <v>57</v>
+      </c>
+      <c r="V56" t="s">
+        <v>57</v>
+      </c>
+      <c r="W56" t="s">
+        <v>164</v>
+      </c>
+      <c r="X56" t="s">
+        <v>481</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>684</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>482</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>694</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>104</v>
+      </c>
+      <c r="AE56" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF56" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG56" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH56" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI56" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ56" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK56" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL56" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM56" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN56" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO56" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP56" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="57" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" t="s">
+        <v>43</v>
+      </c>
+      <c r="C57" t="s">
+        <v>329</v>
+      </c>
+      <c r="D57" t="s">
+        <v>330</v>
+      </c>
+      <c r="E57" t="s">
+        <v>331</v>
+      </c>
+      <c r="F57" t="s">
+        <v>332</v>
+      </c>
+      <c r="G57" t="s">
+        <v>333</v>
+      </c>
+      <c r="H57" t="s">
+        <v>49</v>
+      </c>
+      <c r="I57" t="s">
+        <v>334</v>
+      </c>
+      <c r="J57" t="s">
+        <v>335</v>
+      </c>
+      <c r="K57" t="s">
+        <v>226</v>
+      </c>
+      <c r="L57" t="s">
+        <v>684</v>
+      </c>
+      <c r="M57" t="s">
+        <v>53</v>
+      </c>
+      <c r="N57" t="s">
+        <v>54</v>
+      </c>
+      <c r="O57" t="s">
+        <v>337</v>
+      </c>
+      <c r="P57" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>212</v>
+      </c>
+      <c r="R57" t="s">
+        <v>240</v>
+      </c>
+      <c r="S57" t="s">
+        <v>49</v>
+      </c>
+      <c r="T57" t="s">
+        <v>241</v>
+      </c>
+      <c r="U57" t="s">
+        <v>57</v>
+      </c>
+      <c r="V57" t="s">
+        <v>57</v>
+      </c>
+      <c r="W57" t="s">
+        <v>164</v>
+      </c>
+      <c r="X57" t="s">
+        <v>697</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>684</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>698</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>259</v>
+      </c>
+      <c r="AB57" t="s">
+        <v>699</v>
+      </c>
+      <c r="AC57" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD57" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE57" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF57" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG57" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH57" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI57" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ57" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK57" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL57" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM57" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN57" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO57" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP57" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="58" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58" t="s">
+        <v>701</v>
+      </c>
+      <c r="D58" t="s">
+        <v>702</v>
+      </c>
+      <c r="E58" t="s">
+        <v>703</v>
+      </c>
+      <c r="F58" t="s">
+        <v>173</v>
+      </c>
+      <c r="G58" t="s">
+        <v>704</v>
+      </c>
+      <c r="H58" t="s">
+        <v>705</v>
+      </c>
+      <c r="I58" t="s">
+        <v>705</v>
+      </c>
+      <c r="J58" t="s">
+        <v>706</v>
+      </c>
+      <c r="K58" t="s">
+        <v>684</v>
+      </c>
+      <c r="L58" t="s">
+        <v>684</v>
+      </c>
+      <c r="M58" t="s">
+        <v>53</v>
+      </c>
+      <c r="N58" t="s">
+        <v>54</v>
+      </c>
+      <c r="O58" t="s">
+        <v>55</v>
+      </c>
+      <c r="P58" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>57</v>
+      </c>
+      <c r="R58" t="s">
+        <v>707</v>
+      </c>
+      <c r="S58" t="s">
+        <v>49</v>
+      </c>
+      <c r="T58" t="s">
+        <v>708</v>
+      </c>
+      <c r="U58" t="s">
+        <v>57</v>
+      </c>
+      <c r="V58" t="s">
+        <v>57</v>
+      </c>
+      <c r="W58" t="s">
+        <v>60</v>
+      </c>
+      <c r="X58" t="s">
+        <v>707</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>684</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>381</v>
+      </c>
+      <c r="AB58" t="s">
+        <v>707</v>
+      </c>
+      <c r="AC58" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD58" t="s">
+        <v>229</v>
+      </c>
+      <c r="AE58" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF58" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG58" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH58" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI58" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ58" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK58" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL58" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM58" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN58" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO58" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP58" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="59" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" t="s">
+        <v>43</v>
+      </c>
+      <c r="C59" t="s">
+        <v>710</v>
+      </c>
+      <c r="D59" t="s">
+        <v>711</v>
+      </c>
+      <c r="E59" t="s">
+        <v>712</v>
+      </c>
+      <c r="F59" t="s">
+        <v>173</v>
+      </c>
+      <c r="G59" t="s">
+        <v>704</v>
+      </c>
+      <c r="H59" t="s">
+        <v>49</v>
+      </c>
+      <c r="I59" t="s">
+        <v>713</v>
+      </c>
+      <c r="J59" t="s">
+        <v>714</v>
+      </c>
+      <c r="K59" t="s">
+        <v>684</v>
+      </c>
+      <c r="L59" t="s">
+        <v>715</v>
+      </c>
+      <c r="M59" t="s">
+        <v>53</v>
+      </c>
+      <c r="N59" t="s">
+        <v>54</v>
+      </c>
+      <c r="O59" t="s">
+        <v>55</v>
+      </c>
+      <c r="P59" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>57</v>
+      </c>
+      <c r="R59" t="s">
+        <v>707</v>
+      </c>
+      <c r="S59" t="s">
+        <v>49</v>
+      </c>
+      <c r="T59" t="s">
+        <v>708</v>
+      </c>
+      <c r="U59" t="s">
+        <v>57</v>
+      </c>
+      <c r="V59" t="s">
+        <v>57</v>
+      </c>
+      <c r="W59" t="s">
+        <v>60</v>
+      </c>
+      <c r="X59" t="s">
+        <v>707</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>715</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>239</v>
+      </c>
+      <c r="AB59" t="s">
+        <v>707</v>
+      </c>
+      <c r="AC59" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD59" t="s">
+        <v>229</v>
+      </c>
+      <c r="AE59" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF59" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG59" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH59" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI59" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ59" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK59" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL59" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM59" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN59" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO59" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP59" t="s">
+        <v>716</v>
       </c>
     </row>
   </sheetData>

--- a/datos/CV_PF.xlsx
+++ b/datos/CV_PF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://funerariaimchile-my.sharepoint.com/personal/anais_gonzalez_funerariaim_cl/Documents/Dashboard_Control Diario de Ventas/Archivos diarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FEA576D-D88B-4BEE-B0BD-C8C25729F120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{209904C7-2047-4A83-A536-14BE0857E281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2478" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2730" uniqueCount="776">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -703,12 +703,18 @@
     <t>06/03/2026</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>1320000</t>
   </si>
   <si>
     <t>1109244</t>
   </si>
   <si>
+    <t>100000</t>
+  </si>
+  <si>
     <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO PERSONAL</t>
   </si>
   <si>
@@ -1294,9 +1300,6 @@
     <t>2226891</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>40000</t>
   </si>
   <si>
@@ -2152,6 +2155,111 @@
     <t>3981</t>
   </si>
   <si>
+    <t>8542318-5</t>
+  </si>
+  <si>
+    <t>ALFARO VALENZUELA GUILLERMO ALBERTO</t>
+  </si>
+  <si>
+    <t>25/06/1966</t>
+  </si>
+  <si>
+    <t>2829 - Maipú - Santiago -CP</t>
+  </si>
+  <si>
+    <t>981574866</t>
+  </si>
+  <si>
+    <t>asesoresayl@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>35333</t>
+  </si>
+  <si>
+    <t>3983</t>
+  </si>
+  <si>
+    <t>26667</t>
+  </si>
+  <si>
+    <t>3984</t>
+  </si>
+  <si>
+    <t>9128819-2</t>
+  </si>
+  <si>
+    <t>REYES AVILES ANDREA MARGARITA</t>
+  </si>
+  <si>
+    <t>15/09/1965</t>
+  </si>
+  <si>
+    <t>240 - Quilicura - Santiago -CP</t>
+  </si>
+  <si>
+    <t>983363102</t>
+  </si>
+  <si>
+    <t>reyesavilesandrea@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>1650000</t>
+  </si>
+  <si>
+    <t>1386555</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>650000</t>
+  </si>
+  <si>
+    <t>27083</t>
+  </si>
+  <si>
+    <t>3991</t>
+  </si>
+  <si>
+    <t>11399404-5</t>
+  </si>
+  <si>
+    <t>GUERRA LEIVA ANA EDELMIRA</t>
+  </si>
+  <si>
+    <t>24/09/1968</t>
+  </si>
+  <si>
+    <t>456 - Quilicura - Santiago -CP</t>
+  </si>
+  <si>
+    <t>942854716</t>
+  </si>
+  <si>
+    <t>edelmiraguerraleiv@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>Nayaret tatiana puga marchant</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>1656000</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>28068</t>
+  </si>
+  <si>
+    <t>3993</t>
+  </si>
+  <si>
     <t>7545444-9</t>
   </si>
   <si>
@@ -2167,10 +2275,79 @@
     <t>macggo@gmail.com; ; ; ;</t>
   </si>
   <si>
-    <t>24/03/2026</t>
-  </si>
-  <si>
     <t>3994</t>
+  </si>
+  <si>
+    <t>19936540-1</t>
+  </si>
+  <si>
+    <t>ARZOLA GUTIERREZ MARÍA JOSE</t>
+  </si>
+  <si>
+    <t>27/09/1997</t>
+  </si>
+  <si>
+    <t>4985 - Macul - Santiago -CP</t>
+  </si>
+  <si>
+    <t>988044270</t>
+  </si>
+  <si>
+    <t>kote27.arzola@hotmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>María Isabel Gutiérrez</t>
+  </si>
+  <si>
+    <t>1430000</t>
+  </si>
+  <si>
+    <t>1201681</t>
+  </si>
+  <si>
+    <t>143000</t>
+  </si>
+  <si>
+    <t>1287000</t>
+  </si>
+  <si>
+    <t>35750</t>
+  </si>
+  <si>
+    <t>3998</t>
+  </si>
+  <si>
+    <t>16625980-0</t>
+  </si>
+  <si>
+    <t>ROCHAT DIAZ DENISSE MABEL</t>
+  </si>
+  <si>
+    <t>25/09/1987</t>
+  </si>
+  <si>
+    <t>Padre Hurtado</t>
+  </si>
+  <si>
+    <t>582 - Padre Hurtado - Talagante -CP</t>
+  </si>
+  <si>
+    <t>977289600</t>
+  </si>
+  <si>
+    <t>denisita198050@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>221000</t>
+  </si>
+  <si>
+    <t>1989000</t>
+  </si>
+  <si>
+    <t>41438</t>
+  </si>
+  <si>
+    <t>3999</t>
   </si>
 </sst>
 </file>
@@ -3031,7 +3208,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AP59"/>
+  <dimension ref="A1:AP65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="42" width="8" customWidth="1"/>
@@ -4751,16 +4928,16 @@
         <v>94</v>
       </c>
       <c r="Q14" t="s">
-        <v>57</v>
+        <v>227</v>
       </c>
       <c r="R14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="S14" t="s">
         <v>49</v>
       </c>
       <c r="T14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="U14" t="s">
         <v>57</v>
@@ -4772,25 +4949,25 @@
         <v>60</v>
       </c>
       <c r="X14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y14" t="s">
         <v>226</v>
       </c>
       <c r="Z14" t="s">
-        <v>49</v>
+        <v>230</v>
       </c>
       <c r="AA14" t="s">
         <v>203</v>
       </c>
       <c r="AB14" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AC14" t="s">
         <v>62</v>
       </c>
       <c r="AD14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AE14" t="s">
         <v>112</v>
@@ -4826,7 +5003,7 @@
         <v>49</v>
       </c>
       <c r="AP14" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.3">
@@ -4837,28 +5014,28 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D15" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E15" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F15" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G15" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H15" t="s">
         <v>49</v>
       </c>
       <c r="I15" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J15" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K15" t="s">
         <v>226</v>
@@ -4876,19 +5053,19 @@
         <v>140</v>
       </c>
       <c r="P15" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="R15" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="S15" t="s">
         <v>49</v>
       </c>
       <c r="T15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="U15" t="s">
         <v>57</v>
@@ -4900,19 +5077,19 @@
         <v>164</v>
       </c>
       <c r="X15" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Y15" t="s">
         <v>226</v>
       </c>
       <c r="Z15" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AA15" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AB15" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AC15" t="s">
         <v>62</v>
@@ -4954,7 +5131,7 @@
         <v>49</v>
       </c>
       <c r="AP15" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.3">
@@ -4965,28 +5142,28 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D16" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E16" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H16" t="s">
         <v>49</v>
       </c>
       <c r="I16" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K16" t="s">
         <v>177</v>
@@ -5010,13 +5187,13 @@
         <v>76</v>
       </c>
       <c r="R16" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="S16" t="s">
         <v>49</v>
       </c>
       <c r="T16" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="U16" t="s">
         <v>57</v>
@@ -5025,31 +5202,31 @@
         <v>57</v>
       </c>
       <c r="W16" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="X16" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y16" t="s">
         <v>226</v>
       </c>
       <c r="Z16" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AA16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AB16" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AC16" t="s">
         <v>62</v>
       </c>
       <c r="AD16" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AE16" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AF16" t="s">
         <v>65</v>
@@ -5082,7 +5259,7 @@
         <v>49</v>
       </c>
       <c r="AP16" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.3">
@@ -5093,28 +5270,28 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E17" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F17" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G17" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H17" t="s">
         <v>49</v>
       </c>
       <c r="I17" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J17" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K17" t="s">
         <v>226</v>
@@ -5138,13 +5315,13 @@
         <v>143</v>
       </c>
       <c r="R17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="S17" t="s">
         <v>49</v>
       </c>
       <c r="T17" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="U17" t="s">
         <v>57</v>
@@ -5153,19 +5330,19 @@
         <v>57</v>
       </c>
       <c r="W17" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="X17" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Y17" t="s">
         <v>226</v>
       </c>
       <c r="Z17" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AA17" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AB17" t="s">
         <v>201</v>
@@ -5210,7 +5387,7 @@
         <v>49</v>
       </c>
       <c r="AP17" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.3">
@@ -5221,28 +5398,28 @@
         <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E18" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F18" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G18" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K18" t="s">
         <v>226</v>
@@ -5266,13 +5443,13 @@
         <v>143</v>
       </c>
       <c r="R18" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="S18" t="s">
         <v>49</v>
       </c>
       <c r="T18" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="U18" t="s">
         <v>57</v>
@@ -5284,7 +5461,7 @@
         <v>164</v>
       </c>
       <c r="X18" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Y18" t="s">
         <v>226</v>
@@ -5293,19 +5470,19 @@
         <v>198</v>
       </c>
       <c r="AA18" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AB18" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AC18" t="s">
         <v>62</v>
       </c>
       <c r="AD18" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AE18" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AF18" t="s">
         <v>65</v>
@@ -5338,7 +5515,7 @@
         <v>49</v>
       </c>
       <c r="AP18" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:42" x14ac:dyDescent="0.3">
@@ -5349,28 +5526,28 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E19" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F19" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J19" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K19" t="s">
         <v>226</v>
@@ -5394,13 +5571,13 @@
         <v>197</v>
       </c>
       <c r="R19" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="S19" t="s">
         <v>49</v>
       </c>
       <c r="T19" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="U19" t="s">
         <v>57</v>
@@ -5412,28 +5589,28 @@
         <v>200</v>
       </c>
       <c r="X19" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Y19" t="s">
         <v>226</v>
       </c>
       <c r="Z19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AA19" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AB19" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AC19" t="s">
         <v>62</v>
       </c>
       <c r="AD19" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AE19" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AF19" t="s">
         <v>65</v>
@@ -5466,7 +5643,7 @@
         <v>49</v>
       </c>
       <c r="AP19" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:42" x14ac:dyDescent="0.3">
@@ -5477,34 +5654,34 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D20" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F20" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G20" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H20" t="s">
         <v>49</v>
       </c>
       <c r="I20" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J20" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K20" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L20" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M20" t="s">
         <v>53</v>
@@ -5528,7 +5705,7 @@
         <v>49</v>
       </c>
       <c r="T20" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="U20" t="s">
         <v>57</v>
@@ -5540,28 +5717,28 @@
         <v>200</v>
       </c>
       <c r="X20" t="s">
+        <v>307</v>
+      </c>
+      <c r="Y20" t="s">
         <v>305</v>
       </c>
-      <c r="Y20" t="s">
-        <v>303</v>
-      </c>
       <c r="Z20" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AA20" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AB20" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AC20" t="s">
         <v>62</v>
       </c>
       <c r="AD20" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AE20" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AF20" t="s">
         <v>65</v>
@@ -5594,7 +5771,7 @@
         <v>49</v>
       </c>
       <c r="AP20" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="1:42" x14ac:dyDescent="0.3">
@@ -5605,34 +5782,34 @@
         <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D21" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E21" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F21" t="s">
         <v>89</v>
       </c>
       <c r="G21" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H21" t="s">
         <v>49</v>
       </c>
       <c r="I21" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J21" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K21" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L21" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M21" t="s">
         <v>53</v>
@@ -5644,19 +5821,19 @@
         <v>55</v>
       </c>
       <c r="P21" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="R21" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="S21" t="s">
         <v>49</v>
       </c>
       <c r="T21" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="U21" t="s">
         <v>57</v>
@@ -5665,31 +5842,31 @@
         <v>57</v>
       </c>
       <c r="W21" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="X21" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y21" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Z21" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AA21" t="s">
         <v>179</v>
       </c>
       <c r="AB21" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AC21" t="s">
         <v>62</v>
       </c>
       <c r="AD21" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AE21" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AF21" t="s">
         <v>65</v>
@@ -5722,7 +5899,7 @@
         <v>49</v>
       </c>
       <c r="AP21" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.3">
@@ -5733,34 +5910,34 @@
         <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D22" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E22" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F22" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G22" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H22" t="s">
         <v>49</v>
       </c>
       <c r="I22" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J22" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K22" t="s">
         <v>226</v>
       </c>
       <c r="L22" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M22" t="s">
         <v>53</v>
@@ -5769,22 +5946,22 @@
         <v>54</v>
       </c>
       <c r="O22" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P22" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q22" t="s">
         <v>57</v>
       </c>
       <c r="R22" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S22" t="s">
         <v>49</v>
       </c>
       <c r="T22" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="U22" t="s">
         <v>57</v>
@@ -5796,19 +5973,19 @@
         <v>60</v>
       </c>
       <c r="X22" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Y22" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Z22" t="s">
         <v>49</v>
       </c>
       <c r="AA22" t="s">
+        <v>343</v>
+      </c>
+      <c r="AB22" t="s">
         <v>341</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>339</v>
       </c>
       <c r="AC22" t="s">
         <v>62</v>
@@ -5850,7 +6027,7 @@
         <v>49</v>
       </c>
       <c r="AP22" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="23" spans="1:42" x14ac:dyDescent="0.3">
@@ -5861,34 +6038,34 @@
         <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D23" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E23" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F23" t="s">
         <v>89</v>
       </c>
       <c r="G23" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H23" t="s">
         <v>49</v>
       </c>
       <c r="I23" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J23" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K23" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L23" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M23" t="s">
         <v>53</v>
@@ -5900,19 +6077,19 @@
         <v>55</v>
       </c>
       <c r="P23" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q23" t="s">
         <v>76</v>
       </c>
       <c r="R23" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="S23" t="s">
         <v>49</v>
       </c>
       <c r="T23" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="U23" t="s">
         <v>57</v>
@@ -5921,22 +6098,22 @@
         <v>57</v>
       </c>
       <c r="W23" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X23" t="s">
         <v>165</v>
       </c>
       <c r="Y23" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Z23" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AA23" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AB23" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AC23" t="s">
         <v>62</v>
@@ -5978,7 +6155,7 @@
         <v>49</v>
       </c>
       <c r="AP23" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="24" spans="1:42" x14ac:dyDescent="0.3">
@@ -5989,34 +6166,34 @@
         <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D24" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E24" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F24" t="s">
         <v>89</v>
       </c>
       <c r="G24" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="H24" t="s">
         <v>49</v>
       </c>
       <c r="I24" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J24" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K24" t="s">
         <v>226</v>
       </c>
       <c r="L24" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M24" t="s">
         <v>53</v>
@@ -6034,13 +6211,13 @@
         <v>57</v>
       </c>
       <c r="R24" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="S24" t="s">
         <v>49</v>
       </c>
       <c r="T24" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U24" t="s">
         <v>57</v>
@@ -6052,25 +6229,25 @@
         <v>60</v>
       </c>
       <c r="X24" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Y24" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Z24" t="s">
         <v>49</v>
       </c>
       <c r="AA24" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AB24" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AC24" t="s">
         <v>62</v>
       </c>
       <c r="AD24" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AE24" t="s">
         <v>64</v>
@@ -6106,7 +6283,7 @@
         <v>49</v>
       </c>
       <c r="AP24" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" spans="1:42" x14ac:dyDescent="0.3">
@@ -6117,34 +6294,34 @@
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D25" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E25" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F25" t="s">
         <v>89</v>
       </c>
       <c r="G25" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="H25" t="s">
         <v>49</v>
       </c>
       <c r="I25" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J25" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K25" t="s">
         <v>226</v>
       </c>
       <c r="L25" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M25" t="s">
         <v>53</v>
@@ -6162,13 +6339,13 @@
         <v>57</v>
       </c>
       <c r="R25" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="S25" t="s">
         <v>49</v>
       </c>
       <c r="T25" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U25" t="s">
         <v>57</v>
@@ -6180,25 +6357,25 @@
         <v>60</v>
       </c>
       <c r="X25" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Y25" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Z25" t="s">
         <v>49</v>
       </c>
       <c r="AA25" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AB25" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AC25" t="s">
         <v>62</v>
       </c>
       <c r="AD25" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AE25" t="s">
         <v>64</v>
@@ -6234,7 +6411,7 @@
         <v>49</v>
       </c>
       <c r="AP25" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="26" spans="1:42" x14ac:dyDescent="0.3">
@@ -6245,34 +6422,34 @@
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D26" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E26" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F26" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G26" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H26" t="s">
         <v>49</v>
       </c>
       <c r="I26" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J26" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K26" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L26" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M26" t="s">
         <v>53</v>
@@ -6284,19 +6461,19 @@
         <v>55</v>
       </c>
       <c r="P26" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q26" t="s">
         <v>76</v>
       </c>
       <c r="R26" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="S26" t="s">
         <v>49</v>
       </c>
       <c r="T26" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="U26" t="s">
         <v>57</v>
@@ -6308,16 +6485,16 @@
         <v>79</v>
       </c>
       <c r="X26" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Y26" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Z26" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AA26" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AB26" t="s">
         <v>201</v>
@@ -6326,7 +6503,7 @@
         <v>62</v>
       </c>
       <c r="AD26" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AE26" t="s">
         <v>84</v>
@@ -6362,7 +6539,7 @@
         <v>49</v>
       </c>
       <c r="AP26" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="27" spans="1:42" x14ac:dyDescent="0.3">
@@ -6373,34 +6550,34 @@
         <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D27" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E27" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F27" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G27" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H27" t="s">
         <v>49</v>
       </c>
       <c r="I27" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J27" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K27" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L27" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M27" t="s">
         <v>53</v>
@@ -6412,19 +6589,19 @@
         <v>55</v>
       </c>
       <c r="P27" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q27" t="s">
         <v>76</v>
       </c>
       <c r="R27" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="S27" t="s">
         <v>49</v>
       </c>
       <c r="T27" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="U27" t="s">
         <v>57</v>
@@ -6436,16 +6613,16 @@
         <v>79</v>
       </c>
       <c r="X27" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Y27" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Z27" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AA27" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AB27" t="s">
         <v>201</v>
@@ -6454,7 +6631,7 @@
         <v>62</v>
       </c>
       <c r="AD27" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AE27" t="s">
         <v>84</v>
@@ -6490,7 +6667,7 @@
         <v>49</v>
       </c>
       <c r="AP27" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="28" spans="1:42" x14ac:dyDescent="0.3">
@@ -6501,34 +6678,34 @@
         <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D28" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E28" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F28" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G28" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H28" t="s">
         <v>49</v>
       </c>
       <c r="I28" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J28" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L28" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M28" t="s">
         <v>53</v>
@@ -6537,10 +6714,10 @@
         <v>54</v>
       </c>
       <c r="O28" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P28" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q28" t="s">
         <v>143</v>
@@ -6567,16 +6744,16 @@
         <v>80</v>
       </c>
       <c r="Y28" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Z28" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AA28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AB28" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AC28" t="s">
         <v>62</v>
@@ -6618,7 +6795,7 @@
         <v>49</v>
       </c>
       <c r="AP28" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="29" spans="1:42" x14ac:dyDescent="0.3">
@@ -6629,28 +6806,28 @@
         <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D29" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E29" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F29" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G29" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="H29" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="I29" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J29" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K29" t="s">
         <v>226</v>
@@ -6668,19 +6845,19 @@
         <v>140</v>
       </c>
       <c r="P29" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q29" t="s">
         <v>95</v>
       </c>
       <c r="R29" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="S29" t="s">
         <v>49</v>
       </c>
       <c r="T29" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="U29" t="s">
         <v>57</v>
@@ -6692,19 +6869,19 @@
         <v>164</v>
       </c>
       <c r="X29" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Y29" t="s">
         <v>226</v>
       </c>
       <c r="Z29" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AA29" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AB29" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AC29" t="s">
         <v>62</v>
@@ -6737,7 +6914,7 @@
         <v>49</v>
       </c>
       <c r="AM29" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN29" t="s">
         <v>49</v>
@@ -6746,7 +6923,7 @@
         <v>49</v>
       </c>
       <c r="AP29" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="30" spans="1:42" x14ac:dyDescent="0.3">
@@ -6757,34 +6934,34 @@
         <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D30" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E30" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F30" t="s">
         <v>89</v>
       </c>
       <c r="G30" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H30" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="I30" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J30" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="K30" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L30" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M30" t="s">
         <v>53</v>
@@ -6802,13 +6979,13 @@
         <v>76</v>
       </c>
       <c r="R30" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="S30" t="s">
         <v>49</v>
       </c>
       <c r="T30" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="U30" t="s">
         <v>57</v>
@@ -6817,22 +6994,22 @@
         <v>57</v>
       </c>
       <c r="W30" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X30" t="s">
         <v>215</v>
       </c>
       <c r="Y30" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Z30" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AA30" t="s">
-        <v>424</v>
+        <v>227</v>
       </c>
       <c r="AB30" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AC30" t="s">
         <v>62</v>
@@ -6874,7 +7051,7 @@
         <v>49</v>
       </c>
       <c r="AP30" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" spans="1:42" x14ac:dyDescent="0.3">
@@ -6885,34 +7062,34 @@
         <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D31" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E31" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F31" t="s">
         <v>89</v>
       </c>
       <c r="G31" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H31" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I31" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J31" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="K31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M31" t="s">
         <v>53</v>
@@ -6930,13 +7107,13 @@
         <v>76</v>
       </c>
       <c r="R31" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="S31" t="s">
         <v>49</v>
       </c>
       <c r="T31" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="U31" t="s">
         <v>57</v>
@@ -6945,22 +7122,22 @@
         <v>57</v>
       </c>
       <c r="W31" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X31" t="s">
         <v>215</v>
       </c>
       <c r="Y31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Z31" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AA31" t="s">
-        <v>424</v>
+        <v>227</v>
       </c>
       <c r="AB31" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AC31" t="s">
         <v>62</v>
@@ -7002,7 +7179,7 @@
         <v>49</v>
       </c>
       <c r="AP31" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="32" spans="1:42" x14ac:dyDescent="0.3">
@@ -7013,34 +7190,34 @@
         <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D32" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E32" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F32" t="s">
         <v>157</v>
       </c>
       <c r="G32" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H32" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I32" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J32" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K32" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L32" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M32" t="s">
         <v>53</v>
@@ -7052,7 +7229,7 @@
         <v>140</v>
       </c>
       <c r="P32" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q32" t="s">
         <v>212</v>
@@ -7079,16 +7256,16 @@
         <v>165</v>
       </c>
       <c r="Y32" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Z32" t="s">
         <v>166</v>
       </c>
       <c r="AA32" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AB32" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AC32" t="s">
         <v>103</v>
@@ -7130,7 +7307,7 @@
         <v>49</v>
       </c>
       <c r="AP32" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="33" spans="1:42" x14ac:dyDescent="0.3">
@@ -7141,34 +7318,34 @@
         <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D33" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E33" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F33" t="s">
         <v>157</v>
       </c>
       <c r="G33" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H33" t="s">
         <v>49</v>
       </c>
       <c r="I33" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J33" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K33" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L33" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M33" t="s">
         <v>53</v>
@@ -7180,19 +7357,19 @@
         <v>140</v>
       </c>
       <c r="P33" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q33" t="s">
         <v>76</v>
       </c>
       <c r="R33" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="S33" t="s">
         <v>49</v>
       </c>
       <c r="T33" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U33" t="s">
         <v>57</v>
@@ -7204,28 +7381,28 @@
         <v>164</v>
       </c>
       <c r="X33" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Y33" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Z33" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA33" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AB33" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AC33" t="s">
         <v>103</v>
       </c>
       <c r="AD33" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AE33" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AF33" t="s">
         <v>65</v>
@@ -7258,7 +7435,7 @@
         <v>49</v>
       </c>
       <c r="AP33" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="34" spans="1:42" x14ac:dyDescent="0.3">
@@ -7269,34 +7446,34 @@
         <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D34" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E34" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F34" t="s">
         <v>157</v>
       </c>
       <c r="G34" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H34" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I34" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J34" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K34" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L34" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M34" t="s">
         <v>53</v>
@@ -7308,7 +7485,7 @@
         <v>140</v>
       </c>
       <c r="P34" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q34" t="s">
         <v>60</v>
@@ -7320,7 +7497,7 @@
         <v>49</v>
       </c>
       <c r="T34" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="U34" t="s">
         <v>57</v>
@@ -7329,28 +7506,28 @@
         <v>57</v>
       </c>
       <c r="W34" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="X34" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Y34" t="s">
         <v>49</v>
       </c>
       <c r="Z34" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AA34" t="s">
         <v>95</v>
       </c>
       <c r="AB34" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AC34" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AD34" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AE34" t="s">
         <v>112</v>
@@ -7365,7 +7542,7 @@
         <v>65</v>
       </c>
       <c r="AI34" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AJ34" t="s">
         <v>65</v>
@@ -7377,7 +7554,7 @@
         <v>49</v>
       </c>
       <c r="AM34" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN34" t="s">
         <v>49</v>
@@ -7386,7 +7563,7 @@
         <v>49</v>
       </c>
       <c r="AP34" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="35" spans="1:42" x14ac:dyDescent="0.3">
@@ -7397,34 +7574,34 @@
         <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D35" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E35" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H35" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I35" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J35" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K35" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L35" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M35" t="s">
         <v>53</v>
@@ -7436,19 +7613,19 @@
         <v>55</v>
       </c>
       <c r="P35" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q35" t="s">
         <v>212</v>
       </c>
       <c r="R35" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="S35" t="s">
         <v>49</v>
       </c>
       <c r="T35" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="U35" t="s">
         <v>57</v>
@@ -7460,22 +7637,22 @@
         <v>164</v>
       </c>
       <c r="X35" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Y35" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z35" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AA35" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AB35" t="s">
         <v>201</v>
       </c>
       <c r="AC35" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AD35" t="s">
         <v>104</v>
@@ -7493,7 +7670,7 @@
         <v>65</v>
       </c>
       <c r="AI35" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AJ35" t="s">
         <v>65</v>
@@ -7514,7 +7691,7 @@
         <v>49</v>
       </c>
       <c r="AP35" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="36" spans="1:42" x14ac:dyDescent="0.3">
@@ -7525,34 +7702,34 @@
         <v>43</v>
       </c>
       <c r="C36" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D36" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E36" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H36" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I36" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J36" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K36" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L36" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M36" t="s">
         <v>53</v>
@@ -7564,19 +7741,19 @@
         <v>55</v>
       </c>
       <c r="P36" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q36" t="s">
         <v>212</v>
       </c>
       <c r="R36" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="S36" t="s">
         <v>49</v>
       </c>
       <c r="T36" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="U36" t="s">
         <v>57</v>
@@ -7588,22 +7765,22 @@
         <v>164</v>
       </c>
       <c r="X36" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Y36" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z36" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AA36" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AB36" t="s">
         <v>201</v>
       </c>
       <c r="AC36" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AD36" t="s">
         <v>104</v>
@@ -7621,7 +7798,7 @@
         <v>65</v>
       </c>
       <c r="AI36" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AJ36" t="s">
         <v>65</v>
@@ -7642,7 +7819,7 @@
         <v>49</v>
       </c>
       <c r="AP36" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="37" spans="1:42" x14ac:dyDescent="0.3">
@@ -7653,34 +7830,34 @@
         <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D37" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E37" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F37" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G37" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H37" t="s">
         <v>49</v>
       </c>
       <c r="I37" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J37" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K37" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L37" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M37" t="s">
         <v>53</v>
@@ -7698,13 +7875,13 @@
         <v>57</v>
       </c>
       <c r="R37" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="S37" t="s">
         <v>49</v>
       </c>
       <c r="T37" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="U37" t="s">
         <v>57</v>
@@ -7716,10 +7893,10 @@
         <v>60</v>
       </c>
       <c r="X37" t="s">
+        <v>497</v>
+      </c>
+      <c r="Y37" t="s">
         <v>496</v>
-      </c>
-      <c r="Y37" t="s">
-        <v>495</v>
       </c>
       <c r="Z37" t="s">
         <v>49</v>
@@ -7728,16 +7905,16 @@
         <v>167</v>
       </c>
       <c r="AB37" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AC37" t="s">
         <v>62</v>
       </c>
       <c r="AD37" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AE37" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AF37" t="s">
         <v>65</v>
@@ -7770,7 +7947,7 @@
         <v>49</v>
       </c>
       <c r="AP37" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="38" spans="1:42" x14ac:dyDescent="0.3">
@@ -7778,37 +7955,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C38" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D38" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E38" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F38" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G38" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H38" t="s">
         <v>49</v>
       </c>
       <c r="I38" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J38" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K38" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L38" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M38" t="s">
         <v>53</v>
@@ -7817,55 +7994,55 @@
         <v>54</v>
       </c>
       <c r="O38" t="s">
+        <v>510</v>
+      </c>
+      <c r="P38" t="s">
+        <v>511</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>241</v>
+      </c>
+      <c r="R38" t="s">
+        <v>483</v>
+      </c>
+      <c r="S38" t="s">
+        <v>49</v>
+      </c>
+      <c r="T38" t="s">
+        <v>512</v>
+      </c>
+      <c r="U38" t="s">
+        <v>57</v>
+      </c>
+      <c r="V38" t="s">
+        <v>57</v>
+      </c>
+      <c r="W38" t="s">
+        <v>258</v>
+      </c>
+      <c r="X38" t="s">
+        <v>482</v>
+      </c>
+      <c r="Y38" t="s">
         <v>509</v>
       </c>
-      <c r="P38" t="s">
-        <v>510</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>239</v>
-      </c>
-      <c r="R38" t="s">
-        <v>482</v>
-      </c>
-      <c r="S38" t="s">
-        <v>49</v>
-      </c>
-      <c r="T38" t="s">
-        <v>511</v>
-      </c>
-      <c r="U38" t="s">
-        <v>57</v>
-      </c>
-      <c r="V38" t="s">
-        <v>57</v>
-      </c>
-      <c r="W38" t="s">
-        <v>256</v>
-      </c>
-      <c r="X38" t="s">
-        <v>481</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>508</v>
-      </c>
       <c r="Z38" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA38" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AB38" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AC38" t="s">
         <v>62</v>
       </c>
       <c r="AD38" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AE38" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AF38" t="s">
         <v>65</v>
@@ -7889,7 +8066,7 @@
         <v>49</v>
       </c>
       <c r="AM38" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN38" t="s">
         <v>49</v>
@@ -7898,7 +8075,7 @@
         <v>49</v>
       </c>
       <c r="AP38" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="39" spans="1:42" x14ac:dyDescent="0.3">
@@ -7906,37 +8083,37 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C39" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D39" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E39" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F39" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G39" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H39" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I39" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="J39" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K39" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L39" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M39" t="s">
         <v>53</v>
@@ -7945,22 +8122,22 @@
         <v>54</v>
       </c>
       <c r="O39" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P39" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="Q39" t="s">
         <v>57</v>
       </c>
       <c r="R39" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S39" t="s">
         <v>49</v>
       </c>
       <c r="T39" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="U39" t="s">
         <v>57</v>
@@ -7972,28 +8149,28 @@
         <v>60</v>
       </c>
       <c r="X39" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="Y39" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Z39" t="s">
         <v>49</v>
       </c>
       <c r="AA39" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AB39" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AC39" t="s">
         <v>62</v>
       </c>
       <c r="AD39" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AE39" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AF39" t="s">
         <v>65</v>
@@ -8026,7 +8203,7 @@
         <v>49</v>
       </c>
       <c r="AP39" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="40" spans="1:42" x14ac:dyDescent="0.3">
@@ -8037,34 +8214,34 @@
         <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D40" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E40" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F40" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G40" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H40" t="s">
         <v>49</v>
       </c>
       <c r="I40" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J40" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="K40" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L40" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M40" t="s">
         <v>53</v>
@@ -8073,22 +8250,22 @@
         <v>54</v>
       </c>
       <c r="O40" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P40" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="Q40" t="s">
         <v>212</v>
       </c>
       <c r="R40" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="S40" t="s">
         <v>49</v>
       </c>
       <c r="T40" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="U40" t="s">
         <v>57</v>
@@ -8100,28 +8277,28 @@
         <v>164</v>
       </c>
       <c r="X40" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Y40" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z40" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AA40" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AB40" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AC40" t="s">
         <v>62</v>
       </c>
       <c r="AD40" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AE40" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AF40" t="s">
         <v>65</v>
@@ -8154,7 +8331,7 @@
         <v>49</v>
       </c>
       <c r="AP40" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="41" spans="1:42" x14ac:dyDescent="0.3">
@@ -8165,34 +8342,34 @@
         <v>43</v>
       </c>
       <c r="C41" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D41" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E41" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F41" t="s">
         <v>89</v>
       </c>
       <c r="G41" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H41" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I41" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J41" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K41" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L41" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M41" t="s">
         <v>53</v>
@@ -8204,19 +8381,19 @@
         <v>55</v>
       </c>
       <c r="P41" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q41" t="s">
         <v>60</v>
       </c>
       <c r="R41" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="S41" t="s">
         <v>49</v>
       </c>
       <c r="T41" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="U41" t="s">
         <v>57</v>
@@ -8228,28 +8405,28 @@
         <v>146</v>
       </c>
       <c r="X41" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Y41" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z41" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AA41" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AB41" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AC41" t="s">
         <v>103</v>
       </c>
       <c r="AD41" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AE41" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AF41" t="s">
         <v>65</v>
@@ -8273,7 +8450,7 @@
         <v>49</v>
       </c>
       <c r="AM41" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN41" t="s">
         <v>49</v>
@@ -8282,7 +8459,7 @@
         <v>49</v>
       </c>
       <c r="AP41" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="42" spans="1:42" x14ac:dyDescent="0.3">
@@ -8293,34 +8470,34 @@
         <v>43</v>
       </c>
       <c r="C42" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D42" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E42" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F42" t="s">
         <v>157</v>
       </c>
       <c r="G42" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H42" t="s">
         <v>49</v>
       </c>
       <c r="I42" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="J42" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K42" t="s">
         <v>178</v>
       </c>
       <c r="L42" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M42" t="s">
         <v>53</v>
@@ -8329,22 +8506,22 @@
         <v>54</v>
       </c>
       <c r="O42" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P42" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q42" t="s">
         <v>76</v>
       </c>
       <c r="R42" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="S42" t="s">
         <v>49</v>
       </c>
       <c r="T42" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="U42" t="s">
         <v>57</v>
@@ -8353,31 +8530,31 @@
         <v>57</v>
       </c>
       <c r="W42" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="X42" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="Y42" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z42" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AA42" t="s">
         <v>179</v>
       </c>
       <c r="AB42" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AC42" t="s">
         <v>103</v>
       </c>
       <c r="AD42" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AE42" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AF42" t="s">
         <v>65</v>
@@ -8410,7 +8587,7 @@
         <v>49</v>
       </c>
       <c r="AP42" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="43" spans="1:42" x14ac:dyDescent="0.3">
@@ -8421,34 +8598,34 @@
         <v>43</v>
       </c>
       <c r="C43" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D43" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E43" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F43" t="s">
         <v>157</v>
       </c>
       <c r="G43" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H43" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I43" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J43" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="K43" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L43" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M43" t="s">
         <v>53</v>
@@ -8460,19 +8637,19 @@
         <v>140</v>
       </c>
       <c r="P43" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q43" t="s">
         <v>212</v>
       </c>
       <c r="R43" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="S43" t="s">
         <v>49</v>
       </c>
       <c r="T43" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="U43" t="s">
         <v>57</v>
@@ -8484,25 +8661,25 @@
         <v>146</v>
       </c>
       <c r="X43" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Y43" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z43" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AA43" t="s">
         <v>61</v>
       </c>
       <c r="AB43" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AC43" t="s">
         <v>103</v>
       </c>
       <c r="AD43" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AE43" t="s">
         <v>64</v>
@@ -8538,7 +8715,7 @@
         <v>49</v>
       </c>
       <c r="AP43" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="44" spans="1:42" x14ac:dyDescent="0.3">
@@ -8549,34 +8726,34 @@
         <v>43</v>
       </c>
       <c r="C44" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D44" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E44" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F44" t="s">
         <v>157</v>
       </c>
       <c r="G44" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H44" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I44" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J44" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K44" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L44" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M44" t="s">
         <v>53</v>
@@ -8588,19 +8765,19 @@
         <v>140</v>
       </c>
       <c r="P44" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q44" t="s">
         <v>57</v>
       </c>
       <c r="R44" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="S44" t="s">
         <v>49</v>
       </c>
       <c r="T44" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="U44" t="s">
         <v>57</v>
@@ -8612,25 +8789,25 @@
         <v>60</v>
       </c>
       <c r="X44" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Y44" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Z44" t="s">
         <v>49</v>
       </c>
       <c r="AA44" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AB44" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AC44" t="s">
         <v>62</v>
       </c>
       <c r="AD44" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AE44" t="s">
         <v>112</v>
@@ -8657,7 +8834,7 @@
         <v>49</v>
       </c>
       <c r="AM44" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN44" t="s">
         <v>49</v>
@@ -8666,7 +8843,7 @@
         <v>49</v>
       </c>
       <c r="AP44" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="45" spans="1:42" x14ac:dyDescent="0.3">
@@ -8677,34 +8854,34 @@
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D45" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E45" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F45" t="s">
         <v>157</v>
       </c>
       <c r="G45" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H45" t="s">
         <v>49</v>
       </c>
       <c r="I45" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="J45" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K45" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L45" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M45" t="s">
         <v>53</v>
@@ -8716,19 +8893,19 @@
         <v>140</v>
       </c>
       <c r="P45" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="Q45" t="s">
         <v>95</v>
       </c>
       <c r="R45" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="S45" t="s">
         <v>49</v>
       </c>
       <c r="T45" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="U45" t="s">
         <v>57</v>
@@ -8740,25 +8917,25 @@
         <v>164</v>
       </c>
       <c r="X45" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Y45" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Z45" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA45" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AB45" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AC45" t="s">
         <v>62</v>
       </c>
       <c r="AD45" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AE45" t="s">
         <v>112</v>
@@ -8794,7 +8971,7 @@
         <v>49</v>
       </c>
       <c r="AP45" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="46" spans="1:42" x14ac:dyDescent="0.3">
@@ -8805,34 +8982,34 @@
         <v>43</v>
       </c>
       <c r="C46" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D46" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E46" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F46" t="s">
         <v>157</v>
       </c>
       <c r="G46" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H46" t="s">
         <v>49</v>
       </c>
       <c r="I46" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J46" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="K46" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L46" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M46" t="s">
         <v>53</v>
@@ -8841,22 +9018,22 @@
         <v>54</v>
       </c>
       <c r="O46" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P46" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Q46" t="s">
         <v>212</v>
       </c>
       <c r="R46" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
       </c>
       <c r="T46" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="U46" t="s">
         <v>57</v>
@@ -8865,31 +9042,31 @@
         <v>57</v>
       </c>
       <c r="W46" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="X46" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="Y46" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="Z46" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AA46" t="s">
         <v>61</v>
       </c>
       <c r="AB46" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AC46" t="s">
         <v>103</v>
       </c>
       <c r="AD46" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AE46" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AF46" t="s">
         <v>65</v>
@@ -8913,7 +9090,7 @@
         <v>49</v>
       </c>
       <c r="AM46" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN46" t="s">
         <v>49</v>
@@ -8922,7 +9099,7 @@
         <v>49</v>
       </c>
       <c r="AP46" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="47" spans="1:42" x14ac:dyDescent="0.3">
@@ -8930,37 +9107,37 @@
         <v>42</v>
       </c>
       <c r="B47" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C47" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D47" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E47" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F47" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G47" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H47" t="s">
         <v>49</v>
       </c>
       <c r="I47" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J47" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="K47" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L47" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M47" t="s">
         <v>53</v>
@@ -8969,22 +9146,22 @@
         <v>54</v>
       </c>
       <c r="O47" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P47" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="Q47" t="s">
         <v>57</v>
       </c>
       <c r="R47" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S47" t="s">
         <v>49</v>
       </c>
       <c r="T47" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="U47" t="s">
         <v>57</v>
@@ -8996,28 +9173,28 @@
         <v>60</v>
       </c>
       <c r="X47" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="Y47" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Z47" t="s">
         <v>49</v>
       </c>
       <c r="AA47" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AB47" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AC47" t="s">
         <v>62</v>
       </c>
       <c r="AD47" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AE47" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AF47" t="s">
         <v>65</v>
@@ -9050,7 +9227,7 @@
         <v>49</v>
       </c>
       <c r="AP47" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="48" spans="1:42" x14ac:dyDescent="0.3">
@@ -9061,34 +9238,34 @@
         <v>43</v>
       </c>
       <c r="C48" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D48" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E48" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F48" t="s">
         <v>157</v>
       </c>
       <c r="G48" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H48" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="I48" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="J48" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K48" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L48" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M48" t="s">
         <v>53</v>
@@ -9097,22 +9274,22 @@
         <v>54</v>
       </c>
       <c r="O48" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P48" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="Q48" t="s">
         <v>212</v>
       </c>
       <c r="R48" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="S48" t="s">
         <v>49</v>
       </c>
       <c r="T48" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="U48" t="s">
         <v>57</v>
@@ -9121,28 +9298,28 @@
         <v>57</v>
       </c>
       <c r="W48" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="X48" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="Y48" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="Z48" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AA48" t="s">
         <v>125</v>
       </c>
       <c r="AB48" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AC48" t="s">
         <v>103</v>
       </c>
       <c r="AD48" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AE48" t="s">
         <v>64</v>
@@ -9169,7 +9346,7 @@
         <v>49</v>
       </c>
       <c r="AM48" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN48" t="s">
         <v>49</v>
@@ -9178,7 +9355,7 @@
         <v>49</v>
       </c>
       <c r="AP48" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="49" spans="1:42" x14ac:dyDescent="0.3">
@@ -9189,34 +9366,34 @@
         <v>43</v>
       </c>
       <c r="C49" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D49" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E49" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F49" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G49" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H49" t="s">
         <v>49</v>
       </c>
       <c r="I49" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J49" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="K49" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L49" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M49" t="s">
         <v>53</v>
@@ -9225,46 +9402,46 @@
         <v>54</v>
       </c>
       <c r="O49" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P49" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>627</v>
+      </c>
+      <c r="R49" t="s">
+        <v>480</v>
+      </c>
+      <c r="S49" t="s">
+        <v>49</v>
+      </c>
+      <c r="T49" t="s">
+        <v>481</v>
+      </c>
+      <c r="U49" t="s">
+        <v>57</v>
+      </c>
+      <c r="V49" t="s">
+        <v>57</v>
+      </c>
+      <c r="W49" t="s">
+        <v>353</v>
+      </c>
+      <c r="X49" t="s">
+        <v>539</v>
+      </c>
+      <c r="Y49" t="s">
         <v>625</v>
       </c>
-      <c r="Q49" t="s">
-        <v>626</v>
-      </c>
-      <c r="R49" t="s">
-        <v>479</v>
-      </c>
-      <c r="S49" t="s">
-        <v>49</v>
-      </c>
-      <c r="T49" t="s">
-        <v>480</v>
-      </c>
-      <c r="U49" t="s">
-        <v>57</v>
-      </c>
-      <c r="V49" t="s">
-        <v>57</v>
-      </c>
-      <c r="W49" t="s">
-        <v>351</v>
-      </c>
-      <c r="X49" t="s">
-        <v>538</v>
-      </c>
-      <c r="Y49" t="s">
-        <v>624</v>
-      </c>
       <c r="Z49" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AA49" t="s">
         <v>125</v>
       </c>
       <c r="AB49" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AC49" t="s">
         <v>103</v>
@@ -9306,7 +9483,7 @@
         <v>49</v>
       </c>
       <c r="AP49" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="50" spans="1:42" x14ac:dyDescent="0.3">
@@ -9317,34 +9494,34 @@
         <v>43</v>
       </c>
       <c r="C50" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D50" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E50" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F50" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G50" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H50" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="I50" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="J50" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K50" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L50" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M50" t="s">
         <v>53</v>
@@ -9353,22 +9530,22 @@
         <v>54</v>
       </c>
       <c r="O50" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P50" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="Q50" t="s">
         <v>57</v>
       </c>
       <c r="R50" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="S50" t="s">
         <v>49</v>
       </c>
       <c r="T50" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="U50" t="s">
         <v>57</v>
@@ -9380,28 +9557,28 @@
         <v>60</v>
       </c>
       <c r="X50" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="Y50" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="Z50" t="s">
         <v>49</v>
       </c>
       <c r="AA50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AB50" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AC50" t="s">
         <v>62</v>
       </c>
       <c r="AD50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AE50" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AF50" t="s">
         <v>65</v>
@@ -9434,7 +9611,7 @@
         <v>49</v>
       </c>
       <c r="AP50" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="51" spans="1:42" x14ac:dyDescent="0.3">
@@ -9445,34 +9622,34 @@
         <v>43</v>
       </c>
       <c r="C51" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D51" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E51" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F51" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G51" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H51" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="I51" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="J51" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K51" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L51" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M51" t="s">
         <v>53</v>
@@ -9484,19 +9661,19 @@
         <v>55</v>
       </c>
       <c r="P51" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="Q51" t="s">
         <v>57</v>
       </c>
       <c r="R51" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="S51" t="s">
         <v>49</v>
       </c>
       <c r="T51" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="U51" t="s">
         <v>57</v>
@@ -9508,28 +9685,28 @@
         <v>60</v>
       </c>
       <c r="X51" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Y51" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z51" t="s">
         <v>49</v>
       </c>
       <c r="AA51" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AB51" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AC51" t="s">
         <v>62</v>
       </c>
       <c r="AD51" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AE51" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AF51" t="s">
         <v>65</v>
@@ -9562,7 +9739,7 @@
         <v>49</v>
       </c>
       <c r="AP51" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="52" spans="1:42" x14ac:dyDescent="0.3">
@@ -9573,34 +9750,34 @@
         <v>43</v>
       </c>
       <c r="C52" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D52" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E52" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F52" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G52" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H52" t="s">
         <v>49</v>
       </c>
       <c r="I52" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J52" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="K52" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L52" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M52" t="s">
         <v>53</v>
@@ -9609,55 +9786,55 @@
         <v>54</v>
       </c>
       <c r="O52" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P52" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="Q52" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="R52" t="s">
+        <v>661</v>
+      </c>
+      <c r="S52" t="s">
+        <v>49</v>
+      </c>
+      <c r="T52" t="s">
+        <v>662</v>
+      </c>
+      <c r="U52" t="s">
+        <v>57</v>
+      </c>
+      <c r="V52" t="s">
+        <v>57</v>
+      </c>
+      <c r="W52" t="s">
+        <v>663</v>
+      </c>
+      <c r="X52" t="s">
+        <v>664</v>
+      </c>
+      <c r="Y52" t="s">
         <v>660</v>
       </c>
-      <c r="S52" t="s">
-        <v>49</v>
-      </c>
-      <c r="T52" t="s">
-        <v>661</v>
-      </c>
-      <c r="U52" t="s">
-        <v>57</v>
-      </c>
-      <c r="V52" t="s">
-        <v>57</v>
-      </c>
-      <c r="W52" t="s">
-        <v>662</v>
-      </c>
-      <c r="X52" t="s">
-        <v>663</v>
-      </c>
-      <c r="Y52" t="s">
-        <v>659</v>
-      </c>
       <c r="Z52" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AA52" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AB52" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AC52" t="s">
         <v>103</v>
       </c>
       <c r="AD52" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AE52" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AF52" t="s">
         <v>65</v>
@@ -9690,7 +9867,7 @@
         <v>49</v>
       </c>
       <c r="AP52" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="53" spans="1:42" x14ac:dyDescent="0.3">
@@ -9701,34 +9878,34 @@
         <v>43</v>
       </c>
       <c r="C53" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D53" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E53" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F53" t="s">
         <v>157</v>
       </c>
       <c r="G53" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H53" t="s">
         <v>49</v>
       </c>
       <c r="I53" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="J53" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K53" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L53" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M53" t="s">
         <v>53</v>
@@ -9743,16 +9920,16 @@
         <v>94</v>
       </c>
       <c r="Q53" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="R53" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="S53" t="s">
         <v>49</v>
       </c>
       <c r="T53" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="U53" t="s">
         <v>57</v>
@@ -9764,28 +9941,28 @@
         <v>146</v>
       </c>
       <c r="X53" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Y53" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="Z53" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AA53" t="s">
         <v>203</v>
       </c>
       <c r="AB53" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AC53" t="s">
         <v>103</v>
       </c>
       <c r="AD53" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AE53" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AF53" t="s">
         <v>65</v>
@@ -9818,7 +9995,7 @@
         <v>49</v>
       </c>
       <c r="AP53" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="54" spans="1:42" x14ac:dyDescent="0.3">
@@ -9829,34 +10006,34 @@
         <v>43</v>
       </c>
       <c r="C54" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D54" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E54" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F54" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="G54" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H54" t="s">
         <v>49</v>
       </c>
       <c r="I54" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="J54" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="K54" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L54" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M54" t="s">
         <v>53</v>
@@ -9865,22 +10042,22 @@
         <v>54</v>
       </c>
       <c r="O54" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P54" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="Q54" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="R54" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="S54" t="s">
         <v>49</v>
       </c>
       <c r="T54" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="U54" t="s">
         <v>57</v>
@@ -9892,19 +10069,19 @@
         <v>164</v>
       </c>
       <c r="X54" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Y54" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="Z54" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AA54" t="s">
         <v>179</v>
       </c>
       <c r="AB54" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AC54" t="s">
         <v>103</v>
@@ -9946,7 +10123,7 @@
         <v>49</v>
       </c>
       <c r="AP54" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="55" spans="1:42" x14ac:dyDescent="0.3">
@@ -9957,34 +10134,34 @@
         <v>43</v>
       </c>
       <c r="C55" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D55" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E55" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F55" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G55" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H55" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="I55" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="J55" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="K55" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="L55" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M55" t="s">
         <v>53</v>
@@ -9996,19 +10173,19 @@
         <v>55</v>
       </c>
       <c r="P55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q55" t="s">
         <v>179</v>
       </c>
       <c r="R55" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="S55" t="s">
         <v>49</v>
       </c>
       <c r="T55" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="U55" t="s">
         <v>57</v>
@@ -10020,19 +10197,19 @@
         <v>164</v>
       </c>
       <c r="X55" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Y55" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="Z55" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AA55" t="s">
         <v>179</v>
       </c>
       <c r="AB55" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AC55" t="s">
         <v>103</v>
@@ -10074,7 +10251,7 @@
         <v>49</v>
       </c>
       <c r="AP55" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="56" spans="1:42" x14ac:dyDescent="0.3">
@@ -10085,34 +10262,34 @@
         <v>43</v>
       </c>
       <c r="C56" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D56" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E56" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F56" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G56" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H56" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="I56" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="J56" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="K56" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="L56" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M56" t="s">
         <v>53</v>
@@ -10124,19 +10301,19 @@
         <v>55</v>
       </c>
       <c r="P56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q56" t="s">
         <v>179</v>
       </c>
       <c r="R56" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="S56" t="s">
         <v>49</v>
       </c>
       <c r="T56" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="U56" t="s">
         <v>57</v>
@@ -10148,19 +10325,19 @@
         <v>164</v>
       </c>
       <c r="X56" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Y56" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="Z56" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AA56" t="s">
         <v>179</v>
       </c>
       <c r="AB56" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AC56" t="s">
         <v>103</v>
@@ -10202,7 +10379,7 @@
         <v>49</v>
       </c>
       <c r="AP56" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="57" spans="1:42" x14ac:dyDescent="0.3">
@@ -10213,34 +10390,34 @@
         <v>43</v>
       </c>
       <c r="C57" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D57" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E57" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F57" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G57" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H57" t="s">
         <v>49</v>
       </c>
       <c r="I57" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J57" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K57" t="s">
         <v>226</v>
       </c>
       <c r="L57" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M57" t="s">
         <v>53</v>
@@ -10249,22 +10426,22 @@
         <v>54</v>
       </c>
       <c r="O57" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P57" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q57" t="s">
         <v>212</v>
       </c>
       <c r="R57" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="S57" t="s">
         <v>49</v>
       </c>
       <c r="T57" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="U57" t="s">
         <v>57</v>
@@ -10276,22 +10453,22 @@
         <v>164</v>
       </c>
       <c r="X57" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="Y57" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="Z57" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AA57" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AB57" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AC57" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="AD57" t="s">
         <v>126</v>
@@ -10330,7 +10507,7 @@
         <v>49</v>
       </c>
       <c r="AP57" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="58" spans="1:42" x14ac:dyDescent="0.3">
@@ -10341,34 +10518,34 @@
         <v>43</v>
       </c>
       <c r="C58" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D58" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E58" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F58" t="s">
         <v>173</v>
       </c>
       <c r="G58" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H58" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="I58" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="J58" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="K58" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="L58" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M58" t="s">
         <v>53</v>
@@ -10386,13 +10563,13 @@
         <v>57</v>
       </c>
       <c r="R58" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="S58" t="s">
         <v>49</v>
       </c>
       <c r="T58" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="U58" t="s">
         <v>57</v>
@@ -10404,25 +10581,25 @@
         <v>60</v>
       </c>
       <c r="X58" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="Y58" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="Z58" t="s">
         <v>49</v>
       </c>
       <c r="AA58" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AB58" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AC58" t="s">
         <v>62</v>
       </c>
       <c r="AD58" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AE58" t="s">
         <v>112</v>
@@ -10458,7 +10635,7 @@
         <v>49</v>
       </c>
       <c r="AP58" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="59" spans="1:42" x14ac:dyDescent="0.3">
@@ -10469,34 +10646,34 @@
         <v>43</v>
       </c>
       <c r="C59" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D59" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E59" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F59" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="G59" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="H59" t="s">
         <v>49</v>
       </c>
       <c r="I59" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="J59" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="K59" t="s">
-        <v>684</v>
+        <v>717</v>
       </c>
       <c r="L59" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="M59" t="s">
         <v>53</v>
@@ -10508,19 +10685,19 @@
         <v>55</v>
       </c>
       <c r="P59" t="s">
-        <v>94</v>
+        <v>378</v>
       </c>
       <c r="Q59" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="R59" t="s">
-        <v>707</v>
+        <v>563</v>
       </c>
       <c r="S59" t="s">
         <v>49</v>
       </c>
       <c r="T59" t="s">
-        <v>708</v>
+        <v>564</v>
       </c>
       <c r="U59" t="s">
         <v>57</v>
@@ -10529,31 +10706,31 @@
         <v>57</v>
       </c>
       <c r="W59" t="s">
-        <v>60</v>
+        <v>258</v>
       </c>
       <c r="X59" t="s">
-        <v>707</v>
+        <v>615</v>
       </c>
       <c r="Y59" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="Z59" t="s">
-        <v>49</v>
+        <v>616</v>
       </c>
       <c r="AA59" t="s">
-        <v>239</v>
+        <v>179</v>
       </c>
       <c r="AB59" t="s">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="AC59" t="s">
         <v>103</v>
       </c>
       <c r="AD59" t="s">
-        <v>229</v>
+        <v>366</v>
       </c>
       <c r="AE59" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="AF59" t="s">
         <v>65</v>
@@ -10586,7 +10763,775 @@
         <v>49</v>
       </c>
       <c r="AP59" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="60" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" t="s">
+        <v>43</v>
+      </c>
+      <c r="C60" t="s">
+        <v>711</v>
+      </c>
+      <c r="D60" t="s">
+        <v>712</v>
+      </c>
+      <c r="E60" t="s">
+        <v>713</v>
+      </c>
+      <c r="F60" t="s">
+        <v>236</v>
+      </c>
+      <c r="G60" t="s">
+        <v>714</v>
+      </c>
+      <c r="H60" t="s">
+        <v>49</v>
+      </c>
+      <c r="I60" t="s">
+        <v>715</v>
+      </c>
+      <c r="J60" t="s">
         <v>716</v>
+      </c>
+      <c r="K60" t="s">
+        <v>717</v>
+      </c>
+      <c r="L60" t="s">
+        <v>717</v>
+      </c>
+      <c r="M60" t="s">
+        <v>53</v>
+      </c>
+      <c r="N60" t="s">
+        <v>54</v>
+      </c>
+      <c r="O60" t="s">
+        <v>55</v>
+      </c>
+      <c r="P60" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>76</v>
+      </c>
+      <c r="R60" t="s">
+        <v>483</v>
+      </c>
+      <c r="S60" t="s">
+        <v>49</v>
+      </c>
+      <c r="T60" t="s">
+        <v>512</v>
+      </c>
+      <c r="U60" t="s">
+        <v>57</v>
+      </c>
+      <c r="V60" t="s">
+        <v>57</v>
+      </c>
+      <c r="W60" t="s">
+        <v>258</v>
+      </c>
+      <c r="X60" t="s">
+        <v>482</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>717</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>513</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB60" t="s">
+        <v>720</v>
+      </c>
+      <c r="AC60" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD60" t="s">
+        <v>104</v>
+      </c>
+      <c r="AE60" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF60" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG60" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH60" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI60" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ60" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK60" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL60" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM60" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN60" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO60" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP60" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="61" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>42</v>
+      </c>
+      <c r="B61" t="s">
+        <v>43</v>
+      </c>
+      <c r="C61" t="s">
+        <v>722</v>
+      </c>
+      <c r="D61" t="s">
+        <v>723</v>
+      </c>
+      <c r="E61" t="s">
+        <v>724</v>
+      </c>
+      <c r="F61" t="s">
+        <v>157</v>
+      </c>
+      <c r="G61" t="s">
+        <v>725</v>
+      </c>
+      <c r="H61" t="s">
+        <v>49</v>
+      </c>
+      <c r="I61" t="s">
+        <v>726</v>
+      </c>
+      <c r="J61" t="s">
+        <v>727</v>
+      </c>
+      <c r="K61" t="s">
+        <v>717</v>
+      </c>
+      <c r="L61" t="s">
+        <v>717</v>
+      </c>
+      <c r="M61" t="s">
+        <v>53</v>
+      </c>
+      <c r="N61" t="s">
+        <v>54</v>
+      </c>
+      <c r="O61" t="s">
+        <v>55</v>
+      </c>
+      <c r="P61" t="s">
+        <v>648</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>241</v>
+      </c>
+      <c r="R61" t="s">
+        <v>728</v>
+      </c>
+      <c r="S61" t="s">
+        <v>49</v>
+      </c>
+      <c r="T61" t="s">
+        <v>729</v>
+      </c>
+      <c r="U61" t="s">
+        <v>57</v>
+      </c>
+      <c r="V61" t="s">
+        <v>57</v>
+      </c>
+      <c r="W61" t="s">
+        <v>730</v>
+      </c>
+      <c r="X61" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>717</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>731</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB61" t="s">
+        <v>732</v>
+      </c>
+      <c r="AC61" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD61" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE61" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF61" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG61" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH61" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI61" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ61" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK61" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL61" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM61" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN61" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO61" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP61" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="62" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" t="s">
+        <v>43</v>
+      </c>
+      <c r="C62" t="s">
+        <v>734</v>
+      </c>
+      <c r="D62" t="s">
+        <v>735</v>
+      </c>
+      <c r="E62" t="s">
+        <v>736</v>
+      </c>
+      <c r="F62" t="s">
+        <v>157</v>
+      </c>
+      <c r="G62" t="s">
+        <v>737</v>
+      </c>
+      <c r="H62" t="s">
+        <v>49</v>
+      </c>
+      <c r="I62" t="s">
+        <v>738</v>
+      </c>
+      <c r="J62" t="s">
+        <v>739</v>
+      </c>
+      <c r="K62" t="s">
+        <v>717</v>
+      </c>
+      <c r="L62" t="s">
+        <v>717</v>
+      </c>
+      <c r="M62" t="s">
+        <v>53</v>
+      </c>
+      <c r="N62" t="s">
+        <v>54</v>
+      </c>
+      <c r="O62" t="s">
+        <v>399</v>
+      </c>
+      <c r="P62" t="s">
+        <v>740</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>627</v>
+      </c>
+      <c r="R62" t="s">
+        <v>483</v>
+      </c>
+      <c r="S62" t="s">
+        <v>49</v>
+      </c>
+      <c r="T62" t="s">
+        <v>512</v>
+      </c>
+      <c r="U62" t="s">
+        <v>57</v>
+      </c>
+      <c r="V62" t="s">
+        <v>57</v>
+      </c>
+      <c r="W62" t="s">
+        <v>741</v>
+      </c>
+      <c r="X62" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>717</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>742</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>743</v>
+      </c>
+      <c r="AB62" t="s">
+        <v>744</v>
+      </c>
+      <c r="AC62" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD62" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE62" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF62" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG62" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH62" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI62" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ62" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK62" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL62" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM62" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN62" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO62" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP62" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="63" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" t="s">
+        <v>43</v>
+      </c>
+      <c r="C63" t="s">
+        <v>746</v>
+      </c>
+      <c r="D63" t="s">
+        <v>747</v>
+      </c>
+      <c r="E63" t="s">
+        <v>748</v>
+      </c>
+      <c r="F63" t="s">
+        <v>173</v>
+      </c>
+      <c r="G63" t="s">
+        <v>705</v>
+      </c>
+      <c r="H63" t="s">
+        <v>49</v>
+      </c>
+      <c r="I63" t="s">
+        <v>749</v>
+      </c>
+      <c r="J63" t="s">
+        <v>750</v>
+      </c>
+      <c r="K63" t="s">
+        <v>685</v>
+      </c>
+      <c r="L63" t="s">
+        <v>717</v>
+      </c>
+      <c r="M63" t="s">
+        <v>53</v>
+      </c>
+      <c r="N63" t="s">
+        <v>54</v>
+      </c>
+      <c r="O63" t="s">
+        <v>55</v>
+      </c>
+      <c r="P63" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>57</v>
+      </c>
+      <c r="R63" t="s">
+        <v>708</v>
+      </c>
+      <c r="S63" t="s">
+        <v>49</v>
+      </c>
+      <c r="T63" t="s">
+        <v>709</v>
+      </c>
+      <c r="U63" t="s">
+        <v>57</v>
+      </c>
+      <c r="V63" t="s">
+        <v>57</v>
+      </c>
+      <c r="W63" t="s">
+        <v>60</v>
+      </c>
+      <c r="X63" t="s">
+        <v>708</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>717</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB63" t="s">
+        <v>708</v>
+      </c>
+      <c r="AC63" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD63" t="s">
+        <v>231</v>
+      </c>
+      <c r="AE63" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF63" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG63" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH63" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI63" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ63" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK63" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL63" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM63" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN63" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO63" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP63" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="64" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" t="s">
+        <v>43</v>
+      </c>
+      <c r="C64" t="s">
+        <v>752</v>
+      </c>
+      <c r="D64" t="s">
+        <v>753</v>
+      </c>
+      <c r="E64" t="s">
+        <v>754</v>
+      </c>
+      <c r="F64" t="s">
+        <v>269</v>
+      </c>
+      <c r="G64" t="s">
+        <v>755</v>
+      </c>
+      <c r="H64" t="s">
+        <v>49</v>
+      </c>
+      <c r="I64" t="s">
+        <v>756</v>
+      </c>
+      <c r="J64" t="s">
+        <v>757</v>
+      </c>
+      <c r="K64" t="s">
+        <v>625</v>
+      </c>
+      <c r="L64" t="s">
+        <v>625</v>
+      </c>
+      <c r="M64" t="s">
+        <v>53</v>
+      </c>
+      <c r="N64" t="s">
+        <v>54</v>
+      </c>
+      <c r="O64" t="s">
+        <v>140</v>
+      </c>
+      <c r="P64" t="s">
+        <v>758</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>212</v>
+      </c>
+      <c r="R64" t="s">
+        <v>759</v>
+      </c>
+      <c r="S64" t="s">
+        <v>49</v>
+      </c>
+      <c r="T64" t="s">
+        <v>760</v>
+      </c>
+      <c r="U64" t="s">
+        <v>57</v>
+      </c>
+      <c r="V64" t="s">
+        <v>57</v>
+      </c>
+      <c r="W64" t="s">
+        <v>164</v>
+      </c>
+      <c r="X64" t="s">
+        <v>761</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>625</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>762</v>
+      </c>
+      <c r="AA64" t="s">
+        <v>343</v>
+      </c>
+      <c r="AB64" t="s">
+        <v>763</v>
+      </c>
+      <c r="AC64" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD64" t="s">
+        <v>231</v>
+      </c>
+      <c r="AE64" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF64" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG64" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH64" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI64" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ64" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK64" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL64" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM64" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN64" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO64" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP64" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="65" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" t="s">
+        <v>43</v>
+      </c>
+      <c r="C65" t="s">
+        <v>765</v>
+      </c>
+      <c r="D65" t="s">
+        <v>766</v>
+      </c>
+      <c r="E65" t="s">
+        <v>767</v>
+      </c>
+      <c r="F65" t="s">
+        <v>768</v>
+      </c>
+      <c r="G65" t="s">
+        <v>769</v>
+      </c>
+      <c r="H65" t="s">
+        <v>770</v>
+      </c>
+      <c r="I65" t="s">
+        <v>770</v>
+      </c>
+      <c r="J65" t="s">
+        <v>771</v>
+      </c>
+      <c r="K65" t="s">
+        <v>568</v>
+      </c>
+      <c r="L65" t="s">
+        <v>568</v>
+      </c>
+      <c r="M65" t="s">
+        <v>53</v>
+      </c>
+      <c r="N65" t="s">
+        <v>54</v>
+      </c>
+      <c r="O65" t="s">
+        <v>140</v>
+      </c>
+      <c r="P65" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>143</v>
+      </c>
+      <c r="R65" t="s">
+        <v>593</v>
+      </c>
+      <c r="S65" t="s">
+        <v>49</v>
+      </c>
+      <c r="T65" t="s">
+        <v>594</v>
+      </c>
+      <c r="U65" t="s">
+        <v>57</v>
+      </c>
+      <c r="V65" t="s">
+        <v>57</v>
+      </c>
+      <c r="W65" t="s">
+        <v>164</v>
+      </c>
+      <c r="X65" t="s">
+        <v>772</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>568</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>773</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>343</v>
+      </c>
+      <c r="AB65" t="s">
+        <v>774</v>
+      </c>
+      <c r="AC65" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD65" t="s">
+        <v>328</v>
+      </c>
+      <c r="AE65" t="s">
+        <v>329</v>
+      </c>
+      <c r="AF65" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG65" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH65" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI65" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ65" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK65" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL65" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM65" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN65" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO65" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP65" t="s">
+        <v>775</v>
       </c>
     </row>
   </sheetData>

--- a/datos/CV_PF.xlsx
+++ b/datos/CV_PF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://funerariaimchile-my.sharepoint.com/personal/anais_gonzalez_funerariaim_cl/Documents/Dashboard_Control Diario de Ventas/Archivos diarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{209904C7-2047-4A83-A536-14BE0857E281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC119C9A-4E9A-4ABA-81A6-6C4D1B44A38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2730" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2856" uniqueCount="810">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -2224,6 +2224,42 @@
     <t>3991</t>
   </si>
   <si>
+    <t>6839198-9</t>
+  </si>
+  <si>
+    <t>HERMOSILLA NORAMBUENA GRACIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>05/01/1949</t>
+  </si>
+  <si>
+    <t>La Pintana</t>
+  </si>
+  <si>
+    <t>11122 - La Pintana - Santiago -CP</t>
+  </si>
+  <si>
+    <t>987418795</t>
+  </si>
+  <si>
+    <t>mana2010@live.cl; ; ; ;</t>
+  </si>
+  <si>
+    <t>Nayaret tatiana puga marchant</t>
+  </si>
+  <si>
+    <t>1344538</t>
+  </si>
+  <si>
+    <t>500000</t>
+  </si>
+  <si>
+    <t>18644</t>
+  </si>
+  <si>
+    <t>3992</t>
+  </si>
+  <si>
     <t>11399404-5</t>
   </si>
   <si>
@@ -2242,9 +2278,6 @@
     <t>edelmiraguerraleiv@gmail.com; ; ; ;</t>
   </si>
   <si>
-    <t>Nayaret tatiana puga marchant</t>
-  </si>
-  <si>
     <t>0.08</t>
   </si>
   <si>
@@ -2348,6 +2381,75 @@
   </si>
   <si>
     <t>3999</t>
+  </si>
+  <si>
+    <t>14715130-6</t>
+  </si>
+  <si>
+    <t>VALAREZO MACIAS LAURA  ANGELINA</t>
+  </si>
+  <si>
+    <t>25/03/1976</t>
+  </si>
+  <si>
+    <t>Santo Domingo</t>
+  </si>
+  <si>
+    <t>101 - Santo Domingo - San Antonio -CP</t>
+  </si>
+  <si>
+    <t>992376457</t>
+  </si>
+  <si>
+    <t>laura_valarezo@yahoo.es; ; ; ;</t>
+  </si>
+  <si>
+    <t>25/03/2026</t>
+  </si>
+  <si>
+    <t>6630000</t>
+  </si>
+  <si>
+    <t>5571429</t>
+  </si>
+  <si>
+    <t>663000</t>
+  </si>
+  <si>
+    <t>5967000</t>
+  </si>
+  <si>
+    <t>165750</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO TESOROS DEL ALMA SOLUCIÓN TOTAL FAMILIAR</t>
+  </si>
+  <si>
+    <t>4002</t>
+  </si>
+  <si>
+    <t>22010293-9</t>
+  </si>
+  <si>
+    <t>AVILA CANDIA CAMILA VALERIA</t>
+  </si>
+  <si>
+    <t>29/12/2005</t>
+  </si>
+  <si>
+    <t>239 - San Bernardo - Maipo -CP</t>
+  </si>
+  <si>
+    <t>990934743</t>
+  </si>
+  <si>
+    <t>camila.avila.candia@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>4003</t>
   </si>
 </sst>
 </file>
@@ -3208,10 +3310,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AP65"/>
+  <dimension ref="A1:AP68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="42" width="8" customWidth="1"/>
+    <col min="1" max="41" width="8" customWidth="1"/>
+    <col min="42" max="42" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.3">
@@ -8548,7 +8651,7 @@
         <v>555</v>
       </c>
       <c r="AC42" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="AD42" t="s">
         <v>311</v>
@@ -9649,7 +9752,7 @@
         <v>423</v>
       </c>
       <c r="L51" t="s">
-        <v>479</v>
+        <v>568</v>
       </c>
       <c r="M51" t="s">
         <v>53</v>
@@ -10084,7 +10187,7 @@
         <v>687</v>
       </c>
       <c r="AC54" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="AD54" t="s">
         <v>104</v>
@@ -11039,25 +11142,25 @@
         <v>736</v>
       </c>
       <c r="F62" t="s">
-        <v>157</v>
+        <v>737</v>
       </c>
       <c r="G62" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H62" t="s">
         <v>49</v>
       </c>
       <c r="I62" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="J62" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="K62" t="s">
-        <v>717</v>
+        <v>660</v>
       </c>
       <c r="L62" t="s">
-        <v>717</v>
+        <v>660</v>
       </c>
       <c r="M62" t="s">
         <v>53</v>
@@ -11069,19 +11172,19 @@
         <v>399</v>
       </c>
       <c r="P62" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="Q62" t="s">
         <v>627</v>
       </c>
       <c r="R62" t="s">
-        <v>483</v>
+        <v>513</v>
       </c>
       <c r="S62" t="s">
         <v>49</v>
       </c>
       <c r="T62" t="s">
-        <v>512</v>
+        <v>742</v>
       </c>
       <c r="U62" t="s">
         <v>57</v>
@@ -11090,19 +11193,19 @@
         <v>57</v>
       </c>
       <c r="W62" t="s">
-        <v>741</v>
+        <v>182</v>
       </c>
       <c r="X62" t="s">
-        <v>165</v>
+        <v>743</v>
       </c>
       <c r="Y62" t="s">
-        <v>717</v>
+        <v>660</v>
       </c>
       <c r="Z62" t="s">
-        <v>742</v>
+        <v>469</v>
       </c>
       <c r="AA62" t="s">
-        <v>743</v>
+        <v>309</v>
       </c>
       <c r="AB62" t="s">
         <v>744</v>
@@ -11111,10 +11214,10 @@
         <v>103</v>
       </c>
       <c r="AD62" t="s">
-        <v>111</v>
+        <v>516</v>
       </c>
       <c r="AE62" t="s">
-        <v>112</v>
+        <v>312</v>
       </c>
       <c r="AF62" t="s">
         <v>65</v>
@@ -11167,22 +11270,22 @@
         <v>748</v>
       </c>
       <c r="F63" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="G63" t="s">
-        <v>705</v>
+        <v>749</v>
       </c>
       <c r="H63" t="s">
         <v>49</v>
       </c>
       <c r="I63" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="J63" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="K63" t="s">
-        <v>685</v>
+        <v>717</v>
       </c>
       <c r="L63" t="s">
         <v>717</v>
@@ -11194,22 +11297,22 @@
         <v>54</v>
       </c>
       <c r="O63" t="s">
-        <v>55</v>
+        <v>399</v>
       </c>
       <c r="P63" t="s">
-        <v>94</v>
+        <v>741</v>
       </c>
       <c r="Q63" t="s">
-        <v>57</v>
+        <v>627</v>
       </c>
       <c r="R63" t="s">
-        <v>708</v>
+        <v>483</v>
       </c>
       <c r="S63" t="s">
         <v>49</v>
       </c>
       <c r="T63" t="s">
-        <v>709</v>
+        <v>512</v>
       </c>
       <c r="U63" t="s">
         <v>57</v>
@@ -11218,28 +11321,28 @@
         <v>57</v>
       </c>
       <c r="W63" t="s">
-        <v>60</v>
+        <v>752</v>
       </c>
       <c r="X63" t="s">
-        <v>708</v>
+        <v>165</v>
       </c>
       <c r="Y63" t="s">
         <v>717</v>
       </c>
       <c r="Z63" t="s">
-        <v>49</v>
+        <v>753</v>
       </c>
       <c r="AA63" t="s">
-        <v>241</v>
+        <v>754</v>
       </c>
       <c r="AB63" t="s">
-        <v>708</v>
+        <v>755</v>
       </c>
       <c r="AC63" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="AD63" t="s">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="AE63" t="s">
         <v>112</v>
@@ -11275,7 +11378,7 @@
         <v>49</v>
       </c>
       <c r="AP63" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
     </row>
     <row r="64" spans="1:42" x14ac:dyDescent="0.3">
@@ -11286,34 +11389,34 @@
         <v>43</v>
       </c>
       <c r="C64" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="D64" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="E64" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="F64" t="s">
-        <v>269</v>
+        <v>173</v>
       </c>
       <c r="G64" t="s">
-        <v>755</v>
+        <v>705</v>
       </c>
       <c r="H64" t="s">
         <v>49</v>
       </c>
       <c r="I64" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="J64" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="K64" t="s">
-        <v>625</v>
+        <v>685</v>
       </c>
       <c r="L64" t="s">
-        <v>625</v>
+        <v>717</v>
       </c>
       <c r="M64" t="s">
         <v>53</v>
@@ -11322,22 +11425,22 @@
         <v>54</v>
       </c>
       <c r="O64" t="s">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="P64" t="s">
-        <v>758</v>
+        <v>94</v>
       </c>
       <c r="Q64" t="s">
-        <v>212</v>
+        <v>57</v>
       </c>
       <c r="R64" t="s">
-        <v>759</v>
+        <v>708</v>
       </c>
       <c r="S64" t="s">
         <v>49</v>
       </c>
       <c r="T64" t="s">
-        <v>760</v>
+        <v>709</v>
       </c>
       <c r="U64" t="s">
         <v>57</v>
@@ -11346,25 +11449,25 @@
         <v>57</v>
       </c>
       <c r="W64" t="s">
-        <v>164</v>
+        <v>60</v>
       </c>
       <c r="X64" t="s">
-        <v>761</v>
+        <v>708</v>
       </c>
       <c r="Y64" t="s">
-        <v>625</v>
+        <v>717</v>
       </c>
       <c r="Z64" t="s">
-        <v>762</v>
+        <v>49</v>
       </c>
       <c r="AA64" t="s">
-        <v>343</v>
+        <v>241</v>
       </c>
       <c r="AB64" t="s">
-        <v>763</v>
+        <v>708</v>
       </c>
       <c r="AC64" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="AD64" t="s">
         <v>231</v>
@@ -11403,7 +11506,7 @@
         <v>49</v>
       </c>
       <c r="AP64" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="65" spans="1:42" x14ac:dyDescent="0.3">
@@ -11414,34 +11517,34 @@
         <v>43</v>
       </c>
       <c r="C65" t="s">
+        <v>763</v>
+      </c>
+      <c r="D65" t="s">
+        <v>764</v>
+      </c>
+      <c r="E65" t="s">
         <v>765</v>
       </c>
-      <c r="D65" t="s">
+      <c r="F65" t="s">
+        <v>269</v>
+      </c>
+      <c r="G65" t="s">
         <v>766</v>
       </c>
-      <c r="E65" t="s">
+      <c r="H65" t="s">
+        <v>49</v>
+      </c>
+      <c r="I65" t="s">
         <v>767</v>
       </c>
-      <c r="F65" t="s">
+      <c r="J65" t="s">
         <v>768</v>
       </c>
-      <c r="G65" t="s">
-        <v>769</v>
-      </c>
-      <c r="H65" t="s">
-        <v>770</v>
-      </c>
-      <c r="I65" t="s">
-        <v>770</v>
-      </c>
-      <c r="J65" t="s">
-        <v>771</v>
-      </c>
       <c r="K65" t="s">
-        <v>568</v>
+        <v>625</v>
       </c>
       <c r="L65" t="s">
-        <v>568</v>
+        <v>625</v>
       </c>
       <c r="M65" t="s">
         <v>53</v>
@@ -11453,19 +11556,19 @@
         <v>140</v>
       </c>
       <c r="P65" t="s">
-        <v>240</v>
+        <v>769</v>
       </c>
       <c r="Q65" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="R65" t="s">
-        <v>593</v>
+        <v>770</v>
       </c>
       <c r="S65" t="s">
         <v>49</v>
       </c>
       <c r="T65" t="s">
-        <v>594</v>
+        <v>771</v>
       </c>
       <c r="U65" t="s">
         <v>57</v>
@@ -11480,7 +11583,7 @@
         <v>772</v>
       </c>
       <c r="Y65" t="s">
-        <v>568</v>
+        <v>625</v>
       </c>
       <c r="Z65" t="s">
         <v>773</v>
@@ -11495,10 +11598,10 @@
         <v>103</v>
       </c>
       <c r="AD65" t="s">
-        <v>328</v>
+        <v>231</v>
       </c>
       <c r="AE65" t="s">
-        <v>329</v>
+        <v>112</v>
       </c>
       <c r="AF65" t="s">
         <v>65</v>
@@ -11532,6 +11635,390 @@
       </c>
       <c r="AP65" t="s">
         <v>775</v>
+      </c>
+    </row>
+    <row r="66" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>42</v>
+      </c>
+      <c r="B66" t="s">
+        <v>43</v>
+      </c>
+      <c r="C66" t="s">
+        <v>776</v>
+      </c>
+      <c r="D66" t="s">
+        <v>777</v>
+      </c>
+      <c r="E66" t="s">
+        <v>778</v>
+      </c>
+      <c r="F66" t="s">
+        <v>779</v>
+      </c>
+      <c r="G66" t="s">
+        <v>780</v>
+      </c>
+      <c r="H66" t="s">
+        <v>781</v>
+      </c>
+      <c r="I66" t="s">
+        <v>781</v>
+      </c>
+      <c r="J66" t="s">
+        <v>782</v>
+      </c>
+      <c r="K66" t="s">
+        <v>568</v>
+      </c>
+      <c r="L66" t="s">
+        <v>568</v>
+      </c>
+      <c r="M66" t="s">
+        <v>53</v>
+      </c>
+      <c r="N66" t="s">
+        <v>54</v>
+      </c>
+      <c r="O66" t="s">
+        <v>140</v>
+      </c>
+      <c r="P66" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>143</v>
+      </c>
+      <c r="R66" t="s">
+        <v>593</v>
+      </c>
+      <c r="S66" t="s">
+        <v>49</v>
+      </c>
+      <c r="T66" t="s">
+        <v>594</v>
+      </c>
+      <c r="U66" t="s">
+        <v>57</v>
+      </c>
+      <c r="V66" t="s">
+        <v>57</v>
+      </c>
+      <c r="W66" t="s">
+        <v>164</v>
+      </c>
+      <c r="X66" t="s">
+        <v>783</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>568</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>784</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>343</v>
+      </c>
+      <c r="AB66" t="s">
+        <v>785</v>
+      </c>
+      <c r="AC66" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD66" t="s">
+        <v>328</v>
+      </c>
+      <c r="AE66" t="s">
+        <v>329</v>
+      </c>
+      <c r="AF66" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG66" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH66" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI66" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ66" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK66" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL66" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM66" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN66" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO66" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP66" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="67" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>42</v>
+      </c>
+      <c r="B67" t="s">
+        <v>501</v>
+      </c>
+      <c r="C67" t="s">
+        <v>787</v>
+      </c>
+      <c r="D67" t="s">
+        <v>788</v>
+      </c>
+      <c r="E67" t="s">
+        <v>789</v>
+      </c>
+      <c r="F67" t="s">
+        <v>790</v>
+      </c>
+      <c r="G67" t="s">
+        <v>791</v>
+      </c>
+      <c r="H67" t="s">
+        <v>49</v>
+      </c>
+      <c r="I67" t="s">
+        <v>792</v>
+      </c>
+      <c r="J67" t="s">
+        <v>793</v>
+      </c>
+      <c r="K67" t="s">
+        <v>479</v>
+      </c>
+      <c r="L67" t="s">
+        <v>794</v>
+      </c>
+      <c r="M67" t="s">
+        <v>53</v>
+      </c>
+      <c r="N67" t="s">
+        <v>54</v>
+      </c>
+      <c r="O67" t="s">
+        <v>339</v>
+      </c>
+      <c r="P67" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>212</v>
+      </c>
+      <c r="R67" t="s">
+        <v>795</v>
+      </c>
+      <c r="S67" t="s">
+        <v>49</v>
+      </c>
+      <c r="T67" t="s">
+        <v>796</v>
+      </c>
+      <c r="U67" t="s">
+        <v>57</v>
+      </c>
+      <c r="V67" t="s">
+        <v>57</v>
+      </c>
+      <c r="W67" t="s">
+        <v>164</v>
+      </c>
+      <c r="X67" t="s">
+        <v>797</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>798</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>651</v>
+      </c>
+      <c r="AB67" t="s">
+        <v>799</v>
+      </c>
+      <c r="AC67" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD67" t="s">
+        <v>800</v>
+      </c>
+      <c r="AE67" t="s">
+        <v>457</v>
+      </c>
+      <c r="AF67" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG67" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH67" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI67" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ67" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK67" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL67" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM67" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN67" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO67" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP67" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="68" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" t="s">
+        <v>43</v>
+      </c>
+      <c r="C68" t="s">
+        <v>802</v>
+      </c>
+      <c r="D68" t="s">
+        <v>803</v>
+      </c>
+      <c r="E68" t="s">
+        <v>804</v>
+      </c>
+      <c r="F68" t="s">
+        <v>372</v>
+      </c>
+      <c r="G68" t="s">
+        <v>805</v>
+      </c>
+      <c r="H68" t="s">
+        <v>49</v>
+      </c>
+      <c r="I68" t="s">
+        <v>806</v>
+      </c>
+      <c r="J68" t="s">
+        <v>807</v>
+      </c>
+      <c r="K68" t="s">
+        <v>613</v>
+      </c>
+      <c r="L68" t="s">
+        <v>613</v>
+      </c>
+      <c r="M68" t="s">
+        <v>53</v>
+      </c>
+      <c r="N68" t="s">
+        <v>54</v>
+      </c>
+      <c r="O68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P68" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>57</v>
+      </c>
+      <c r="R68" t="s">
+        <v>469</v>
+      </c>
+      <c r="S68" t="s">
+        <v>49</v>
+      </c>
+      <c r="T68" t="s">
+        <v>569</v>
+      </c>
+      <c r="U68" t="s">
+        <v>57</v>
+      </c>
+      <c r="V68" t="s">
+        <v>57</v>
+      </c>
+      <c r="W68" t="s">
+        <v>60</v>
+      </c>
+      <c r="X68" t="s">
+        <v>469</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>613</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA68" t="s">
+        <v>808</v>
+      </c>
+      <c r="AB68" t="s">
+        <v>469</v>
+      </c>
+      <c r="AC68" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD68" t="s">
+        <v>231</v>
+      </c>
+      <c r="AE68" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF68" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG68" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH68" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI68" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ68" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK68" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL68" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM68" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN68" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO68" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP68" t="s">
+        <v>809</v>
       </c>
     </row>
   </sheetData>

--- a/datos/CV_PF.xlsx
+++ b/datos/CV_PF.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://funerariaimchile-my.sharepoint.com/personal/anais_gonzalez_funerariaim_cl/Documents/Dashboard_Control Diario de Ventas/Archivos diarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC119C9A-4E9A-4ABA-81A6-6C4D1B44A38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{079E242A-E170-4632-B6D2-CEC0CD3413F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -331,1327 +331,1327 @@
     <t>113333</t>
   </si>
   <si>
+    <t>SERVICIO FUNERARIO RAICES DE VIDA ADULTO MAYOR</t>
+  </si>
+  <si>
+    <t>3738</t>
+  </si>
+  <si>
+    <t>1350000</t>
+  </si>
+  <si>
+    <t>1134454</t>
+  </si>
+  <si>
+    <t>270000</t>
+  </si>
+  <si>
+    <t>1080000</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO RAICES DE VIDA PERSONAL</t>
+  </si>
+  <si>
+    <t>PERSONAL</t>
+  </si>
+  <si>
+    <t>3739</t>
+  </si>
+  <si>
+    <t>8825803-7</t>
+  </si>
+  <si>
+    <t>DE LA FUENTE CELPA CAROLINA ELVIRA JACQUELINE</t>
+  </si>
+  <si>
+    <t>15/07/1964</t>
+  </si>
+  <si>
+    <t>Ñuñoa</t>
+  </si>
+  <si>
+    <t>401 - Ñuñoa - Santiago -CP</t>
+  </si>
+  <si>
+    <t>993176608</t>
+  </si>
+  <si>
+    <t>oyarzoquijada@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>26/02/2026</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>1710000</t>
+  </si>
+  <si>
+    <t>1436975</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO SOLUCIÓN TOTAL PERSONAL</t>
+  </si>
+  <si>
+    <t>PERSONAL SOLUCIÓN TOTAL</t>
+  </si>
+  <si>
+    <t>3744</t>
+  </si>
+  <si>
+    <t>7880880-2</t>
+  </si>
+  <si>
+    <t>OYARZO QUIJADA SANTOS JAVIER</t>
+  </si>
+  <si>
+    <t>15/03/1960</t>
+  </si>
+  <si>
+    <t>3745</t>
+  </si>
+  <si>
+    <t>8854225-8</t>
+  </si>
+  <si>
+    <t>MÉNDEZ SEPÚLVEDA JOSÉ</t>
+  </si>
+  <si>
+    <t>10/12/1960</t>
+  </si>
+  <si>
+    <t>Peñalolén</t>
+  </si>
+  <si>
+    <t>6299 - Peñalolén - Santiago -CP</t>
+  </si>
+  <si>
+    <t>988251457</t>
+  </si>
+  <si>
+    <t>joseedelfin@hotmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>Camilo Jesus Medel Rojas</t>
+  </si>
+  <si>
+    <t>Luis Alberto Osores   Osores</t>
+  </si>
+  <si>
+    <t>3746</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>7950000</t>
+  </si>
+  <si>
+    <t>6680672</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>1060000</t>
+  </si>
+  <si>
+    <t>6890000</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>143542</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO SOLUCIÓN TOTAL SIEMPRE JUNTOS</t>
+  </si>
+  <si>
+    <t>SIEMPRE JUNTOS SOLUCIÓN TOTAL</t>
+  </si>
+  <si>
+    <t>3747</t>
+  </si>
+  <si>
+    <t>7563296-7</t>
+  </si>
+  <si>
+    <t>AYALA VILLARROEL NORMA DE LAS MERCEDES</t>
+  </si>
+  <si>
+    <t>11/11/1954</t>
+  </si>
+  <si>
+    <t>Quilicura</t>
+  </si>
+  <si>
+    <t>1093 - Quilicura - Santiago -CP</t>
+  </si>
+  <si>
+    <t>962053244</t>
+  </si>
+  <si>
+    <t>normaayala982@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>Francesca Nicole Sanchez pacheco</t>
+  </si>
+  <si>
+    <t>1440000</t>
+  </si>
+  <si>
+    <t>1210084</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>144000</t>
+  </si>
+  <si>
+    <t>1296000</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>27000</t>
+  </si>
+  <si>
+    <t>3751</t>
+  </si>
+  <si>
+    <t>5202611-3</t>
+  </si>
+  <si>
+    <t>PEREZ LAZO JUAN EUGENIO</t>
+  </si>
+  <si>
+    <t>06/02/1946</t>
+  </si>
+  <si>
+    <t>La Florida</t>
+  </si>
+  <si>
+    <t>6887 - La Florida - Santiago -CP</t>
+  </si>
+  <si>
+    <t>940660261</t>
+  </si>
+  <si>
+    <t>perezlazojuan46@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
+    <t>05/03/2026</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>3200000</t>
+  </si>
+  <si>
+    <t>2689076</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>1000000</t>
+  </si>
+  <si>
+    <t>2200000</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>440000</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO TESOROS DEL ALMA PERSONAL</t>
+  </si>
+  <si>
+    <t>3756</t>
+  </si>
+  <si>
+    <t>21589354-5</t>
+  </si>
+  <si>
+    <t>ORELLANA AVILA BELEN JESUS</t>
+  </si>
+  <si>
+    <t>21/10/1997</t>
+  </si>
+  <si>
+    <t>Huechuraba</t>
+  </si>
+  <si>
+    <t>591 - Huechuraba - Santiago -CP</t>
+  </si>
+  <si>
+    <t>979210576</t>
+  </si>
+  <si>
+    <t>belenorellana2424@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>HERLIZ DANIELA REQUENA GAMBOA</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>2850000</t>
+  </si>
+  <si>
+    <t>2394958</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>2800000</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>59574</t>
+  </si>
+  <si>
+    <t>3765</t>
+  </si>
+  <si>
+    <t>11054685-8</t>
+  </si>
+  <si>
+    <t>MOLINA OLMEDO JENNY ELIZABETH</t>
+  </si>
+  <si>
+    <t>29/05/1966</t>
+  </si>
+  <si>
+    <t>760 - Puente Alto - Cordillera -CP</t>
+  </si>
+  <si>
+    <t>987395077</t>
+  </si>
+  <si>
+    <t>jennydelaconso@hotmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>2500000</t>
+  </si>
+  <si>
+    <t>2100840</t>
+  </si>
+  <si>
+    <t>250000</t>
+  </si>
+  <si>
+    <t>2250000</t>
+  </si>
+  <si>
+    <t>62500</t>
+  </si>
+  <si>
+    <t>3767</t>
+  </si>
+  <si>
+    <t>9806863-5</t>
+  </si>
+  <si>
+    <t>CARDENAS MARTINEZ CECILIA OLGA</t>
+  </si>
+  <si>
+    <t>03/09/1963</t>
+  </si>
+  <si>
+    <t>San Ramón</t>
+  </si>
+  <si>
+    <t>9770 - San Ramón - Santiago -CP</t>
+  </si>
+  <si>
+    <t>971074760</t>
+  </si>
+  <si>
+    <t>ceciliacarmar@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>1320000</t>
+  </si>
+  <si>
+    <t>1109244</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO PERSONAL</t>
+  </si>
+  <si>
+    <t>3768</t>
+  </si>
+  <si>
+    <t>17487955-9</t>
+  </si>
+  <si>
+    <t>PIZARRO ROMERO BETZABE ALEJANDRA</t>
+  </si>
+  <si>
+    <t>04/09/1990</t>
+  </si>
+  <si>
+    <t>Maipú</t>
+  </si>
+  <si>
+    <t>2328 - Maipú - Santiago -CP</t>
+  </si>
+  <si>
+    <t>988146014</t>
+  </si>
+  <si>
+    <t>b.pizarro.romero@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>Alejandra Edith Otelo Zuñiga</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>2565000</t>
+  </si>
+  <si>
+    <t>2155462</t>
+  </si>
+  <si>
+    <t>256500</t>
+  </si>
+  <si>
+    <t>2308500</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>96188</t>
+  </si>
+  <si>
+    <t>3777</t>
+  </si>
+  <si>
+    <t>9603079-7</t>
+  </si>
+  <si>
+    <t>SEPULVEDA DIAZ PATRICIO EUGENIO</t>
+  </si>
+  <si>
+    <t>01/04/1964</t>
+  </si>
+  <si>
+    <t>Conchali</t>
+  </si>
+  <si>
+    <t>1337 - Conchali - Santiago -CP</t>
+  </si>
+  <si>
+    <t>982949955</t>
+  </si>
+  <si>
+    <t>psepulveda64@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>3100000</t>
+  </si>
+  <si>
+    <t>2605042</t>
+  </si>
+  <si>
+    <t>0.11</t>
+  </si>
+  <si>
+    <t>350000</t>
+  </si>
+  <si>
+    <t>2750000</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>45833</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO SOLUCIÓN TOTAL LIBRE</t>
+  </si>
+  <si>
+    <t>LIBRE SOLUCIÓN TOTAL</t>
+  </si>
+  <si>
+    <t>3781</t>
+  </si>
+  <si>
+    <t>4237433-4</t>
+  </si>
+  <si>
+    <t>ARAYA PEREZ GLADYS HEYDÉE</t>
+  </si>
+  <si>
+    <t>28/12/1941</t>
+  </si>
+  <si>
+    <t>Macul</t>
+  </si>
+  <si>
+    <t>2240 - Macul - Santiago -CP</t>
+  </si>
+  <si>
+    <t>994005973</t>
+  </si>
+  <si>
+    <t>GLADYSARAYAPEREZ@GMAIL.COM; ; ; ;</t>
+  </si>
+  <si>
+    <t>2700000</t>
+  </si>
+  <si>
+    <t>2268908</t>
+  </si>
+  <si>
+    <t>300000</t>
+  </si>
+  <si>
+    <t>2400000</t>
+  </si>
+  <si>
+    <t>3784</t>
+  </si>
+  <si>
+    <t>13265271-6</t>
+  </si>
+  <si>
+    <t>CARIMAN MUNOZ PAOLA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>19/04/1977</t>
+  </si>
+  <si>
+    <t>1362 - Maipú - Santiago -CP</t>
+  </si>
+  <si>
+    <t>973465528</t>
+  </si>
+  <si>
+    <t>paola.cariman@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>3150000</t>
+  </si>
+  <si>
+    <t>2647059</t>
+  </si>
+  <si>
+    <t>59375</t>
+  </si>
+  <si>
+    <t>3792</t>
+  </si>
+  <si>
+    <t>13682451-1</t>
+  </si>
+  <si>
+    <t>CARIMAN MUNOZ VERONICA CECILIA</t>
+  </si>
+  <si>
+    <t>27/07/1979</t>
+  </si>
+  <si>
+    <t>veronica.cariman@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>3450000</t>
+  </si>
+  <si>
+    <t>2899160</t>
+  </si>
+  <si>
+    <t>72000</t>
+  </si>
+  <si>
+    <t>3378000</t>
+  </si>
+  <si>
+    <t>71872</t>
+  </si>
+  <si>
+    <t>3794</t>
+  </si>
+  <si>
+    <t>17769780-K</t>
+  </si>
+  <si>
+    <t>HERNANDEZ PONCE PATRICIA CAROLINA</t>
+  </si>
+  <si>
+    <t>22/05/1991</t>
+  </si>
+  <si>
+    <t>Quinta Normal</t>
+  </si>
+  <si>
+    <t>2499 - Quinta Normal - Santiago -CP</t>
+  </si>
+  <si>
+    <t>974956288</t>
+  </si>
+  <si>
+    <t>patricia.carolinahp@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>07/03/2026</t>
+  </si>
+  <si>
+    <t>2352941</t>
+  </si>
+  <si>
+    <t>53000</t>
+  </si>
+  <si>
+    <t>2747000</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>58447</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO LIBRE</t>
+  </si>
+  <si>
+    <t>LIBRE</t>
+  </si>
+  <si>
+    <t>3800</t>
+  </si>
+  <si>
+    <t>10551410-7</t>
+  </si>
+  <si>
+    <t>HIDALGO VALDENEGRO MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>12/07/1965</t>
+  </si>
+  <si>
+    <t>31 - Puente Alto - Cordillera -CP</t>
+  </si>
+  <si>
+    <t>986113609</t>
+  </si>
+  <si>
+    <t>marcohidalgov087@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>Daniela Andrea Rivera  Hurtado</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>2550000</t>
+  </si>
+  <si>
+    <t>2142857</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>135000</t>
+  </si>
+  <si>
+    <t>2415000</t>
+  </si>
+  <si>
+    <t>33542</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO RAICES DE VIDA FAMILIAR</t>
+  </si>
+  <si>
+    <t>FAMILIAR</t>
+  </si>
+  <si>
+    <t>3802</t>
+  </si>
+  <si>
+    <t>10170200-6</t>
+  </si>
+  <si>
+    <t>MUÑOZ ZAMORA ANA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>29/07/1966</t>
+  </si>
+  <si>
+    <t>Lampa</t>
+  </si>
+  <si>
+    <t>923 - Lampa - Chacabuco -CP</t>
+  </si>
+  <si>
+    <t>979628954</t>
+  </si>
+  <si>
+    <t>22081986jeannette@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>VIVIANA HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ALEJANDRA VERDUGO</t>
+  </si>
+  <si>
+    <t>1875000</t>
+  </si>
+  <si>
+    <t>1575630</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>3818</t>
+  </si>
+  <si>
+    <t>10774061-9</t>
+  </si>
+  <si>
+    <t>MARTINEZ RIFFO RICHARD OMAR</t>
+  </si>
+  <si>
+    <t>20/01/1967</t>
+  </si>
+  <si>
+    <t>33 - Puente Alto - Cordillera -CP</t>
+  </si>
+  <si>
+    <t>946874213</t>
+  </si>
+  <si>
+    <t>ecommerce.richardmartinez11@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>1620000</t>
+  </si>
+  <si>
+    <t>1361345</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>1476000</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>6583103-1</t>
+  </si>
+  <si>
+    <t>VILCHES VILLALOBOS PEDRO</t>
+  </si>
+  <si>
+    <t>18/06/1952</t>
+  </si>
+  <si>
+    <t>1560 - Puente Alto - Cordillera -CP</t>
+  </si>
+  <si>
+    <t>956788731</t>
+  </si>
+  <si>
+    <t>vilches882018@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>2137500</t>
+  </si>
+  <si>
+    <t>1796218</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO RAICES DE VIDA SOLUCIÓN TOTAL ADULTO MAYOR</t>
+  </si>
+  <si>
+    <t>3823</t>
+  </si>
+  <si>
+    <t>3824</t>
+  </si>
+  <si>
+    <t>5386701-4</t>
+  </si>
+  <si>
+    <t>AGUIRRE RODRIGUEZ MARTA ALIANA</t>
+  </si>
+  <si>
+    <t>21/12/1940</t>
+  </si>
+  <si>
+    <t>San Bernardo</t>
+  </si>
+  <si>
+    <t>991 - San Bernardo - Maipo -CP</t>
+  </si>
+  <si>
+    <t>983516789</t>
+  </si>
+  <si>
+    <t>maguirrero@hotmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>08/03/2026</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>NELSON RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>3400000</t>
+  </si>
+  <si>
+    <t>2857143</t>
+  </si>
+  <si>
+    <t>400000</t>
+  </si>
+  <si>
+    <t>3000000</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO TESOROS DEL ALMA ADULTO MAYOR</t>
+  </si>
+  <si>
+    <t>3828</t>
+  </si>
+  <si>
+    <t>3927346-2</t>
+  </si>
+  <si>
+    <t>PIÑA ZAVALA HUMBERTO ARTURO</t>
+  </si>
+  <si>
+    <t>12/06/1938</t>
+  </si>
+  <si>
+    <t>961116221</t>
+  </si>
+  <si>
+    <t>humbertopina@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>3829</t>
+  </si>
+  <si>
+    <t>17241987-9</t>
+  </si>
+  <si>
+    <t>SALINAS SALINAS CAMILO ANDRES</t>
+  </si>
+  <si>
+    <t>04/03/1989</t>
+  </si>
+  <si>
+    <t>Santiago</t>
+  </si>
+  <si>
+    <t>580 - Santiago - Santiago -CP</t>
+  </si>
+  <si>
+    <t>949508704</t>
+  </si>
+  <si>
+    <t>camilo.salinas89@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>GABRIELA DEL CARMEN ROJAS QUEZADA</t>
+  </si>
+  <si>
+    <t>Margarita Cristina Rojas Quezada</t>
+  </si>
+  <si>
+    <t>2511562</t>
+  </si>
+  <si>
+    <t>53438</t>
+  </si>
+  <si>
+    <t>3832</t>
+  </si>
+  <si>
+    <t>8429029-7</t>
+  </si>
+  <si>
+    <t>LOPEZ CERDA GLORIA ANGELICA</t>
+  </si>
+  <si>
+    <t>09/12/1959</t>
+  </si>
+  <si>
+    <t>1323 - Lampa - Chacabuco -CP</t>
+  </si>
+  <si>
+    <t>986729324</t>
+  </si>
+  <si>
+    <t>diegorlando.lopez212@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>RODRIGO IGNACIO CASTRO FIGUEROA</t>
+  </si>
+  <si>
+    <t>162000</t>
+  </si>
+  <si>
+    <t>1458000</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>121500</t>
+  </si>
+  <si>
+    <t>SUCURSAL</t>
+  </si>
+  <si>
+    <t>3833</t>
+  </si>
+  <si>
+    <t>11127146-1</t>
+  </si>
+  <si>
+    <t>BRAVO MIRANDA ORIANA ALEJANDRINA</t>
+  </si>
+  <si>
+    <t>24/11/1967</t>
+  </si>
+  <si>
+    <t>337 - Puente Alto - Cordillera -CP</t>
+  </si>
+  <si>
+    <t>949101444</t>
+  </si>
+  <si>
+    <t>ivanbananas23@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>11/03/2026</t>
+  </si>
+  <si>
+    <t>2650000</t>
+  </si>
+  <si>
+    <t>2226891</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>3841</t>
+  </si>
+  <si>
+    <t>8176900-1</t>
+  </si>
+  <si>
+    <t>ZUÑIGA GALLARDO IVAN ARTURO</t>
+  </si>
+  <si>
+    <t>10/05/1968</t>
+  </si>
+  <si>
+    <t>3377 - Puente Alto - Cordillera -CP</t>
+  </si>
+  <si>
+    <t>986920954</t>
+  </si>
+  <si>
+    <t>3842</t>
+  </si>
+  <si>
+    <t>10033214-0</t>
+  </si>
+  <si>
+    <t>MENDOZA ORDENES ENNA ELIZABETH</t>
+  </si>
+  <si>
+    <t>21/08/1963</t>
+  </si>
+  <si>
+    <t>24 - Quilicura - Santiago -CP</t>
+  </si>
+  <si>
+    <t>949464419</t>
+  </si>
+  <si>
+    <t>KATHERINSOTOGARRIDO@GMAIL.COM; ; ; ;</t>
+  </si>
+  <si>
+    <t>Fernanda Scarlet Cuevas Olivares</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>3844</t>
+  </si>
+  <si>
+    <t>12478544-8</t>
+  </si>
+  <si>
+    <t>PUGA MENDEZ CLAUDIO ALEJANDRO</t>
+  </si>
+  <si>
+    <t>11/10/1971</t>
+  </si>
+  <si>
+    <t>260 - Quilicura - Santiago -CP</t>
+  </si>
+  <si>
+    <t>994361654</t>
+  </si>
+  <si>
+    <t>CPUGA1971@GMAIL.COM; ; ; ;</t>
+  </si>
+  <si>
+    <t>Marcela Antonia  Valdés  Barrios</t>
+  </si>
+  <si>
+    <t>4400000</t>
+  </si>
+  <si>
+    <t>3697479</t>
+  </si>
+  <si>
+    <t>444000</t>
+  </si>
+  <si>
+    <t>3956000</t>
+  </si>
+  <si>
+    <t>65933</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO SOLUCIÓN TOTAL FAMILIAR</t>
+  </si>
+  <si>
+    <t>FAMILIAR SOLUCIÓN TOTAL</t>
+  </si>
+  <si>
+    <t>3846</t>
+  </si>
+  <si>
+    <t>20944439-9</t>
+  </si>
+  <si>
+    <t>VALDES BARRIOS MARCELA ANTONIA</t>
+  </si>
+  <si>
+    <t>28/12/2001</t>
+  </si>
+  <si>
+    <t>313 - Quilicura - Santiago -CP</t>
+  </si>
+  <si>
+    <t>940987799</t>
+  </si>
+  <si>
+    <t>antovaldes327@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>12/03/2026</t>
+  </si>
+  <si>
+    <t>14/03/2026</t>
+  </si>
+  <si>
+    <t>1848739</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>1100000</t>
+  </si>
+  <si>
+    <t>INACTIVO</t>
+  </si>
+  <si>
+    <t>2026-03-17T00:00:00</t>
+  </si>
+  <si>
+    <t>3868</t>
+  </si>
+  <si>
+    <t>4413981-2</t>
+  </si>
+  <si>
+    <t>SEPULVEDA PEREZ NOEMI</t>
+  </si>
+  <si>
+    <t>07/11/1935</t>
+  </si>
+  <si>
+    <t>1528 - Puente Alto - Cordillera -CP</t>
+  </si>
+  <si>
+    <t>965902208</t>
+  </si>
+  <si>
+    <t>loviedom1528@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>13/03/2026</t>
+  </si>
+  <si>
+    <t>2000000</t>
+  </si>
+  <si>
+    <t>1680672</t>
+  </si>
+  <si>
+    <t>200000</t>
+  </si>
+  <si>
+    <t>1800000</t>
+  </si>
+  <si>
+    <t>2026-03-18T00:00:00</t>
+  </si>
+  <si>
+    <t>3871</t>
+  </si>
+  <si>
+    <t>4754760-1</t>
+  </si>
+  <si>
+    <t>OVIEDO MONSALVE LORENZO</t>
+  </si>
+  <si>
+    <t>14/11/1941</t>
+  </si>
+  <si>
+    <t>3872</t>
+  </si>
+  <si>
+    <t>12873671-9</t>
+  </si>
+  <si>
+    <t>GARRIDO OPAZO CLAUDIO ALEJANDRO</t>
+  </si>
+  <si>
+    <t>04/01/1975</t>
+  </si>
+  <si>
+    <t>2264 - Conchali - Santiago -CP</t>
+  </si>
+  <si>
+    <t>988387593</t>
+  </si>
+  <si>
+    <t>claudiogarridopazoo@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>3360000</t>
+  </si>
+  <si>
+    <t>2823529</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO FAMILIAR</t>
+  </si>
+  <si>
+    <t>3894</t>
+  </si>
+  <si>
+    <t>Valparaíso</t>
+  </si>
+  <si>
+    <t>7551634-7</t>
+  </si>
+  <si>
+    <t>GODOY HORMAZABAL FRANCISCO DELFIN</t>
+  </si>
+  <si>
+    <t>18/10/1957</t>
+  </si>
+  <si>
+    <t>Villa Alemana</t>
+  </si>
+  <si>
+    <t>2175 - Villa Alemana - Valparaíso -CP</t>
+  </si>
+  <si>
+    <t>975347802</t>
+  </si>
+  <si>
+    <t>panchogohor@hotmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t>HUMBERTO CRISTIAN BARBERIS AVENDAÑO</t>
+  </si>
+  <si>
+    <t>JACQUELINE DE LAS MERCEDES VASQUEZ  CASTRO</t>
+  </si>
+  <si>
+    <t>1512605</t>
+  </si>
+  <si>
+    <t>1600000</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>66667</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO RAICES DE VIDA LIBRE</t>
+  </si>
+  <si>
+    <t>3895</t>
+  </si>
+  <si>
+    <t>16068948-K</t>
+  </si>
+  <si>
+    <t>MEDINA ARMIJO LINO ANDRÉS</t>
+  </si>
+  <si>
+    <t>20/04/1985</t>
+  </si>
+  <si>
+    <t>Quintero</t>
+  </si>
+  <si>
+    <t>39 - Quintero - Valparaíso -CP</t>
+  </si>
+  <si>
+    <t>959734686</t>
+  </si>
+  <si>
+    <t>lino.medina.armijo@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>VERONICA MEDINA ARMIJO</t>
+  </si>
+  <si>
+    <t>1855000</t>
+  </si>
+  <si>
+    <t>1558824</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>SERVICIO FUNERARIO RAICES DE VIDA SOLUCIÓN TOTAL LIBRE</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>11415625-6</t>
+  </si>
+  <si>
+    <t>REBOLLEDO WECHSLER ROSE MARIE</t>
+  </si>
+  <si>
+    <t>23/05/1969</t>
+  </si>
+  <si>
+    <t>Providencia</t>
+  </si>
+  <si>
+    <t>157 - Providencia - Santiago -CP</t>
+  </si>
+  <si>
+    <t>996709222</t>
+  </si>
+  <si>
+    <t>lorerebolledow@gmail.com; ; ; ;</t>
+  </si>
+  <si>
+    <t>XIMENA DEL CARMEN LOPEZ ROZAS</t>
+  </si>
+  <si>
+    <t>180000</t>
+  </si>
+  <si>
+    <t>45000</t>
+  </si>
+  <si>
+    <t>3910</t>
+  </si>
+  <si>
+    <t>2521008</t>
+  </si>
+  <si>
+    <t>2600000</t>
+  </si>
+  <si>
     <t>ACTIVO PEND VALIDAR</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO RAICES DE VIDA ADULTO MAYOR</t>
-  </si>
-  <si>
-    <t>3738</t>
-  </si>
-  <si>
-    <t>1350000</t>
-  </si>
-  <si>
-    <t>1134454</t>
-  </si>
-  <si>
-    <t>270000</t>
-  </si>
-  <si>
-    <t>1080000</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO RAICES DE VIDA PERSONAL</t>
-  </si>
-  <si>
-    <t>PERSONAL</t>
-  </si>
-  <si>
-    <t>3739</t>
-  </si>
-  <si>
-    <t>8825803-7</t>
-  </si>
-  <si>
-    <t>DE LA FUENTE CELPA CAROLINA ELVIRA JACQUELINE</t>
-  </si>
-  <si>
-    <t>15/07/1964</t>
-  </si>
-  <si>
-    <t>Ñuñoa</t>
-  </si>
-  <si>
-    <t>401 - Ñuñoa - Santiago -CP</t>
-  </si>
-  <si>
-    <t>993176608</t>
-  </si>
-  <si>
-    <t>oyarzoquijada@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>26/02/2026</t>
-  </si>
-  <si>
-    <t>03/03/2026</t>
-  </si>
-  <si>
-    <t>1710000</t>
-  </si>
-  <si>
-    <t>1436975</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO SOLUCIÓN TOTAL PERSONAL</t>
-  </si>
-  <si>
-    <t>PERSONAL SOLUCIÓN TOTAL</t>
-  </si>
-  <si>
-    <t>3744</t>
-  </si>
-  <si>
-    <t>7880880-2</t>
-  </si>
-  <si>
-    <t>OYARZO QUIJADA SANTOS JAVIER</t>
-  </si>
-  <si>
-    <t>15/03/1960</t>
-  </si>
-  <si>
-    <t>3745</t>
-  </si>
-  <si>
-    <t>8854225-8</t>
-  </si>
-  <si>
-    <t>MÉNDEZ SEPÚLVEDA JOSÉ</t>
-  </si>
-  <si>
-    <t>10/12/1960</t>
-  </si>
-  <si>
-    <t>Peñalolén</t>
-  </si>
-  <si>
-    <t>6299 - Peñalolén - Santiago -CP</t>
-  </si>
-  <si>
-    <t>988251457</t>
-  </si>
-  <si>
-    <t>joseedelfin@hotmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>Camilo Jesus Medel Rojas</t>
-  </si>
-  <si>
-    <t>Luis Alberto Osores   Osores</t>
-  </si>
-  <si>
-    <t>3746</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>7950000</t>
-  </si>
-  <si>
-    <t>6680672</t>
-  </si>
-  <si>
-    <t>0.13</t>
-  </si>
-  <si>
-    <t>1060000</t>
-  </si>
-  <si>
-    <t>6890000</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>143542</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO SOLUCIÓN TOTAL SIEMPRE JUNTOS</t>
-  </si>
-  <si>
-    <t>SIEMPRE JUNTOS SOLUCIÓN TOTAL</t>
-  </si>
-  <si>
-    <t>3747</t>
-  </si>
-  <si>
-    <t>7563296-7</t>
-  </si>
-  <si>
-    <t>AYALA VILLARROEL NORMA DE LAS MERCEDES</t>
-  </si>
-  <si>
-    <t>11/11/1954</t>
-  </si>
-  <si>
-    <t>Quilicura</t>
-  </si>
-  <si>
-    <t>1093 - Quilicura - Santiago -CP</t>
-  </si>
-  <si>
-    <t>962053244</t>
-  </si>
-  <si>
-    <t>normaayala982@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>Francesca Nicole Sanchez pacheco</t>
-  </si>
-  <si>
-    <t>1440000</t>
-  </si>
-  <si>
-    <t>1210084</t>
-  </si>
-  <si>
-    <t>0.1</t>
-  </si>
-  <si>
-    <t>144000</t>
-  </si>
-  <si>
-    <t>1296000</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>27000</t>
-  </si>
-  <si>
-    <t>3751</t>
-  </si>
-  <si>
-    <t>5202611-3</t>
-  </si>
-  <si>
-    <t>PEREZ LAZO JUAN EUGENIO</t>
-  </si>
-  <si>
-    <t>06/02/1946</t>
-  </si>
-  <si>
-    <t>La Florida</t>
-  </si>
-  <si>
-    <t>6887 - La Florida - Santiago -CP</t>
-  </si>
-  <si>
-    <t>940660261</t>
-  </si>
-  <si>
-    <t>perezlazojuan46@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>04/03/2026</t>
-  </si>
-  <si>
-    <t>05/03/2026</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>3200000</t>
-  </si>
-  <si>
-    <t>2689076</t>
-  </si>
-  <si>
-    <t>0.31</t>
-  </si>
-  <si>
-    <t>1000000</t>
-  </si>
-  <si>
-    <t>2200000</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>440000</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO TESOROS DEL ALMA PERSONAL</t>
-  </si>
-  <si>
-    <t>3756</t>
-  </si>
-  <si>
-    <t>21589354-5</t>
-  </si>
-  <si>
-    <t>ORELLANA AVILA BELEN JESUS</t>
-  </si>
-  <si>
-    <t>21/10/1997</t>
-  </si>
-  <si>
-    <t>Huechuraba</t>
-  </si>
-  <si>
-    <t>591 - Huechuraba - Santiago -CP</t>
-  </si>
-  <si>
-    <t>979210576</t>
-  </si>
-  <si>
-    <t>belenorellana2424@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>HERLIZ DANIELA REQUENA GAMBOA</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>2850000</t>
-  </si>
-  <si>
-    <t>2394958</t>
-  </si>
-  <si>
-    <t>0.02</t>
-  </si>
-  <si>
-    <t>50000</t>
-  </si>
-  <si>
-    <t>2800000</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>59574</t>
-  </si>
-  <si>
-    <t>3765</t>
-  </si>
-  <si>
-    <t>11054685-8</t>
-  </si>
-  <si>
-    <t>MOLINA OLMEDO JENNY ELIZABETH</t>
-  </si>
-  <si>
-    <t>29/05/1966</t>
-  </si>
-  <si>
-    <t>760 - Puente Alto - Cordillera -CP</t>
-  </si>
-  <si>
-    <t>987395077</t>
-  </si>
-  <si>
-    <t>jennydelaconso@hotmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>2500000</t>
-  </si>
-  <si>
-    <t>2100840</t>
-  </si>
-  <si>
-    <t>250000</t>
-  </si>
-  <si>
-    <t>2250000</t>
-  </si>
-  <si>
-    <t>62500</t>
-  </si>
-  <si>
-    <t>3767</t>
-  </si>
-  <si>
-    <t>9806863-5</t>
-  </si>
-  <si>
-    <t>CARDENAS MARTINEZ CECILIA OLGA</t>
-  </si>
-  <si>
-    <t>03/09/1963</t>
-  </si>
-  <si>
-    <t>San Ramón</t>
-  </si>
-  <si>
-    <t>9770 - San Ramón - Santiago -CP</t>
-  </si>
-  <si>
-    <t>971074760</t>
-  </si>
-  <si>
-    <t>ceciliacarmar@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>1320000</t>
-  </si>
-  <si>
-    <t>1109244</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO PERSONAL</t>
-  </si>
-  <si>
-    <t>3768</t>
-  </si>
-  <si>
-    <t>17487955-9</t>
-  </si>
-  <si>
-    <t>PIZARRO ROMERO BETZABE ALEJANDRA</t>
-  </si>
-  <si>
-    <t>04/09/1990</t>
-  </si>
-  <si>
-    <t>Maipú</t>
-  </si>
-  <si>
-    <t>2328 - Maipú - Santiago -CP</t>
-  </si>
-  <si>
-    <t>988146014</t>
-  </si>
-  <si>
-    <t>b.pizarro.romero@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>Alejandra Edith Otelo Zuñiga</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>2565000</t>
-  </si>
-  <si>
-    <t>2155462</t>
-  </si>
-  <si>
-    <t>256500</t>
-  </si>
-  <si>
-    <t>2308500</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>96188</t>
-  </si>
-  <si>
-    <t>3777</t>
-  </si>
-  <si>
-    <t>9603079-7</t>
-  </si>
-  <si>
-    <t>SEPULVEDA DIAZ PATRICIO EUGENIO</t>
-  </si>
-  <si>
-    <t>01/04/1964</t>
-  </si>
-  <si>
-    <t>Conchali</t>
-  </si>
-  <si>
-    <t>1337 - Conchali - Santiago -CP</t>
-  </si>
-  <si>
-    <t>982949955</t>
-  </si>
-  <si>
-    <t>psepulveda64@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>3100000</t>
-  </si>
-  <si>
-    <t>2605042</t>
-  </si>
-  <si>
-    <t>0.11</t>
-  </si>
-  <si>
-    <t>350000</t>
-  </si>
-  <si>
-    <t>2750000</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>45833</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO SOLUCIÓN TOTAL LIBRE</t>
-  </si>
-  <si>
-    <t>LIBRE SOLUCIÓN TOTAL</t>
-  </si>
-  <si>
-    <t>3781</t>
-  </si>
-  <si>
-    <t>4237433-4</t>
-  </si>
-  <si>
-    <t>ARAYA PEREZ GLADYS HEYDÉE</t>
-  </si>
-  <si>
-    <t>28/12/1941</t>
-  </si>
-  <si>
-    <t>Macul</t>
-  </si>
-  <si>
-    <t>2240 - Macul - Santiago -CP</t>
-  </si>
-  <si>
-    <t>994005973</t>
-  </si>
-  <si>
-    <t>GLADYSARAYAPEREZ@GMAIL.COM; ; ; ;</t>
-  </si>
-  <si>
-    <t>2700000</t>
-  </si>
-  <si>
-    <t>2268908</t>
-  </si>
-  <si>
-    <t>300000</t>
-  </si>
-  <si>
-    <t>2400000</t>
-  </si>
-  <si>
-    <t>3784</t>
-  </si>
-  <si>
-    <t>13265271-6</t>
-  </si>
-  <si>
-    <t>CARIMAN MUNOZ PAOLA ALEJANDRA</t>
-  </si>
-  <si>
-    <t>19/04/1977</t>
-  </si>
-  <si>
-    <t>1362 - Maipú - Santiago -CP</t>
-  </si>
-  <si>
-    <t>973465528</t>
-  </si>
-  <si>
-    <t>paola.cariman@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>3150000</t>
-  </si>
-  <si>
-    <t>2647059</t>
-  </si>
-  <si>
-    <t>59375</t>
-  </si>
-  <si>
-    <t>3792</t>
-  </si>
-  <si>
-    <t>13682451-1</t>
-  </si>
-  <si>
-    <t>CARIMAN MUNOZ VERONICA CECILIA</t>
-  </si>
-  <si>
-    <t>27/07/1979</t>
-  </si>
-  <si>
-    <t>veronica.cariman@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>3450000</t>
-  </si>
-  <si>
-    <t>2899160</t>
-  </si>
-  <si>
-    <t>72000</t>
-  </si>
-  <si>
-    <t>3378000</t>
-  </si>
-  <si>
-    <t>71872</t>
-  </si>
-  <si>
-    <t>3794</t>
-  </si>
-  <si>
-    <t>17769780-K</t>
-  </si>
-  <si>
-    <t>HERNANDEZ PONCE PATRICIA CAROLINA</t>
-  </si>
-  <si>
-    <t>22/05/1991</t>
-  </si>
-  <si>
-    <t>Quinta Normal</t>
-  </si>
-  <si>
-    <t>2499 - Quinta Normal - Santiago -CP</t>
-  </si>
-  <si>
-    <t>974956288</t>
-  </si>
-  <si>
-    <t>patricia.carolinahp@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>07/03/2026</t>
-  </si>
-  <si>
-    <t>2352941</t>
-  </si>
-  <si>
-    <t>53000</t>
-  </si>
-  <si>
-    <t>2747000</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>58447</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO LIBRE</t>
-  </si>
-  <si>
-    <t>LIBRE</t>
-  </si>
-  <si>
-    <t>3800</t>
-  </si>
-  <si>
-    <t>10551410-7</t>
-  </si>
-  <si>
-    <t>HIDALGO VALDENEGRO MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>12/07/1965</t>
-  </si>
-  <si>
-    <t>31 - Puente Alto - Cordillera -CP</t>
-  </si>
-  <si>
-    <t>986113609</t>
-  </si>
-  <si>
-    <t>marcohidalgov087@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>Daniela Andrea Rivera  Hurtado</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>2550000</t>
-  </si>
-  <si>
-    <t>2142857</t>
-  </si>
-  <si>
-    <t>0.05</t>
-  </si>
-  <si>
-    <t>135000</t>
-  </si>
-  <si>
-    <t>2415000</t>
-  </si>
-  <si>
-    <t>33542</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO RAICES DE VIDA FAMILIAR</t>
-  </si>
-  <si>
-    <t>FAMILIAR</t>
-  </si>
-  <si>
-    <t>3802</t>
-  </si>
-  <si>
-    <t>10170200-6</t>
-  </si>
-  <si>
-    <t>MUÑOZ ZAMORA ANA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>29/07/1966</t>
-  </si>
-  <si>
-    <t>Lampa</t>
-  </si>
-  <si>
-    <t>923 - Lampa - Chacabuco -CP</t>
-  </si>
-  <si>
-    <t>979628954</t>
-  </si>
-  <si>
-    <t>22081986jeannette@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>VIVIANA HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ALEJANDRA VERDUGO</t>
-  </si>
-  <si>
-    <t>1875000</t>
-  </si>
-  <si>
-    <t>1575630</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>3818</t>
-  </si>
-  <si>
-    <t>10774061-9</t>
-  </si>
-  <si>
-    <t>MARTINEZ RIFFO RICHARD OMAR</t>
-  </si>
-  <si>
-    <t>20/01/1967</t>
-  </si>
-  <si>
-    <t>33 - Puente Alto - Cordillera -CP</t>
-  </si>
-  <si>
-    <t>946874213</t>
-  </si>
-  <si>
-    <t>ecommerce.richardmartinez11@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>1620000</t>
-  </si>
-  <si>
-    <t>1361345</t>
-  </si>
-  <si>
-    <t>0.09</t>
-  </si>
-  <si>
-    <t>1476000</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>6583103-1</t>
-  </si>
-  <si>
-    <t>VILCHES VILLALOBOS PEDRO</t>
-  </si>
-  <si>
-    <t>18/06/1952</t>
-  </si>
-  <si>
-    <t>1560 - Puente Alto - Cordillera -CP</t>
-  </si>
-  <si>
-    <t>956788731</t>
-  </si>
-  <si>
-    <t>vilches882018@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>2137500</t>
-  </si>
-  <si>
-    <t>1796218</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO RAICES DE VIDA SOLUCIÓN TOTAL ADULTO MAYOR</t>
-  </si>
-  <si>
-    <t>3823</t>
-  </si>
-  <si>
-    <t>3824</t>
-  </si>
-  <si>
-    <t>5386701-4</t>
-  </si>
-  <si>
-    <t>AGUIRRE RODRIGUEZ MARTA ALIANA</t>
-  </si>
-  <si>
-    <t>21/12/1940</t>
-  </si>
-  <si>
-    <t>San Bernardo</t>
-  </si>
-  <si>
-    <t>991 - San Bernardo - Maipo -CP</t>
-  </si>
-  <si>
-    <t>983516789</t>
-  </si>
-  <si>
-    <t>maguirrero@hotmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>08/03/2026</t>
-  </si>
-  <si>
-    <t>10/03/2026</t>
-  </si>
-  <si>
-    <t>NELSON RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>3400000</t>
-  </si>
-  <si>
-    <t>2857143</t>
-  </si>
-  <si>
-    <t>400000</t>
-  </si>
-  <si>
-    <t>3000000</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO TESOROS DEL ALMA ADULTO MAYOR</t>
-  </si>
-  <si>
-    <t>3828</t>
-  </si>
-  <si>
-    <t>3927346-2</t>
-  </si>
-  <si>
-    <t>PIÑA ZAVALA HUMBERTO ARTURO</t>
-  </si>
-  <si>
-    <t>12/06/1938</t>
-  </si>
-  <si>
-    <t>961116221</t>
-  </si>
-  <si>
-    <t>humbertopina@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>3829</t>
-  </si>
-  <si>
-    <t>17241987-9</t>
-  </si>
-  <si>
-    <t>SALINAS SALINAS CAMILO ANDRES</t>
-  </si>
-  <si>
-    <t>04/03/1989</t>
-  </si>
-  <si>
-    <t>Santiago</t>
-  </si>
-  <si>
-    <t>580 - Santiago - Santiago -CP</t>
-  </si>
-  <si>
-    <t>949508704</t>
-  </si>
-  <si>
-    <t>camilo.salinas89@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>GABRIELA DEL CARMEN ROJAS QUEZADA</t>
-  </si>
-  <si>
-    <t>Margarita Cristina Rojas Quezada</t>
-  </si>
-  <si>
-    <t>2511562</t>
-  </si>
-  <si>
-    <t>53438</t>
-  </si>
-  <si>
-    <t>3832</t>
-  </si>
-  <si>
-    <t>8429029-7</t>
-  </si>
-  <si>
-    <t>LOPEZ CERDA GLORIA ANGELICA</t>
-  </si>
-  <si>
-    <t>09/12/1959</t>
-  </si>
-  <si>
-    <t>1323 - Lampa - Chacabuco -CP</t>
-  </si>
-  <si>
-    <t>986729324</t>
-  </si>
-  <si>
-    <t>diegorlando.lopez212@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>RODRIGO IGNACIO CASTRO FIGUEROA</t>
-  </si>
-  <si>
-    <t>162000</t>
-  </si>
-  <si>
-    <t>1458000</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>121500</t>
-  </si>
-  <si>
-    <t>SUCURSAL</t>
-  </si>
-  <si>
-    <t>3833</t>
-  </si>
-  <si>
-    <t>11127146-1</t>
-  </si>
-  <si>
-    <t>BRAVO MIRANDA ORIANA ALEJANDRINA</t>
-  </si>
-  <si>
-    <t>24/11/1967</t>
-  </si>
-  <si>
-    <t>337 - Puente Alto - Cordillera -CP</t>
-  </si>
-  <si>
-    <t>949101444</t>
-  </si>
-  <si>
-    <t>ivanbananas23@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>11/03/2026</t>
-  </si>
-  <si>
-    <t>2650000</t>
-  </si>
-  <si>
-    <t>2226891</t>
-  </si>
-  <si>
-    <t>40000</t>
-  </si>
-  <si>
-    <t>3841</t>
-  </si>
-  <si>
-    <t>8176900-1</t>
-  </si>
-  <si>
-    <t>ZUÑIGA GALLARDO IVAN ARTURO</t>
-  </si>
-  <si>
-    <t>10/05/1968</t>
-  </si>
-  <si>
-    <t>3377 - Puente Alto - Cordillera -CP</t>
-  </si>
-  <si>
-    <t>986920954</t>
-  </si>
-  <si>
-    <t>3842</t>
-  </si>
-  <si>
-    <t>10033214-0</t>
-  </si>
-  <si>
-    <t>MENDOZA ORDENES ENNA ELIZABETH</t>
-  </si>
-  <si>
-    <t>21/08/1963</t>
-  </si>
-  <si>
-    <t>24 - Quilicura - Santiago -CP</t>
-  </si>
-  <si>
-    <t>949464419</t>
-  </si>
-  <si>
-    <t>KATHERINSOTOGARRIDO@GMAIL.COM; ; ; ;</t>
-  </si>
-  <si>
-    <t>Fernanda Scarlet Cuevas Olivares</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>3844</t>
-  </si>
-  <si>
-    <t>12478544-8</t>
-  </si>
-  <si>
-    <t>PUGA MENDEZ CLAUDIO ALEJANDRO</t>
-  </si>
-  <si>
-    <t>11/11/1971</t>
-  </si>
-  <si>
-    <t>260 - Quilicura - Santiago -CP</t>
-  </si>
-  <si>
-    <t>994361654</t>
-  </si>
-  <si>
-    <t>CPUGA1971@GMAIL.COM; ; ; ;</t>
-  </si>
-  <si>
-    <t>Marcela Antonia  Valdés  Barrios</t>
-  </si>
-  <si>
-    <t>4400000</t>
-  </si>
-  <si>
-    <t>3697479</t>
-  </si>
-  <si>
-    <t>444000</t>
-  </si>
-  <si>
-    <t>3956000</t>
-  </si>
-  <si>
-    <t>65933</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO SOLUCIÓN TOTAL FAMILIAR</t>
-  </si>
-  <si>
-    <t>FAMILIAR SOLUCIÓN TOTAL</t>
-  </si>
-  <si>
-    <t>3846</t>
-  </si>
-  <si>
-    <t>20944439-9</t>
-  </si>
-  <si>
-    <t>VALDES BARRIOS MARCELA ANTONIA</t>
-  </si>
-  <si>
-    <t>28/12/2001</t>
-  </si>
-  <si>
-    <t>313 - Quilicura - Santiago -CP</t>
-  </si>
-  <si>
-    <t>940987799</t>
-  </si>
-  <si>
-    <t>antovaldes327@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>12/03/2026</t>
-  </si>
-  <si>
-    <t>14/03/2026</t>
-  </si>
-  <si>
-    <t>1848739</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>1100000</t>
-  </si>
-  <si>
-    <t>INACTIVO</t>
-  </si>
-  <si>
-    <t>2026-03-17T00:00:00</t>
-  </si>
-  <si>
-    <t>3868</t>
-  </si>
-  <si>
-    <t>4413981-2</t>
-  </si>
-  <si>
-    <t>SEPULVEDA PEREZ NOEMI</t>
-  </si>
-  <si>
-    <t>07/11/1935</t>
-  </si>
-  <si>
-    <t>1528 - Puente Alto - Cordillera -CP</t>
-  </si>
-  <si>
-    <t>965902208</t>
-  </si>
-  <si>
-    <t>loviedom1528@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>13/03/2026</t>
-  </si>
-  <si>
-    <t>2000000</t>
-  </si>
-  <si>
-    <t>1680672</t>
-  </si>
-  <si>
-    <t>200000</t>
-  </si>
-  <si>
-    <t>1800000</t>
-  </si>
-  <si>
-    <t>2026-03-18T00:00:00</t>
-  </si>
-  <si>
-    <t>3871</t>
-  </si>
-  <si>
-    <t>4754760-1</t>
-  </si>
-  <si>
-    <t>OVIEDO MONSALVE LORENZO</t>
-  </si>
-  <si>
-    <t>14/11/1941</t>
-  </si>
-  <si>
-    <t>3872</t>
-  </si>
-  <si>
-    <t>12873671-9</t>
-  </si>
-  <si>
-    <t>GARRIDO OPAZO CLAUDIO ALEJANDRO</t>
-  </si>
-  <si>
-    <t>04/01/1975</t>
-  </si>
-  <si>
-    <t>2264 - Conchali - Santiago -CP</t>
-  </si>
-  <si>
-    <t>988387593</t>
-  </si>
-  <si>
-    <t>claudiogarridopazoo@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>16/03/2026</t>
-  </si>
-  <si>
-    <t>3360000</t>
-  </si>
-  <si>
-    <t>2823529</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO SEMILLAS DE LEGADO FAMILIAR</t>
-  </si>
-  <si>
-    <t>3894</t>
-  </si>
-  <si>
-    <t>Valparaíso</t>
-  </si>
-  <si>
-    <t>7551634-7</t>
-  </si>
-  <si>
-    <t>GODOY HORMAZABAL FRANCISCO DELFIN</t>
-  </si>
-  <si>
-    <t>18/10/1957</t>
-  </si>
-  <si>
-    <t>Villa Alemana</t>
-  </si>
-  <si>
-    <t>2175 - Villa Alemana - Valparaíso -CP</t>
-  </si>
-  <si>
-    <t>975347802</t>
-  </si>
-  <si>
-    <t>panchogohor@hotmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>17/03/2026</t>
-  </si>
-  <si>
-    <t>HUMBERTO CRISTIAN BARBERIS AVENDAÑO</t>
-  </si>
-  <si>
-    <t>JACQUELINE DE LAS MERCEDES VASQUEZ  CASTRO</t>
-  </si>
-  <si>
-    <t>1512605</t>
-  </si>
-  <si>
-    <t>1600000</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>66667</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO RAICES DE VIDA LIBRE</t>
-  </si>
-  <si>
-    <t>3895</t>
-  </si>
-  <si>
-    <t>16068948-K</t>
-  </si>
-  <si>
-    <t>MEDINA ARMIJO LINO ANDRÉS</t>
-  </si>
-  <si>
-    <t>20/04/1985</t>
-  </si>
-  <si>
-    <t>Quintero</t>
-  </si>
-  <si>
-    <t>39 - Quintero - Valparaíso -CP</t>
-  </si>
-  <si>
-    <t>959734686</t>
-  </si>
-  <si>
-    <t>lino.medina.armijo@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>VERONICA MEDINA ARMIJO</t>
-  </si>
-  <si>
-    <t>1855000</t>
-  </si>
-  <si>
-    <t>1558824</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>SERVICIO FUNERARIO RAICES DE VIDA SOLUCIÓN TOTAL LIBRE</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>11415625-6</t>
-  </si>
-  <si>
-    <t>REBOLLEDO WECHSLER ROSE MARIE</t>
-  </si>
-  <si>
-    <t>23/05/1969</t>
-  </si>
-  <si>
-    <t>Providencia</t>
-  </si>
-  <si>
-    <t>157 - Providencia - Santiago -CP</t>
-  </si>
-  <si>
-    <t>996709222</t>
-  </si>
-  <si>
-    <t>lorerebolledow@gmail.com; ; ; ;</t>
-  </si>
-  <si>
-    <t>XIMENA DEL CARMEN LOPEZ ROZAS</t>
-  </si>
-  <si>
-    <t>180000</t>
-  </si>
-  <si>
-    <t>45000</t>
-  </si>
-  <si>
-    <t>3910</t>
-  </si>
-  <si>
-    <t>2521008</t>
-  </si>
-  <si>
-    <t>2600000</t>
   </si>
   <si>
     <t>3912</t>
@@ -3787,10 +3787,10 @@
         <v>102</v>
       </c>
       <c r="AC4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD4" t="s">
         <v>103</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>104</v>
       </c>
       <c r="AE4" t="s">
         <v>84</v>
@@ -3826,7 +3826,7 @@
         <v>49</v>
       </c>
       <c r="AP4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.3">
@@ -3882,13 +3882,13 @@
         <v>95</v>
       </c>
       <c r="R5" t="s">
+        <v>105</v>
+      </c>
+      <c r="S5" t="s">
+        <v>49</v>
+      </c>
+      <c r="T5" t="s">
         <v>106</v>
-      </c>
-      <c r="S5" t="s">
-        <v>49</v>
-      </c>
-      <c r="T5" t="s">
-        <v>107</v>
       </c>
       <c r="U5" t="s">
         <v>57</v>
@@ -3900,28 +3900,28 @@
         <v>98</v>
       </c>
       <c r="X5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Y5" t="s">
         <v>52</v>
       </c>
       <c r="Z5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA5" t="s">
         <v>101</v>
       </c>
       <c r="AB5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD5" t="s">
         <v>110</v>
       </c>
-      <c r="AC5" t="s">
-        <v>103</v>
-      </c>
-      <c r="AD5" t="s">
+      <c r="AE5" t="s">
         <v>111</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>112</v>
       </c>
       <c r="AF5" t="s">
         <v>65</v>
@@ -3954,7 +3954,7 @@
         <v>49</v>
       </c>
       <c r="AP5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.3">
@@ -3965,34 +3965,34 @@
         <v>43</v>
       </c>
       <c r="C6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" t="s">
         <v>114</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>115</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>116</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>117</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>118</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J6" t="s">
         <v>119</v>
       </c>
-      <c r="I6" t="s">
-        <v>119</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>120</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>121</v>
-      </c>
-      <c r="L6" t="s">
-        <v>122</v>
       </c>
       <c r="M6" t="s">
         <v>53</v>
@@ -4010,13 +4010,13 @@
         <v>57</v>
       </c>
       <c r="R6" t="s">
+        <v>122</v>
+      </c>
+      <c r="S6" t="s">
+        <v>49</v>
+      </c>
+      <c r="T6" t="s">
         <v>123</v>
-      </c>
-      <c r="S6" t="s">
-        <v>49</v>
-      </c>
-      <c r="T6" t="s">
-        <v>124</v>
       </c>
       <c r="U6" t="s">
         <v>57</v>
@@ -4028,28 +4028,28 @@
         <v>60</v>
       </c>
       <c r="X6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y6" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AB6" t="s">
         <v>122</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>125</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>123</v>
       </c>
       <c r="AC6" t="s">
         <v>62</v>
       </c>
       <c r="AD6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE6" t="s">
         <v>126</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>127</v>
       </c>
       <c r="AF6" t="s">
         <v>65</v>
@@ -4082,7 +4082,7 @@
         <v>49</v>
       </c>
       <c r="AP6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.3">
@@ -4093,34 +4093,34 @@
         <v>43</v>
       </c>
       <c r="C7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" t="s">
         <v>129</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>130</v>
       </c>
-      <c r="E7" t="s">
-        <v>131</v>
-      </c>
       <c r="F7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G7" t="s">
         <v>117</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>118</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
+        <v>118</v>
+      </c>
+      <c r="J7" t="s">
         <v>119</v>
       </c>
-      <c r="I7" t="s">
-        <v>119</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>120</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>121</v>
-      </c>
-      <c r="L7" t="s">
-        <v>122</v>
       </c>
       <c r="M7" t="s">
         <v>53</v>
@@ -4138,13 +4138,13 @@
         <v>57</v>
       </c>
       <c r="R7" t="s">
+        <v>122</v>
+      </c>
+      <c r="S7" t="s">
+        <v>49</v>
+      </c>
+      <c r="T7" t="s">
         <v>123</v>
-      </c>
-      <c r="S7" t="s">
-        <v>49</v>
-      </c>
-      <c r="T7" t="s">
-        <v>124</v>
       </c>
       <c r="U7" t="s">
         <v>57</v>
@@ -4156,28 +4156,28 @@
         <v>60</v>
       </c>
       <c r="X7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y7" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>124</v>
+      </c>
+      <c r="AB7" t="s">
         <v>122</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>125</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>123</v>
       </c>
       <c r="AC7" t="s">
         <v>62</v>
       </c>
       <c r="AD7" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE7" t="s">
         <v>126</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>127</v>
       </c>
       <c r="AF7" t="s">
         <v>65</v>
@@ -4210,7 +4210,7 @@
         <v>49</v>
       </c>
       <c r="AP7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.3">
@@ -4221,34 +4221,34 @@
         <v>43</v>
       </c>
       <c r="C8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" t="s">
         <v>133</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>134</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>135</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>136</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>137</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
+        <v>137</v>
+      </c>
+      <c r="J8" t="s">
         <v>138</v>
       </c>
-      <c r="I8" t="s">
-        <v>138</v>
-      </c>
-      <c r="J8" t="s">
-        <v>139</v>
-      </c>
       <c r="K8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M8" t="s">
         <v>53</v>
@@ -4257,10 +4257,10 @@
         <v>54</v>
       </c>
       <c r="O8" t="s">
+        <v>139</v>
+      </c>
+      <c r="P8" t="s">
         <v>140</v>
-      </c>
-      <c r="P8" t="s">
-        <v>141</v>
       </c>
       <c r="Q8" t="s">
         <v>57</v>
@@ -4287,13 +4287,13 @@
         <v>96</v>
       </c>
       <c r="Y8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Z8" t="s">
         <v>49</v>
       </c>
       <c r="AA8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AB8" t="s">
         <v>96</v>
@@ -4302,7 +4302,7 @@
         <v>62</v>
       </c>
       <c r="AD8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AE8" t="s">
         <v>84</v>
@@ -4338,7 +4338,7 @@
         <v>49</v>
       </c>
       <c r="AP8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.3">
@@ -4349,34 +4349,34 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" t="s">
         <v>133</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>134</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>135</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>136</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>137</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
+        <v>137</v>
+      </c>
+      <c r="J9" t="s">
         <v>138</v>
       </c>
-      <c r="I9" t="s">
-        <v>138</v>
-      </c>
-      <c r="J9" t="s">
-        <v>139</v>
-      </c>
       <c r="K9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M9" t="s">
         <v>53</v>
@@ -4385,55 +4385,55 @@
         <v>54</v>
       </c>
       <c r="O9" t="s">
+        <v>139</v>
+      </c>
+      <c r="P9" t="s">
         <v>140</v>
       </c>
-      <c r="P9" t="s">
-        <v>141</v>
-      </c>
       <c r="Q9" t="s">
+        <v>142</v>
+      </c>
+      <c r="R9" t="s">
         <v>143</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
+        <v>49</v>
+      </c>
+      <c r="T9" t="s">
         <v>144</v>
       </c>
-      <c r="S9" t="s">
-        <v>49</v>
-      </c>
-      <c r="T9" t="s">
+      <c r="U9" t="s">
+        <v>57</v>
+      </c>
+      <c r="V9" t="s">
+        <v>57</v>
+      </c>
+      <c r="W9" t="s">
         <v>145</v>
       </c>
-      <c r="U9" t="s">
-        <v>57</v>
-      </c>
-      <c r="V9" t="s">
-        <v>57</v>
-      </c>
-      <c r="W9" t="s">
+      <c r="X9" t="s">
         <v>146</v>
       </c>
-      <c r="X9" t="s">
+      <c r="Y9" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z9" t="s">
         <v>147</v>
       </c>
-      <c r="Y9" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z9" t="s">
+      <c r="AA9" t="s">
         <v>148</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AB9" t="s">
         <v>149</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>150</v>
       </c>
       <c r="AC9" t="s">
         <v>62</v>
       </c>
       <c r="AD9" t="s">
+        <v>150</v>
+      </c>
+      <c r="AE9" t="s">
         <v>151</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>152</v>
       </c>
       <c r="AF9" t="s">
         <v>65</v>
@@ -4466,7 +4466,7 @@
         <v>49</v>
       </c>
       <c r="AP9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.3">
@@ -4477,28 +4477,28 @@
         <v>43</v>
       </c>
       <c r="C10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10" t="s">
         <v>154</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>155</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>156</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>157</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>158</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
+        <v>158</v>
+      </c>
+      <c r="J10" t="s">
         <v>159</v>
-      </c>
-      <c r="I10" t="s">
-        <v>159</v>
-      </c>
-      <c r="J10" t="s">
-        <v>160</v>
       </c>
       <c r="K10" t="s">
         <v>52</v>
@@ -4513,55 +4513,55 @@
         <v>54</v>
       </c>
       <c r="O10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P10" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>142</v>
+      </c>
+      <c r="R10" t="s">
         <v>161</v>
       </c>
-      <c r="Q10" t="s">
-        <v>143</v>
-      </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
+        <v>49</v>
+      </c>
+      <c r="T10" t="s">
         <v>162</v>
       </c>
-      <c r="S10" t="s">
-        <v>49</v>
-      </c>
-      <c r="T10" t="s">
+      <c r="U10" t="s">
+        <v>57</v>
+      </c>
+      <c r="V10" t="s">
+        <v>57</v>
+      </c>
+      <c r="W10" t="s">
         <v>163</v>
       </c>
-      <c r="U10" t="s">
-        <v>57</v>
-      </c>
-      <c r="V10" t="s">
-        <v>57</v>
-      </c>
-      <c r="W10" t="s">
+      <c r="X10" t="s">
         <v>164</v>
-      </c>
-      <c r="X10" t="s">
-        <v>165</v>
       </c>
       <c r="Y10" t="s">
         <v>52</v>
       </c>
       <c r="Z10" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA10" t="s">
         <v>166</v>
       </c>
-      <c r="AA10" t="s">
+      <c r="AB10" t="s">
         <v>167</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>168</v>
       </c>
       <c r="AC10" t="s">
         <v>62</v>
       </c>
       <c r="AD10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE10" t="s">
         <v>111</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>112</v>
       </c>
       <c r="AF10" t="s">
         <v>65</v>
@@ -4594,7 +4594,7 @@
         <v>49</v>
       </c>
       <c r="AP10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.3">
@@ -4605,34 +4605,34 @@
         <v>43</v>
       </c>
       <c r="C11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D11" t="s">
         <v>170</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>171</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>172</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>173</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" t="s">
         <v>174</v>
       </c>
-      <c r="H11" t="s">
-        <v>49</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>175</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>176</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>177</v>
-      </c>
-      <c r="L11" t="s">
-        <v>178</v>
       </c>
       <c r="M11" t="s">
         <v>53</v>
@@ -4647,49 +4647,49 @@
         <v>94</v>
       </c>
       <c r="Q11" t="s">
+        <v>178</v>
+      </c>
+      <c r="R11" t="s">
         <v>179</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T11" t="s">
         <v>180</v>
       </c>
-      <c r="S11" t="s">
-        <v>49</v>
-      </c>
-      <c r="T11" t="s">
+      <c r="U11" t="s">
+        <v>57</v>
+      </c>
+      <c r="V11" t="s">
+        <v>57</v>
+      </c>
+      <c r="W11" t="s">
         <v>181</v>
       </c>
-      <c r="U11" t="s">
-        <v>57</v>
-      </c>
-      <c r="V11" t="s">
-        <v>57</v>
-      </c>
-      <c r="W11" t="s">
+      <c r="X11" t="s">
         <v>182</v>
       </c>
-      <c r="X11" t="s">
+      <c r="Y11" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z11" t="s">
         <v>183</v>
       </c>
-      <c r="Y11" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z11" t="s">
+      <c r="AA11" t="s">
         <v>184</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="AB11" t="s">
         <v>185</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>186</v>
       </c>
       <c r="AC11" t="s">
         <v>62</v>
       </c>
       <c r="AD11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AE11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF11" t="s">
         <v>65</v>
@@ -4722,7 +4722,7 @@
         <v>49</v>
       </c>
       <c r="AP11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.3">
@@ -4733,34 +4733,34 @@
         <v>43</v>
       </c>
       <c r="C12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" t="s">
         <v>189</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>190</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>191</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>192</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" t="s">
         <v>193</v>
       </c>
-      <c r="H12" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>194</v>
       </c>
-      <c r="J12" t="s">
-        <v>195</v>
-      </c>
       <c r="K12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M12" t="s">
         <v>53</v>
@@ -4772,52 +4772,52 @@
         <v>55</v>
       </c>
       <c r="P12" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q12" t="s">
         <v>196</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>197</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
+        <v>49</v>
+      </c>
+      <c r="T12" t="s">
         <v>198</v>
       </c>
-      <c r="S12" t="s">
-        <v>49</v>
-      </c>
-      <c r="T12" t="s">
+      <c r="U12" t="s">
+        <v>57</v>
+      </c>
+      <c r="V12" t="s">
+        <v>57</v>
+      </c>
+      <c r="W12" t="s">
         <v>199</v>
       </c>
-      <c r="U12" t="s">
-        <v>57</v>
-      </c>
-      <c r="V12" t="s">
-        <v>57</v>
-      </c>
-      <c r="W12" t="s">
+      <c r="X12" t="s">
         <v>200</v>
       </c>
-      <c r="X12" t="s">
+      <c r="Y12" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z12" t="s">
         <v>201</v>
       </c>
-      <c r="Y12" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z12" t="s">
+      <c r="AA12" t="s">
         <v>202</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AB12" t="s">
         <v>203</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>204</v>
       </c>
       <c r="AC12" t="s">
         <v>62</v>
       </c>
       <c r="AD12" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE12" t="s">
         <v>126</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>127</v>
       </c>
       <c r="AF12" t="s">
         <v>65</v>
@@ -4850,7 +4850,7 @@
         <v>49</v>
       </c>
       <c r="AP12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.3">
@@ -4861,34 +4861,34 @@
         <v>43</v>
       </c>
       <c r="C13" t="s">
+        <v>205</v>
+      </c>
+      <c r="D13" t="s">
         <v>206</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>207</v>
-      </c>
-      <c r="E13" t="s">
-        <v>208</v>
       </c>
       <c r="F13" t="s">
         <v>89</v>
       </c>
       <c r="G13" t="s">
+        <v>208</v>
+      </c>
+      <c r="H13" t="s">
         <v>209</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
+        <v>209</v>
+      </c>
+      <c r="J13" t="s">
         <v>210</v>
       </c>
-      <c r="I13" t="s">
-        <v>210</v>
-      </c>
-      <c r="J13" t="s">
-        <v>211</v>
-      </c>
       <c r="K13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M13" t="s">
         <v>53</v>
@@ -4903,40 +4903,40 @@
         <v>75</v>
       </c>
       <c r="Q13" t="s">
+        <v>211</v>
+      </c>
+      <c r="R13" t="s">
         <v>212</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
+        <v>49</v>
+      </c>
+      <c r="T13" t="s">
         <v>213</v>
       </c>
-      <c r="S13" t="s">
-        <v>49</v>
-      </c>
-      <c r="T13" t="s">
+      <c r="U13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V13" t="s">
+        <v>57</v>
+      </c>
+      <c r="W13" t="s">
+        <v>163</v>
+      </c>
+      <c r="X13" t="s">
         <v>214</v>
       </c>
-      <c r="U13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V13" t="s">
-        <v>57</v>
-      </c>
-      <c r="W13" t="s">
-        <v>164</v>
-      </c>
-      <c r="X13" t="s">
+      <c r="Y13" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z13" t="s">
         <v>215</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="AA13" t="s">
         <v>178</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="AB13" t="s">
         <v>216</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>217</v>
       </c>
       <c r="AC13" t="s">
         <v>62</v>
@@ -4978,7 +4978,7 @@
         <v>49</v>
       </c>
       <c r="AP13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.3">
@@ -4989,34 +4989,34 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
+        <v>218</v>
+      </c>
+      <c r="D14" t="s">
         <v>219</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>220</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>221</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>222</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" t="s">
         <v>223</v>
       </c>
-      <c r="H14" t="s">
-        <v>49</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>224</v>
-      </c>
-      <c r="J14" t="s">
-        <v>225</v>
       </c>
       <c r="K14" t="s">
         <v>52</v>
       </c>
       <c r="L14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M14" t="s">
         <v>53</v>
@@ -5031,16 +5031,16 @@
         <v>94</v>
       </c>
       <c r="Q14" t="s">
+        <v>226</v>
+      </c>
+      <c r="R14" t="s">
         <v>227</v>
       </c>
-      <c r="R14" t="s">
+      <c r="S14" t="s">
+        <v>49</v>
+      </c>
+      <c r="T14" t="s">
         <v>228</v>
-      </c>
-      <c r="S14" t="s">
-        <v>49</v>
-      </c>
-      <c r="T14" t="s">
-        <v>229</v>
       </c>
       <c r="U14" t="s">
         <v>57</v>
@@ -5052,28 +5052,28 @@
         <v>60</v>
       </c>
       <c r="X14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AA14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AC14" t="s">
         <v>62</v>
       </c>
       <c r="AD14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AE14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF14" t="s">
         <v>65</v>
@@ -5106,7 +5106,7 @@
         <v>49</v>
       </c>
       <c r="AP14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.3">
@@ -5117,34 +5117,34 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
+        <v>232</v>
+      </c>
+      <c r="D15" t="s">
         <v>233</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>234</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>235</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>236</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" t="s">
         <v>237</v>
       </c>
-      <c r="H15" t="s">
-        <v>49</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>238</v>
       </c>
-      <c r="J15" t="s">
-        <v>239</v>
-      </c>
       <c r="K15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M15" t="s">
         <v>53</v>
@@ -5153,55 +5153,55 @@
         <v>54</v>
       </c>
       <c r="O15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P15" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q15" t="s">
         <v>240</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>241</v>
       </c>
-      <c r="R15" t="s">
+      <c r="S15" t="s">
+        <v>49</v>
+      </c>
+      <c r="T15" t="s">
         <v>242</v>
       </c>
-      <c r="S15" t="s">
-        <v>49</v>
-      </c>
-      <c r="T15" t="s">
+      <c r="U15" t="s">
+        <v>57</v>
+      </c>
+      <c r="V15" t="s">
+        <v>57</v>
+      </c>
+      <c r="W15" t="s">
+        <v>163</v>
+      </c>
+      <c r="X15" t="s">
         <v>243</v>
       </c>
-      <c r="U15" t="s">
-        <v>57</v>
-      </c>
-      <c r="V15" t="s">
-        <v>57</v>
-      </c>
-      <c r="W15" t="s">
-        <v>164</v>
-      </c>
-      <c r="X15" t="s">
+      <c r="Y15" t="s">
+        <v>225</v>
+      </c>
+      <c r="Z15" t="s">
         <v>244</v>
       </c>
-      <c r="Y15" t="s">
-        <v>226</v>
-      </c>
-      <c r="Z15" t="s">
+      <c r="AA15" t="s">
         <v>245</v>
       </c>
-      <c r="AA15" t="s">
+      <c r="AB15" t="s">
         <v>246</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>247</v>
       </c>
       <c r="AC15" t="s">
         <v>62</v>
       </c>
       <c r="AD15" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE15" t="s">
         <v>126</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>127</v>
       </c>
       <c r="AF15" t="s">
         <v>65</v>
@@ -5234,7 +5234,7 @@
         <v>49</v>
       </c>
       <c r="AP15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.3">
@@ -5245,34 +5245,34 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
+        <v>248</v>
+      </c>
+      <c r="D16" t="s">
         <v>249</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>250</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>251</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>252</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" t="s">
         <v>253</v>
       </c>
-      <c r="H16" t="s">
-        <v>49</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>254</v>
       </c>
-      <c r="J16" t="s">
-        <v>255</v>
-      </c>
       <c r="K16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M16" t="s">
         <v>53</v>
@@ -5284,52 +5284,52 @@
         <v>55</v>
       </c>
       <c r="P16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q16" t="s">
         <v>76</v>
       </c>
       <c r="R16" t="s">
+        <v>255</v>
+      </c>
+      <c r="S16" t="s">
+        <v>49</v>
+      </c>
+      <c r="T16" t="s">
         <v>256</v>
       </c>
-      <c r="S16" t="s">
-        <v>49</v>
-      </c>
-      <c r="T16" t="s">
+      <c r="U16" t="s">
+        <v>57</v>
+      </c>
+      <c r="V16" t="s">
+        <v>57</v>
+      </c>
+      <c r="W16" t="s">
         <v>257</v>
       </c>
-      <c r="U16" t="s">
-        <v>57</v>
-      </c>
-      <c r="V16" t="s">
-        <v>57</v>
-      </c>
-      <c r="W16" t="s">
+      <c r="X16" t="s">
         <v>258</v>
       </c>
-      <c r="X16" t="s">
+      <c r="Y16" t="s">
+        <v>225</v>
+      </c>
+      <c r="Z16" t="s">
         <v>259</v>
       </c>
-      <c r="Y16" t="s">
-        <v>226</v>
-      </c>
-      <c r="Z16" t="s">
+      <c r="AA16" t="s">
         <v>260</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="AB16" t="s">
         <v>261</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>262</v>
       </c>
       <c r="AC16" t="s">
         <v>62</v>
       </c>
       <c r="AD16" t="s">
+        <v>262</v>
+      </c>
+      <c r="AE16" t="s">
         <v>263</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>264</v>
       </c>
       <c r="AF16" t="s">
         <v>65</v>
@@ -5362,7 +5362,7 @@
         <v>49</v>
       </c>
       <c r="AP16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.3">
@@ -5373,34 +5373,34 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
+        <v>265</v>
+      </c>
+      <c r="D17" t="s">
         <v>266</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>267</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>268</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>269</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" t="s">
         <v>270</v>
       </c>
-      <c r="H17" t="s">
-        <v>49</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>271</v>
       </c>
-      <c r="J17" t="s">
-        <v>272</v>
-      </c>
       <c r="K17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M17" t="s">
         <v>53</v>
@@ -5415,40 +5415,40 @@
         <v>56</v>
       </c>
       <c r="Q17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R17" t="s">
+        <v>272</v>
+      </c>
+      <c r="S17" t="s">
+        <v>49</v>
+      </c>
+      <c r="T17" t="s">
         <v>273</v>
       </c>
-      <c r="S17" t="s">
-        <v>49</v>
-      </c>
-      <c r="T17" t="s">
+      <c r="U17" t="s">
+        <v>57</v>
+      </c>
+      <c r="V17" t="s">
+        <v>57</v>
+      </c>
+      <c r="W17" t="s">
+        <v>257</v>
+      </c>
+      <c r="X17" t="s">
         <v>274</v>
       </c>
-      <c r="U17" t="s">
-        <v>57</v>
-      </c>
-      <c r="V17" t="s">
-        <v>57</v>
-      </c>
-      <c r="W17" t="s">
-        <v>258</v>
-      </c>
-      <c r="X17" t="s">
+      <c r="Y17" t="s">
+        <v>225</v>
+      </c>
+      <c r="Z17" t="s">
         <v>275</v>
       </c>
-      <c r="Y17" t="s">
-        <v>226</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>276</v>
-      </c>
       <c r="AA17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AB17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AC17" t="s">
         <v>62</v>
@@ -5490,7 +5490,7 @@
         <v>49</v>
       </c>
       <c r="AP17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.3">
@@ -5501,34 +5501,34 @@
         <v>43</v>
       </c>
       <c r="C18" t="s">
+        <v>277</v>
+      </c>
+      <c r="D18" t="s">
         <v>278</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>279</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
+        <v>235</v>
+      </c>
+      <c r="G18" t="s">
         <v>280</v>
       </c>
-      <c r="F18" t="s">
-        <v>236</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>281</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
+        <v>281</v>
+      </c>
+      <c r="J18" t="s">
         <v>282</v>
       </c>
-      <c r="I18" t="s">
-        <v>282</v>
-      </c>
-      <c r="J18" t="s">
-        <v>283</v>
-      </c>
       <c r="K18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M18" t="s">
         <v>53</v>
@@ -5543,49 +5543,49 @@
         <v>56</v>
       </c>
       <c r="Q18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R18" t="s">
+        <v>283</v>
+      </c>
+      <c r="S18" t="s">
+        <v>49</v>
+      </c>
+      <c r="T18" t="s">
         <v>284</v>
       </c>
-      <c r="S18" t="s">
-        <v>49</v>
-      </c>
-      <c r="T18" t="s">
+      <c r="U18" t="s">
+        <v>57</v>
+      </c>
+      <c r="V18" t="s">
+        <v>57</v>
+      </c>
+      <c r="W18" t="s">
+        <v>163</v>
+      </c>
+      <c r="X18" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>225</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>240</v>
+      </c>
+      <c r="AB18" t="s">
         <v>285</v>
-      </c>
-      <c r="U18" t="s">
-        <v>57</v>
-      </c>
-      <c r="V18" t="s">
-        <v>57</v>
-      </c>
-      <c r="W18" t="s">
-        <v>164</v>
-      </c>
-      <c r="X18" t="s">
-        <v>275</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>226</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>198</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>241</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>286</v>
       </c>
       <c r="AC18" t="s">
         <v>62</v>
       </c>
       <c r="AD18" t="s">
+        <v>262</v>
+      </c>
+      <c r="AE18" t="s">
         <v>263</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>264</v>
       </c>
       <c r="AF18" t="s">
         <v>65</v>
@@ -5618,7 +5618,7 @@
         <v>49</v>
       </c>
       <c r="AP18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19" spans="1:42" x14ac:dyDescent="0.3">
@@ -5629,34 +5629,34 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
+        <v>287</v>
+      </c>
+      <c r="D19" t="s">
         <v>288</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>289</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>235</v>
+      </c>
+      <c r="G19" t="s">
+        <v>280</v>
+      </c>
+      <c r="H19" t="s">
+        <v>281</v>
+      </c>
+      <c r="I19" t="s">
+        <v>281</v>
+      </c>
+      <c r="J19" t="s">
         <v>290</v>
       </c>
-      <c r="F19" t="s">
-        <v>236</v>
-      </c>
-      <c r="G19" t="s">
-        <v>281</v>
-      </c>
-      <c r="H19" t="s">
-        <v>282</v>
-      </c>
-      <c r="I19" t="s">
-        <v>282</v>
-      </c>
-      <c r="J19" t="s">
-        <v>291</v>
-      </c>
       <c r="K19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M19" t="s">
         <v>53</v>
@@ -5671,49 +5671,49 @@
         <v>56</v>
       </c>
       <c r="Q19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="R19" t="s">
+        <v>291</v>
+      </c>
+      <c r="S19" t="s">
+        <v>49</v>
+      </c>
+      <c r="T19" t="s">
         <v>292</v>
       </c>
-      <c r="S19" t="s">
-        <v>49</v>
-      </c>
-      <c r="T19" t="s">
+      <c r="U19" t="s">
+        <v>57</v>
+      </c>
+      <c r="V19" t="s">
+        <v>57</v>
+      </c>
+      <c r="W19" t="s">
+        <v>199</v>
+      </c>
+      <c r="X19" t="s">
         <v>293</v>
       </c>
-      <c r="U19" t="s">
-        <v>57</v>
-      </c>
-      <c r="V19" t="s">
-        <v>57</v>
-      </c>
-      <c r="W19" t="s">
-        <v>200</v>
-      </c>
-      <c r="X19" t="s">
+      <c r="Y19" t="s">
+        <v>225</v>
+      </c>
+      <c r="Z19" t="s">
         <v>294</v>
       </c>
-      <c r="Y19" t="s">
-        <v>226</v>
-      </c>
-      <c r="Z19" t="s">
+      <c r="AA19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AB19" t="s">
         <v>295</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>241</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>296</v>
       </c>
       <c r="AC19" t="s">
         <v>62</v>
       </c>
       <c r="AD19" t="s">
+        <v>262</v>
+      </c>
+      <c r="AE19" t="s">
         <v>263</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>264</v>
       </c>
       <c r="AF19" t="s">
         <v>65</v>
@@ -5746,7 +5746,7 @@
         <v>49</v>
       </c>
       <c r="AP19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" spans="1:42" x14ac:dyDescent="0.3">
@@ -5757,34 +5757,34 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
+        <v>297</v>
+      </c>
+      <c r="D20" t="s">
         <v>298</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>299</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>300</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>301</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" t="s">
         <v>302</v>
       </c>
-      <c r="H20" t="s">
-        <v>49</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>303</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>304</v>
       </c>
-      <c r="K20" t="s">
-        <v>305</v>
-      </c>
       <c r="L20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M20" t="s">
         <v>53</v>
@@ -5799,49 +5799,49 @@
         <v>94</v>
       </c>
       <c r="Q20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="R20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S20" t="s">
         <v>49</v>
       </c>
       <c r="T20" t="s">
+        <v>305</v>
+      </c>
+      <c r="U20" t="s">
+        <v>57</v>
+      </c>
+      <c r="V20" t="s">
+        <v>57</v>
+      </c>
+      <c r="W20" t="s">
+        <v>199</v>
+      </c>
+      <c r="X20" t="s">
         <v>306</v>
       </c>
-      <c r="U20" t="s">
-        <v>57</v>
-      </c>
-      <c r="V20" t="s">
-        <v>57</v>
-      </c>
-      <c r="W20" t="s">
-        <v>200</v>
-      </c>
-      <c r="X20" t="s">
+      <c r="Y20" t="s">
+        <v>304</v>
+      </c>
+      <c r="Z20" t="s">
         <v>307</v>
       </c>
-      <c r="Y20" t="s">
-        <v>305</v>
-      </c>
-      <c r="Z20" t="s">
+      <c r="AA20" t="s">
         <v>308</v>
       </c>
-      <c r="AA20" t="s">
+      <c r="AB20" t="s">
         <v>309</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>310</v>
       </c>
       <c r="AC20" t="s">
         <v>62</v>
       </c>
       <c r="AD20" t="s">
+        <v>310</v>
+      </c>
+      <c r="AE20" t="s">
         <v>311</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>312</v>
       </c>
       <c r="AF20" t="s">
         <v>65</v>
@@ -5874,7 +5874,7 @@
         <v>49</v>
       </c>
       <c r="AP20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="1:42" x14ac:dyDescent="0.3">
@@ -5885,34 +5885,34 @@
         <v>43</v>
       </c>
       <c r="C21" t="s">
+        <v>313</v>
+      </c>
+      <c r="D21" t="s">
         <v>314</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>315</v>
-      </c>
-      <c r="E21" t="s">
-        <v>316</v>
       </c>
       <c r="F21" t="s">
         <v>89</v>
       </c>
       <c r="G21" t="s">
+        <v>316</v>
+      </c>
+      <c r="H21" t="s">
+        <v>49</v>
+      </c>
+      <c r="I21" t="s">
         <v>317</v>
       </c>
-      <c r="H21" t="s">
-        <v>49</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>318</v>
       </c>
-      <c r="J21" t="s">
-        <v>319</v>
-      </c>
       <c r="K21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M21" t="s">
         <v>53</v>
@@ -5924,52 +5924,52 @@
         <v>55</v>
       </c>
       <c r="P21" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q21" t="s">
         <v>320</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>321</v>
       </c>
-      <c r="R21" t="s">
+      <c r="S21" t="s">
+        <v>49</v>
+      </c>
+      <c r="T21" t="s">
         <v>322</v>
       </c>
-      <c r="S21" t="s">
-        <v>49</v>
-      </c>
-      <c r="T21" t="s">
+      <c r="U21" t="s">
+        <v>57</v>
+      </c>
+      <c r="V21" t="s">
+        <v>57</v>
+      </c>
+      <c r="W21" t="s">
         <v>323</v>
       </c>
-      <c r="U21" t="s">
-        <v>57</v>
-      </c>
-      <c r="V21" t="s">
-        <v>57</v>
-      </c>
-      <c r="W21" t="s">
+      <c r="X21" t="s">
         <v>324</v>
       </c>
-      <c r="X21" t="s">
+      <c r="Y21" t="s">
+        <v>304</v>
+      </c>
+      <c r="Z21" t="s">
         <v>325</v>
       </c>
-      <c r="Y21" t="s">
-        <v>305</v>
-      </c>
-      <c r="Z21" t="s">
+      <c r="AA21" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB21" t="s">
         <v>326</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>327</v>
       </c>
       <c r="AC21" t="s">
         <v>62</v>
       </c>
       <c r="AD21" t="s">
+        <v>327</v>
+      </c>
+      <c r="AE21" t="s">
         <v>328</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>329</v>
       </c>
       <c r="AF21" t="s">
         <v>65</v>
@@ -6002,7 +6002,7 @@
         <v>49</v>
       </c>
       <c r="AP21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.3">
@@ -6013,34 +6013,34 @@
         <v>43</v>
       </c>
       <c r="C22" t="s">
+        <v>330</v>
+      </c>
+      <c r="D22" t="s">
         <v>331</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>332</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>333</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>334</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" t="s">
         <v>335</v>
       </c>
-      <c r="H22" t="s">
-        <v>49</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>336</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
+        <v>225</v>
+      </c>
+      <c r="L22" t="s">
         <v>337</v>
-      </c>
-      <c r="K22" t="s">
-        <v>226</v>
-      </c>
-      <c r="L22" t="s">
-        <v>338</v>
       </c>
       <c r="M22" t="s">
         <v>53</v>
@@ -6049,22 +6049,22 @@
         <v>54</v>
       </c>
       <c r="O22" t="s">
+        <v>338</v>
+      </c>
+      <c r="P22" t="s">
         <v>339</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
+        <v>57</v>
+      </c>
+      <c r="R22" t="s">
         <v>340</v>
       </c>
-      <c r="Q22" t="s">
-        <v>57</v>
-      </c>
-      <c r="R22" t="s">
+      <c r="S22" t="s">
+        <v>49</v>
+      </c>
+      <c r="T22" t="s">
         <v>341</v>
-      </c>
-      <c r="S22" t="s">
-        <v>49</v>
-      </c>
-      <c r="T22" t="s">
-        <v>342</v>
       </c>
       <c r="U22" t="s">
         <v>57</v>
@@ -6076,19 +6076,19 @@
         <v>60</v>
       </c>
       <c r="X22" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Y22" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Z22" t="s">
         <v>49</v>
       </c>
       <c r="AA22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AB22" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AC22" t="s">
         <v>62</v>
@@ -6130,7 +6130,7 @@
         <v>49</v>
       </c>
       <c r="AP22" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="23" spans="1:42" x14ac:dyDescent="0.3">
@@ -6141,34 +6141,34 @@
         <v>43</v>
       </c>
       <c r="C23" t="s">
+        <v>344</v>
+      </c>
+      <c r="D23" t="s">
         <v>345</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>346</v>
-      </c>
-      <c r="E23" t="s">
-        <v>347</v>
       </c>
       <c r="F23" t="s">
         <v>89</v>
       </c>
       <c r="G23" t="s">
+        <v>347</v>
+      </c>
+      <c r="H23" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" t="s">
         <v>348</v>
       </c>
-      <c r="H23" t="s">
-        <v>49</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>349</v>
       </c>
-      <c r="J23" t="s">
-        <v>350</v>
-      </c>
       <c r="K23" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L23" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M23" t="s">
         <v>53</v>
@@ -6180,52 +6180,52 @@
         <v>55</v>
       </c>
       <c r="P23" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q23" t="s">
         <v>76</v>
       </c>
       <c r="R23" t="s">
+        <v>350</v>
+      </c>
+      <c r="S23" t="s">
+        <v>49</v>
+      </c>
+      <c r="T23" t="s">
         <v>351</v>
       </c>
-      <c r="S23" t="s">
-        <v>49</v>
-      </c>
-      <c r="T23" t="s">
+      <c r="U23" t="s">
+        <v>57</v>
+      </c>
+      <c r="V23" t="s">
+        <v>57</v>
+      </c>
+      <c r="W23" t="s">
         <v>352</v>
       </c>
-      <c r="U23" t="s">
-        <v>57</v>
-      </c>
-      <c r="V23" t="s">
-        <v>57</v>
-      </c>
-      <c r="W23" t="s">
+      <c r="X23" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z23" t="s">
         <v>353</v>
       </c>
-      <c r="X23" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>338</v>
-      </c>
-      <c r="Z23" t="s">
+      <c r="AA23" t="s">
         <v>354</v>
       </c>
-      <c r="AA23" t="s">
+      <c r="AB23" t="s">
         <v>355</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>356</v>
       </c>
       <c r="AC23" t="s">
         <v>62</v>
       </c>
       <c r="AD23" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE23" t="s">
         <v>111</v>
-      </c>
-      <c r="AE23" t="s">
-        <v>112</v>
       </c>
       <c r="AF23" t="s">
         <v>65</v>
@@ -6258,7 +6258,7 @@
         <v>49</v>
       </c>
       <c r="AP23" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24" spans="1:42" x14ac:dyDescent="0.3">
@@ -6269,34 +6269,34 @@
         <v>43</v>
       </c>
       <c r="C24" t="s">
+        <v>357</v>
+      </c>
+      <c r="D24" t="s">
         <v>358</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>359</v>
-      </c>
-      <c r="E24" t="s">
-        <v>360</v>
       </c>
       <c r="F24" t="s">
         <v>89</v>
       </c>
       <c r="G24" t="s">
+        <v>360</v>
+      </c>
+      <c r="H24" t="s">
+        <v>49</v>
+      </c>
+      <c r="I24" t="s">
         <v>361</v>
       </c>
-      <c r="H24" t="s">
-        <v>49</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>362</v>
       </c>
-      <c r="J24" t="s">
-        <v>363</v>
-      </c>
       <c r="K24" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L24" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M24" t="s">
         <v>53</v>
@@ -6314,13 +6314,13 @@
         <v>57</v>
       </c>
       <c r="R24" t="s">
+        <v>363</v>
+      </c>
+      <c r="S24" t="s">
+        <v>49</v>
+      </c>
+      <c r="T24" t="s">
         <v>364</v>
-      </c>
-      <c r="S24" t="s">
-        <v>49</v>
-      </c>
-      <c r="T24" t="s">
-        <v>365</v>
       </c>
       <c r="U24" t="s">
         <v>57</v>
@@ -6332,25 +6332,25 @@
         <v>60</v>
       </c>
       <c r="X24" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Y24" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Z24" t="s">
         <v>49</v>
       </c>
       <c r="AA24" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AB24" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AC24" t="s">
         <v>62</v>
       </c>
       <c r="AD24" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AE24" t="s">
         <v>64</v>
@@ -6386,7 +6386,7 @@
         <v>49</v>
       </c>
       <c r="AP24" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="25" spans="1:42" x14ac:dyDescent="0.3">
@@ -6397,34 +6397,34 @@
         <v>43</v>
       </c>
       <c r="C25" t="s">
+        <v>357</v>
+      </c>
+      <c r="D25" t="s">
         <v>358</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>359</v>
-      </c>
-      <c r="E25" t="s">
-        <v>360</v>
       </c>
       <c r="F25" t="s">
         <v>89</v>
       </c>
       <c r="G25" t="s">
+        <v>360</v>
+      </c>
+      <c r="H25" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" t="s">
         <v>361</v>
       </c>
-      <c r="H25" t="s">
-        <v>49</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>362</v>
       </c>
-      <c r="J25" t="s">
-        <v>363</v>
-      </c>
       <c r="K25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L25" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M25" t="s">
         <v>53</v>
@@ -6442,13 +6442,13 @@
         <v>57</v>
       </c>
       <c r="R25" t="s">
+        <v>363</v>
+      </c>
+      <c r="S25" t="s">
+        <v>49</v>
+      </c>
+      <c r="T25" t="s">
         <v>364</v>
-      </c>
-      <c r="S25" t="s">
-        <v>49</v>
-      </c>
-      <c r="T25" t="s">
-        <v>365</v>
       </c>
       <c r="U25" t="s">
         <v>57</v>
@@ -6460,25 +6460,25 @@
         <v>60</v>
       </c>
       <c r="X25" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Y25" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Z25" t="s">
         <v>49</v>
       </c>
       <c r="AA25" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AB25" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AC25" t="s">
         <v>62</v>
       </c>
       <c r="AD25" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AE25" t="s">
         <v>64</v>
@@ -6514,7 +6514,7 @@
         <v>49</v>
       </c>
       <c r="AP25" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="26" spans="1:42" x14ac:dyDescent="0.3">
@@ -6525,34 +6525,34 @@
         <v>43</v>
       </c>
       <c r="C26" t="s">
+        <v>368</v>
+      </c>
+      <c r="D26" t="s">
         <v>369</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>370</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>371</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>372</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
+        <v>49</v>
+      </c>
+      <c r="I26" t="s">
         <v>373</v>
       </c>
-      <c r="H26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>374</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>375</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>376</v>
-      </c>
-      <c r="L26" t="s">
-        <v>377</v>
       </c>
       <c r="M26" t="s">
         <v>53</v>
@@ -6564,19 +6564,19 @@
         <v>55</v>
       </c>
       <c r="P26" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q26" t="s">
         <v>76</v>
       </c>
       <c r="R26" t="s">
+        <v>378</v>
+      </c>
+      <c r="S26" t="s">
+        <v>49</v>
+      </c>
+      <c r="T26" t="s">
         <v>379</v>
-      </c>
-      <c r="S26" t="s">
-        <v>49</v>
-      </c>
-      <c r="T26" t="s">
-        <v>380</v>
       </c>
       <c r="U26" t="s">
         <v>57</v>
@@ -6588,25 +6588,25 @@
         <v>79</v>
       </c>
       <c r="X26" t="s">
+        <v>380</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>376</v>
+      </c>
+      <c r="Z26" t="s">
         <v>381</v>
       </c>
-      <c r="Y26" t="s">
-        <v>377</v>
-      </c>
-      <c r="Z26" t="s">
+      <c r="AA26" t="s">
         <v>382</v>
       </c>
-      <c r="AA26" t="s">
-        <v>383</v>
-      </c>
       <c r="AB26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AC26" t="s">
         <v>62</v>
       </c>
       <c r="AD26" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AE26" t="s">
         <v>84</v>
@@ -6642,7 +6642,7 @@
         <v>49</v>
       </c>
       <c r="AP26" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="27" spans="1:42" x14ac:dyDescent="0.3">
@@ -6653,34 +6653,34 @@
         <v>43</v>
       </c>
       <c r="C27" t="s">
+        <v>385</v>
+      </c>
+      <c r="D27" t="s">
         <v>386</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>387</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
+        <v>371</v>
+      </c>
+      <c r="G27" t="s">
+        <v>372</v>
+      </c>
+      <c r="H27" t="s">
+        <v>49</v>
+      </c>
+      <c r="I27" t="s">
         <v>388</v>
       </c>
-      <c r="F27" t="s">
-        <v>372</v>
-      </c>
-      <c r="G27" t="s">
-        <v>373</v>
-      </c>
-      <c r="H27" t="s">
-        <v>49</v>
-      </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>389</v>
       </c>
-      <c r="J27" t="s">
-        <v>390</v>
-      </c>
       <c r="K27" t="s">
+        <v>375</v>
+      </c>
+      <c r="L27" t="s">
         <v>376</v>
-      </c>
-      <c r="L27" t="s">
-        <v>377</v>
       </c>
       <c r="M27" t="s">
         <v>53</v>
@@ -6692,19 +6692,19 @@
         <v>55</v>
       </c>
       <c r="P27" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q27" t="s">
         <v>76</v>
       </c>
       <c r="R27" t="s">
+        <v>378</v>
+      </c>
+      <c r="S27" t="s">
+        <v>49</v>
+      </c>
+      <c r="T27" t="s">
         <v>379</v>
-      </c>
-      <c r="S27" t="s">
-        <v>49</v>
-      </c>
-      <c r="T27" t="s">
-        <v>380</v>
       </c>
       <c r="U27" t="s">
         <v>57</v>
@@ -6716,25 +6716,25 @@
         <v>79</v>
       </c>
       <c r="X27" t="s">
+        <v>380</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>376</v>
+      </c>
+      <c r="Z27" t="s">
         <v>381</v>
       </c>
-      <c r="Y27" t="s">
-        <v>377</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>382</v>
-      </c>
       <c r="AA27" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AB27" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AC27" t="s">
         <v>62</v>
       </c>
       <c r="AD27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AE27" t="s">
         <v>84</v>
@@ -6770,7 +6770,7 @@
         <v>49</v>
       </c>
       <c r="AP27" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28" spans="1:42" x14ac:dyDescent="0.3">
@@ -6781,34 +6781,34 @@
         <v>43</v>
       </c>
       <c r="C28" t="s">
+        <v>391</v>
+      </c>
+      <c r="D28" t="s">
         <v>392</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>393</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>394</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>395</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
+        <v>49</v>
+      </c>
+      <c r="I28" t="s">
         <v>396</v>
       </c>
-      <c r="H28" t="s">
-        <v>49</v>
-      </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>397</v>
       </c>
-      <c r="J28" t="s">
-        <v>398</v>
-      </c>
       <c r="K28" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L28" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M28" t="s">
         <v>53</v>
@@ -6817,23 +6817,23 @@
         <v>54</v>
       </c>
       <c r="O28" t="s">
+        <v>398</v>
+      </c>
+      <c r="P28" t="s">
         <v>399</v>
       </c>
-      <c r="P28" t="s">
-        <v>400</v>
-      </c>
       <c r="Q28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R28" t="s">
+        <v>197</v>
+      </c>
+      <c r="S28" t="s">
+        <v>49</v>
+      </c>
+      <c r="T28" t="s">
         <v>198</v>
       </c>
-      <c r="S28" t="s">
-        <v>49</v>
-      </c>
-      <c r="T28" t="s">
-        <v>199</v>
-      </c>
       <c r="U28" t="s">
         <v>57</v>
       </c>
@@ -6841,31 +6841,31 @@
         <v>57</v>
       </c>
       <c r="W28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X28" t="s">
         <v>80</v>
       </c>
       <c r="Y28" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Z28" t="s">
+        <v>400</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>260</v>
+      </c>
+      <c r="AB28" t="s">
         <v>401</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>261</v>
-      </c>
-      <c r="AB28" t="s">
-        <v>402</v>
       </c>
       <c r="AC28" t="s">
         <v>62</v>
       </c>
       <c r="AD28" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE28" t="s">
         <v>126</v>
-      </c>
-      <c r="AE28" t="s">
-        <v>127</v>
       </c>
       <c r="AF28" t="s">
         <v>65</v>
@@ -6898,7 +6898,7 @@
         <v>49</v>
       </c>
       <c r="AP28" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="29" spans="1:42" x14ac:dyDescent="0.3">
@@ -6909,34 +6909,34 @@
         <v>43</v>
       </c>
       <c r="C29" t="s">
+        <v>403</v>
+      </c>
+      <c r="D29" t="s">
         <v>404</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>405</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
+        <v>333</v>
+      </c>
+      <c r="G29" t="s">
         <v>406</v>
       </c>
-      <c r="F29" t="s">
-        <v>334</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>407</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
+        <v>407</v>
+      </c>
+      <c r="J29" t="s">
         <v>408</v>
       </c>
-      <c r="I29" t="s">
-        <v>408</v>
-      </c>
-      <c r="J29" t="s">
-        <v>409</v>
-      </c>
       <c r="K29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M29" t="s">
         <v>53</v>
@@ -6945,23 +6945,23 @@
         <v>54</v>
       </c>
       <c r="O29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P29" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q29" t="s">
         <v>95</v>
       </c>
       <c r="R29" t="s">
+        <v>350</v>
+      </c>
+      <c r="S29" t="s">
+        <v>49</v>
+      </c>
+      <c r="T29" t="s">
         <v>351</v>
       </c>
-      <c r="S29" t="s">
-        <v>49</v>
-      </c>
-      <c r="T29" t="s">
-        <v>352</v>
-      </c>
       <c r="U29" t="s">
         <v>57</v>
       </c>
@@ -6969,32 +6969,32 @@
         <v>57</v>
       </c>
       <c r="W29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X29" t="s">
+        <v>410</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>225</v>
+      </c>
+      <c r="Z29" t="s">
         <v>411</v>
       </c>
-      <c r="Y29" t="s">
-        <v>226</v>
-      </c>
-      <c r="Z29" t="s">
+      <c r="AA29" t="s">
         <v>412</v>
       </c>
-      <c r="AA29" t="s">
+      <c r="AB29" t="s">
         <v>413</v>
-      </c>
-      <c r="AB29" t="s">
-        <v>414</v>
       </c>
       <c r="AC29" t="s">
         <v>62</v>
       </c>
       <c r="AD29" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE29" t="s">
         <v>111</v>
       </c>
-      <c r="AE29" t="s">
-        <v>112</v>
-      </c>
       <c r="AF29" t="s">
         <v>65</v>
       </c>
@@ -7017,16 +7017,16 @@
         <v>49</v>
       </c>
       <c r="AM29" t="s">
+        <v>414</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO29" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP29" t="s">
         <v>415</v>
-      </c>
-      <c r="AN29" t="s">
-        <v>49</v>
-      </c>
-      <c r="AO29" t="s">
-        <v>49</v>
-      </c>
-      <c r="AP29" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="30" spans="1:42" x14ac:dyDescent="0.3">
@@ -7037,34 +7037,34 @@
         <v>43</v>
       </c>
       <c r="C30" t="s">
+        <v>416</v>
+      </c>
+      <c r="D30" t="s">
         <v>417</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>418</v>
-      </c>
-      <c r="E30" t="s">
-        <v>419</v>
       </c>
       <c r="F30" t="s">
         <v>89</v>
       </c>
       <c r="G30" t="s">
+        <v>419</v>
+      </c>
+      <c r="H30" t="s">
         <v>420</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
+        <v>420</v>
+      </c>
+      <c r="J30" t="s">
         <v>421</v>
       </c>
-      <c r="I30" t="s">
-        <v>421</v>
-      </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>422</v>
       </c>
-      <c r="K30" t="s">
-        <v>423</v>
-      </c>
       <c r="L30" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="M30" t="s">
         <v>53</v>
@@ -7082,46 +7082,46 @@
         <v>76</v>
       </c>
       <c r="R30" t="s">
+        <v>423</v>
+      </c>
+      <c r="S30" t="s">
+        <v>49</v>
+      </c>
+      <c r="T30" t="s">
         <v>424</v>
       </c>
-      <c r="S30" t="s">
-        <v>49</v>
-      </c>
-      <c r="T30" t="s">
+      <c r="U30" t="s">
+        <v>57</v>
+      </c>
+      <c r="V30" t="s">
+        <v>57</v>
+      </c>
+      <c r="W30" t="s">
+        <v>352</v>
+      </c>
+      <c r="X30" t="s">
+        <v>214</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>226</v>
+      </c>
+      <c r="AB30" t="s">
         <v>425</v>
-      </c>
-      <c r="U30" t="s">
-        <v>57</v>
-      </c>
-      <c r="V30" t="s">
-        <v>57</v>
-      </c>
-      <c r="W30" t="s">
-        <v>353</v>
-      </c>
-      <c r="X30" t="s">
-        <v>215</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>423</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>276</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>227</v>
-      </c>
-      <c r="AB30" t="s">
-        <v>426</v>
       </c>
       <c r="AC30" t="s">
         <v>62</v>
       </c>
       <c r="AD30" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE30" t="s">
         <v>126</v>
-      </c>
-      <c r="AE30" t="s">
-        <v>127</v>
       </c>
       <c r="AF30" t="s">
         <v>65</v>
@@ -7154,7 +7154,7 @@
         <v>49</v>
       </c>
       <c r="AP30" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="31" spans="1:42" x14ac:dyDescent="0.3">
@@ -7165,34 +7165,34 @@
         <v>43</v>
       </c>
       <c r="C31" t="s">
+        <v>427</v>
+      </c>
+      <c r="D31" t="s">
         <v>428</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>429</v>
-      </c>
-      <c r="E31" t="s">
-        <v>430</v>
       </c>
       <c r="F31" t="s">
         <v>89</v>
       </c>
       <c r="G31" t="s">
+        <v>430</v>
+      </c>
+      <c r="H31" t="s">
         <v>431</v>
       </c>
-      <c r="H31" t="s">
-        <v>432</v>
-      </c>
       <c r="I31" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="J31" t="s">
+        <v>421</v>
+      </c>
+      <c r="K31" t="s">
         <v>422</v>
       </c>
-      <c r="K31" t="s">
-        <v>423</v>
-      </c>
       <c r="L31" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="M31" t="s">
         <v>53</v>
@@ -7210,46 +7210,46 @@
         <v>76</v>
       </c>
       <c r="R31" t="s">
+        <v>423</v>
+      </c>
+      <c r="S31" t="s">
+        <v>49</v>
+      </c>
+      <c r="T31" t="s">
         <v>424</v>
       </c>
-      <c r="S31" t="s">
-        <v>49</v>
-      </c>
-      <c r="T31" t="s">
+      <c r="U31" t="s">
+        <v>57</v>
+      </c>
+      <c r="V31" t="s">
+        <v>57</v>
+      </c>
+      <c r="W31" t="s">
+        <v>352</v>
+      </c>
+      <c r="X31" t="s">
+        <v>214</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>275</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>226</v>
+      </c>
+      <c r="AB31" t="s">
         <v>425</v>
-      </c>
-      <c r="U31" t="s">
-        <v>57</v>
-      </c>
-      <c r="V31" t="s">
-        <v>57</v>
-      </c>
-      <c r="W31" t="s">
-        <v>353</v>
-      </c>
-      <c r="X31" t="s">
-        <v>215</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>423</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>276</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>227</v>
-      </c>
-      <c r="AB31" t="s">
-        <v>426</v>
       </c>
       <c r="AC31" t="s">
         <v>62</v>
       </c>
       <c r="AD31" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE31" t="s">
         <v>126</v>
-      </c>
-      <c r="AE31" t="s">
-        <v>127</v>
       </c>
       <c r="AF31" t="s">
         <v>65</v>
@@ -7282,7 +7282,7 @@
         <v>49</v>
       </c>
       <c r="AP31" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="32" spans="1:42" x14ac:dyDescent="0.3">
@@ -7293,34 +7293,34 @@
         <v>43</v>
       </c>
       <c r="C32" t="s">
+        <v>433</v>
+      </c>
+      <c r="D32" t="s">
         <v>434</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>435</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
+        <v>156</v>
+      </c>
+      <c r="G32" t="s">
         <v>436</v>
       </c>
-      <c r="F32" t="s">
-        <v>157</v>
-      </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>437</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
+        <v>437</v>
+      </c>
+      <c r="J32" t="s">
         <v>438</v>
       </c>
-      <c r="I32" t="s">
-        <v>438</v>
-      </c>
-      <c r="J32" t="s">
-        <v>439</v>
-      </c>
       <c r="K32" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L32" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M32" t="s">
         <v>53</v>
@@ -7329,55 +7329,55 @@
         <v>54</v>
       </c>
       <c r="O32" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P32" t="s">
+        <v>439</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>211</v>
+      </c>
+      <c r="R32" t="s">
+        <v>161</v>
+      </c>
+      <c r="S32" t="s">
+        <v>49</v>
+      </c>
+      <c r="T32" t="s">
+        <v>162</v>
+      </c>
+      <c r="U32" t="s">
+        <v>57</v>
+      </c>
+      <c r="V32" t="s">
+        <v>57</v>
+      </c>
+      <c r="W32" t="s">
+        <v>163</v>
+      </c>
+      <c r="X32" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA32" t="s">
         <v>440</v>
       </c>
-      <c r="Q32" t="s">
-        <v>212</v>
-      </c>
-      <c r="R32" t="s">
-        <v>162</v>
-      </c>
-      <c r="S32" t="s">
-        <v>49</v>
-      </c>
-      <c r="T32" t="s">
-        <v>163</v>
-      </c>
-      <c r="U32" t="s">
-        <v>57</v>
-      </c>
-      <c r="V32" t="s">
-        <v>57</v>
-      </c>
-      <c r="W32" t="s">
-        <v>164</v>
-      </c>
-      <c r="X32" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>338</v>
-      </c>
-      <c r="Z32" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA32" t="s">
+      <c r="AB32" t="s">
         <v>441</v>
       </c>
-      <c r="AB32" t="s">
-        <v>442</v>
-      </c>
       <c r="AC32" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="AD32" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE32" t="s">
         <v>111</v>
-      </c>
-      <c r="AE32" t="s">
-        <v>112</v>
       </c>
       <c r="AF32" t="s">
         <v>65</v>
@@ -7410,7 +7410,7 @@
         <v>49</v>
       </c>
       <c r="AP32" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="33" spans="1:42" x14ac:dyDescent="0.3">
@@ -7421,34 +7421,34 @@
         <v>43</v>
       </c>
       <c r="C33" t="s">
+        <v>443</v>
+      </c>
+      <c r="D33" t="s">
         <v>444</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>445</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
+        <v>156</v>
+      </c>
+      <c r="G33" t="s">
         <v>446</v>
       </c>
-      <c r="F33" t="s">
-        <v>157</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
+        <v>49</v>
+      </c>
+      <c r="I33" t="s">
         <v>447</v>
       </c>
-      <c r="H33" t="s">
-        <v>49</v>
-      </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>448</v>
       </c>
-      <c r="J33" t="s">
-        <v>449</v>
-      </c>
       <c r="K33" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L33" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M33" t="s">
         <v>53</v>
@@ -7457,55 +7457,55 @@
         <v>54</v>
       </c>
       <c r="O33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P33" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Q33" t="s">
         <v>76</v>
       </c>
       <c r="R33" t="s">
+        <v>450</v>
+      </c>
+      <c r="S33" t="s">
+        <v>49</v>
+      </c>
+      <c r="T33" t="s">
         <v>451</v>
       </c>
-      <c r="S33" t="s">
-        <v>49</v>
-      </c>
-      <c r="T33" t="s">
+      <c r="U33" t="s">
+        <v>57</v>
+      </c>
+      <c r="V33" t="s">
+        <v>57</v>
+      </c>
+      <c r="W33" t="s">
+        <v>163</v>
+      </c>
+      <c r="X33" t="s">
         <v>452</v>
       </c>
-      <c r="U33" t="s">
-        <v>57</v>
-      </c>
-      <c r="V33" t="s">
-        <v>57</v>
-      </c>
-      <c r="W33" t="s">
-        <v>164</v>
-      </c>
-      <c r="X33" t="s">
+      <c r="Y33" t="s">
+        <v>376</v>
+      </c>
+      <c r="Z33" t="s">
         <v>453</v>
       </c>
-      <c r="Y33" t="s">
-        <v>377</v>
-      </c>
-      <c r="Z33" t="s">
+      <c r="AA33" t="s">
+        <v>240</v>
+      </c>
+      <c r="AB33" t="s">
         <v>454</v>
       </c>
-      <c r="AA33" t="s">
-        <v>241</v>
-      </c>
-      <c r="AB33" t="s">
+      <c r="AC33" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD33" t="s">
         <v>455</v>
       </c>
-      <c r="AC33" t="s">
-        <v>103</v>
-      </c>
-      <c r="AD33" t="s">
+      <c r="AE33" t="s">
         <v>456</v>
-      </c>
-      <c r="AE33" t="s">
-        <v>457</v>
       </c>
       <c r="AF33" t="s">
         <v>65</v>
@@ -7538,7 +7538,7 @@
         <v>49</v>
       </c>
       <c r="AP33" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="34" spans="1:42" x14ac:dyDescent="0.3">
@@ -7549,34 +7549,34 @@
         <v>43</v>
       </c>
       <c r="C34" t="s">
+        <v>458</v>
+      </c>
+      <c r="D34" t="s">
         <v>459</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>460</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
+        <v>156</v>
+      </c>
+      <c r="G34" t="s">
         <v>461</v>
       </c>
-      <c r="F34" t="s">
-        <v>157</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>462</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
+        <v>462</v>
+      </c>
+      <c r="J34" t="s">
         <v>463</v>
       </c>
-      <c r="I34" t="s">
-        <v>463</v>
-      </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>464</v>
       </c>
-      <c r="K34" t="s">
+      <c r="L34" t="s">
         <v>465</v>
-      </c>
-      <c r="L34" t="s">
-        <v>466</v>
       </c>
       <c r="M34" t="s">
         <v>53</v>
@@ -7585,88 +7585,88 @@
         <v>54</v>
       </c>
       <c r="O34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P34" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Q34" t="s">
         <v>60</v>
       </c>
       <c r="R34" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S34" t="s">
         <v>49</v>
       </c>
       <c r="T34" t="s">
+        <v>466</v>
+      </c>
+      <c r="U34" t="s">
+        <v>57</v>
+      </c>
+      <c r="V34" t="s">
+        <v>57</v>
+      </c>
+      <c r="W34" t="s">
         <v>467</v>
       </c>
-      <c r="U34" t="s">
-        <v>57</v>
-      </c>
-      <c r="V34" t="s">
-        <v>57</v>
-      </c>
-      <c r="W34" t="s">
+      <c r="X34" t="s">
         <v>468</v>
       </c>
-      <c r="X34" t="s">
-        <v>469</v>
-      </c>
       <c r="Y34" t="s">
         <v>49</v>
       </c>
       <c r="Z34" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AA34" t="s">
         <v>95</v>
       </c>
       <c r="AB34" t="s">
+        <v>468</v>
+      </c>
+      <c r="AC34" t="s">
         <v>469</v>
       </c>
-      <c r="AC34" t="s">
+      <c r="AD34" t="s">
+        <v>230</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI34" t="s">
         <v>470</v>
       </c>
-      <c r="AD34" t="s">
-        <v>231</v>
-      </c>
-      <c r="AE34" t="s">
-        <v>112</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>65</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH34" t="s">
-        <v>65</v>
-      </c>
-      <c r="AI34" t="s">
+      <c r="AJ34" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM34" t="s">
+        <v>414</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO34" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP34" t="s">
         <v>471</v>
-      </c>
-      <c r="AJ34" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK34" t="s">
-        <v>65</v>
-      </c>
-      <c r="AL34" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM34" t="s">
-        <v>415</v>
-      </c>
-      <c r="AN34" t="s">
-        <v>49</v>
-      </c>
-      <c r="AO34" t="s">
-        <v>49</v>
-      </c>
-      <c r="AP34" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="35" spans="1:42" x14ac:dyDescent="0.3">
@@ -7677,34 +7677,34 @@
         <v>43</v>
       </c>
       <c r="C35" t="s">
+        <v>472</v>
+      </c>
+      <c r="D35" t="s">
         <v>473</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>474</v>
-      </c>
-      <c r="E35" t="s">
-        <v>475</v>
       </c>
       <c r="F35" t="s">
         <v>89</v>
       </c>
       <c r="G35" t="s">
+        <v>475</v>
+      </c>
+      <c r="H35" t="s">
         <v>476</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
+        <v>476</v>
+      </c>
+      <c r="J35" t="s">
         <v>477</v>
       </c>
-      <c r="I35" t="s">
-        <v>477</v>
-      </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>478</v>
       </c>
-      <c r="K35" t="s">
-        <v>479</v>
-      </c>
       <c r="L35" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="M35" t="s">
         <v>53</v>
@@ -7716,49 +7716,49 @@
         <v>55</v>
       </c>
       <c r="P35" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R35" t="s">
+        <v>479</v>
+      </c>
+      <c r="S35" t="s">
+        <v>49</v>
+      </c>
+      <c r="T35" t="s">
         <v>480</v>
       </c>
-      <c r="S35" t="s">
-        <v>49</v>
-      </c>
-      <c r="T35" t="s">
+      <c r="U35" t="s">
+        <v>57</v>
+      </c>
+      <c r="V35" t="s">
+        <v>57</v>
+      </c>
+      <c r="W35" t="s">
+        <v>163</v>
+      </c>
+      <c r="X35" t="s">
         <v>481</v>
       </c>
-      <c r="U35" t="s">
-        <v>57</v>
-      </c>
-      <c r="V35" t="s">
-        <v>57</v>
-      </c>
-      <c r="W35" t="s">
-        <v>164</v>
-      </c>
-      <c r="X35" t="s">
+      <c r="Y35" t="s">
+        <v>478</v>
+      </c>
+      <c r="Z35" t="s">
         <v>482</v>
       </c>
-      <c r="Y35" t="s">
-        <v>479</v>
-      </c>
-      <c r="Z35" t="s">
-        <v>483</v>
-      </c>
       <c r="AA35" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AB35" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AC35" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AD35" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AE35" t="s">
         <v>84</v>
@@ -7773,7 +7773,7 @@
         <v>65</v>
       </c>
       <c r="AI35" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AJ35" t="s">
         <v>65</v>
@@ -7794,7 +7794,7 @@
         <v>49</v>
       </c>
       <c r="AP35" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="36" spans="1:42" x14ac:dyDescent="0.3">
@@ -7805,34 +7805,34 @@
         <v>43</v>
       </c>
       <c r="C36" t="s">
+        <v>485</v>
+      </c>
+      <c r="D36" t="s">
         <v>486</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>487</v>
-      </c>
-      <c r="E36" t="s">
-        <v>488</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
       </c>
       <c r="G36" t="s">
+        <v>475</v>
+      </c>
+      <c r="H36" t="s">
         <v>476</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
+        <v>476</v>
+      </c>
+      <c r="J36" t="s">
         <v>477</v>
       </c>
-      <c r="I36" t="s">
-        <v>477</v>
-      </c>
-      <c r="J36" t="s">
+      <c r="K36" t="s">
         <v>478</v>
       </c>
-      <c r="K36" t="s">
-        <v>479</v>
-      </c>
       <c r="L36" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="M36" t="s">
         <v>53</v>
@@ -7844,49 +7844,49 @@
         <v>55</v>
       </c>
       <c r="P36" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q36" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R36" t="s">
+        <v>479</v>
+      </c>
+      <c r="S36" t="s">
+        <v>49</v>
+      </c>
+      <c r="T36" t="s">
         <v>480</v>
       </c>
-      <c r="S36" t="s">
-        <v>49</v>
-      </c>
-      <c r="T36" t="s">
+      <c r="U36" t="s">
+        <v>57</v>
+      </c>
+      <c r="V36" t="s">
+        <v>57</v>
+      </c>
+      <c r="W36" t="s">
+        <v>163</v>
+      </c>
+      <c r="X36" t="s">
         <v>481</v>
       </c>
-      <c r="U36" t="s">
-        <v>57</v>
-      </c>
-      <c r="V36" t="s">
-        <v>57</v>
-      </c>
-      <c r="W36" t="s">
-        <v>164</v>
-      </c>
-      <c r="X36" t="s">
+      <c r="Y36" t="s">
+        <v>478</v>
+      </c>
+      <c r="Z36" t="s">
         <v>482</v>
       </c>
-      <c r="Y36" t="s">
-        <v>479</v>
-      </c>
-      <c r="Z36" t="s">
-        <v>483</v>
-      </c>
       <c r="AA36" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AB36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AC36" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AD36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AE36" t="s">
         <v>84</v>
@@ -7901,7 +7901,7 @@
         <v>65</v>
       </c>
       <c r="AI36" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AJ36" t="s">
         <v>65</v>
@@ -7922,7 +7922,7 @@
         <v>49</v>
       </c>
       <c r="AP36" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="37" spans="1:42" x14ac:dyDescent="0.3">
@@ -7933,34 +7933,34 @@
         <v>43</v>
       </c>
       <c r="C37" t="s">
+        <v>489</v>
+      </c>
+      <c r="D37" t="s">
         <v>490</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>491</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
+        <v>251</v>
+      </c>
+      <c r="G37" t="s">
         <v>492</v>
       </c>
-      <c r="F37" t="s">
-        <v>252</v>
-      </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
+        <v>49</v>
+      </c>
+      <c r="I37" t="s">
         <v>493</v>
       </c>
-      <c r="H37" t="s">
-        <v>49</v>
-      </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>494</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
+        <v>376</v>
+      </c>
+      <c r="L37" t="s">
         <v>495</v>
-      </c>
-      <c r="K37" t="s">
-        <v>377</v>
-      </c>
-      <c r="L37" t="s">
-        <v>496</v>
       </c>
       <c r="M37" t="s">
         <v>53</v>
@@ -7972,19 +7972,19 @@
         <v>55</v>
       </c>
       <c r="P37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q37" t="s">
         <v>57</v>
       </c>
       <c r="R37" t="s">
+        <v>496</v>
+      </c>
+      <c r="S37" t="s">
+        <v>49</v>
+      </c>
+      <c r="T37" t="s">
         <v>497</v>
-      </c>
-      <c r="S37" t="s">
-        <v>49</v>
-      </c>
-      <c r="T37" t="s">
-        <v>498</v>
       </c>
       <c r="U37" t="s">
         <v>57</v>
@@ -7996,28 +7996,28 @@
         <v>60</v>
       </c>
       <c r="X37" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y37" t="s">
+        <v>495</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>166</v>
+      </c>
+      <c r="AB37" t="s">
         <v>496</v>
-      </c>
-      <c r="Z37" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA37" t="s">
-        <v>167</v>
-      </c>
-      <c r="AB37" t="s">
-        <v>497</v>
       </c>
       <c r="AC37" t="s">
         <v>62</v>
       </c>
       <c r="AD37" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AE37" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AF37" t="s">
         <v>65</v>
@@ -8050,7 +8050,7 @@
         <v>49</v>
       </c>
       <c r="AP37" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="38" spans="1:42" x14ac:dyDescent="0.3">
@@ -8058,37 +8058,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="s">
+        <v>500</v>
+      </c>
+      <c r="C38" t="s">
         <v>501</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>502</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>503</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>504</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>505</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
+        <v>49</v>
+      </c>
+      <c r="I38" t="s">
         <v>506</v>
       </c>
-      <c r="H38" t="s">
-        <v>49</v>
-      </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>507</v>
       </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
+        <v>495</v>
+      </c>
+      <c r="L38" t="s">
         <v>508</v>
-      </c>
-      <c r="K38" t="s">
-        <v>496</v>
-      </c>
-      <c r="L38" t="s">
-        <v>509</v>
       </c>
       <c r="M38" t="s">
         <v>53</v>
@@ -8097,88 +8097,88 @@
         <v>54</v>
       </c>
       <c r="O38" t="s">
+        <v>509</v>
+      </c>
+      <c r="P38" t="s">
         <v>510</v>
       </c>
-      <c r="P38" t="s">
+      <c r="Q38" t="s">
+        <v>240</v>
+      </c>
+      <c r="R38" t="s">
+        <v>482</v>
+      </c>
+      <c r="S38" t="s">
+        <v>49</v>
+      </c>
+      <c r="T38" t="s">
         <v>511</v>
       </c>
-      <c r="Q38" t="s">
-        <v>241</v>
-      </c>
-      <c r="R38" t="s">
-        <v>483</v>
-      </c>
-      <c r="S38" t="s">
-        <v>49</v>
-      </c>
-      <c r="T38" t="s">
+      <c r="U38" t="s">
+        <v>57</v>
+      </c>
+      <c r="V38" t="s">
+        <v>57</v>
+      </c>
+      <c r="W38" t="s">
+        <v>257</v>
+      </c>
+      <c r="X38" t="s">
+        <v>481</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>508</v>
+      </c>
+      <c r="Z38" t="s">
         <v>512</v>
       </c>
-      <c r="U38" t="s">
-        <v>57</v>
-      </c>
-      <c r="V38" t="s">
-        <v>57</v>
-      </c>
-      <c r="W38" t="s">
-        <v>258</v>
-      </c>
-      <c r="X38" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>509</v>
-      </c>
-      <c r="Z38" t="s">
+      <c r="AA38" t="s">
         <v>513</v>
       </c>
-      <c r="AA38" t="s">
+      <c r="AB38" t="s">
         <v>514</v>
-      </c>
-      <c r="AB38" t="s">
-        <v>515</v>
       </c>
       <c r="AC38" t="s">
         <v>62</v>
       </c>
       <c r="AD38" t="s">
+        <v>515</v>
+      </c>
+      <c r="AE38" t="s">
+        <v>311</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG38" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL38" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM38" t="s">
+        <v>414</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO38" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP38" t="s">
         <v>516</v>
-      </c>
-      <c r="AE38" t="s">
-        <v>312</v>
-      </c>
-      <c r="AF38" t="s">
-        <v>65</v>
-      </c>
-      <c r="AG38" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH38" t="s">
-        <v>65</v>
-      </c>
-      <c r="AI38" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ38" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK38" t="s">
-        <v>65</v>
-      </c>
-      <c r="AL38" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM38" t="s">
-        <v>415</v>
-      </c>
-      <c r="AN38" t="s">
-        <v>49</v>
-      </c>
-      <c r="AO38" t="s">
-        <v>49</v>
-      </c>
-      <c r="AP38" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="39" spans="1:42" x14ac:dyDescent="0.3">
@@ -8186,37 +8186,37 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C39" t="s">
+        <v>517</v>
+      </c>
+      <c r="D39" t="s">
         <v>518</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>519</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>520</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>521</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>522</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
+        <v>522</v>
+      </c>
+      <c r="J39" t="s">
         <v>523</v>
       </c>
-      <c r="I39" t="s">
-        <v>523</v>
-      </c>
-      <c r="J39" t="s">
-        <v>524</v>
-      </c>
       <c r="K39" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L39" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M39" t="s">
         <v>53</v>
@@ -8225,22 +8225,22 @@
         <v>54</v>
       </c>
       <c r="O39" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P39" t="s">
+        <v>524</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>57</v>
+      </c>
+      <c r="R39" t="s">
         <v>525</v>
       </c>
-      <c r="Q39" t="s">
-        <v>57</v>
-      </c>
-      <c r="R39" t="s">
+      <c r="S39" t="s">
+        <v>49</v>
+      </c>
+      <c r="T39" t="s">
         <v>526</v>
-      </c>
-      <c r="S39" t="s">
-        <v>49</v>
-      </c>
-      <c r="T39" t="s">
-        <v>527</v>
       </c>
       <c r="U39" t="s">
         <v>57</v>
@@ -8252,28 +8252,28 @@
         <v>60</v>
       </c>
       <c r="X39" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="Y39" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="Z39" t="s">
         <v>49</v>
       </c>
       <c r="AA39" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AB39" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AC39" t="s">
         <v>62</v>
       </c>
       <c r="AD39" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AE39" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AF39" t="s">
         <v>65</v>
@@ -8306,7 +8306,7 @@
         <v>49</v>
       </c>
       <c r="AP39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="40" spans="1:42" x14ac:dyDescent="0.3">
@@ -8317,34 +8317,34 @@
         <v>43</v>
       </c>
       <c r="C40" t="s">
+        <v>530</v>
+      </c>
+      <c r="D40" t="s">
         <v>531</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>532</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>533</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>534</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
+        <v>49</v>
+      </c>
+      <c r="I40" t="s">
         <v>535</v>
       </c>
-      <c r="H40" t="s">
-        <v>49</v>
-      </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>536</v>
       </c>
-      <c r="J40" t="s">
-        <v>537</v>
-      </c>
       <c r="K40" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="L40" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="M40" t="s">
         <v>53</v>
@@ -8353,55 +8353,55 @@
         <v>54</v>
       </c>
       <c r="O40" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P40" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>211</v>
+      </c>
+      <c r="R40" t="s">
+        <v>482</v>
+      </c>
+      <c r="S40" t="s">
+        <v>49</v>
+      </c>
+      <c r="T40" t="s">
+        <v>511</v>
+      </c>
+      <c r="U40" t="s">
+        <v>57</v>
+      </c>
+      <c r="V40" t="s">
+        <v>57</v>
+      </c>
+      <c r="W40" t="s">
+        <v>163</v>
+      </c>
+      <c r="X40" t="s">
         <v>538</v>
       </c>
-      <c r="Q40" t="s">
-        <v>212</v>
-      </c>
-      <c r="R40" t="s">
-        <v>483</v>
-      </c>
-      <c r="S40" t="s">
-        <v>49</v>
-      </c>
-      <c r="T40" t="s">
-        <v>512</v>
-      </c>
-      <c r="U40" t="s">
-        <v>57</v>
-      </c>
-      <c r="V40" t="s">
-        <v>57</v>
-      </c>
-      <c r="W40" t="s">
-        <v>164</v>
-      </c>
-      <c r="X40" t="s">
+      <c r="Y40" t="s">
+        <v>478</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>350</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>513</v>
+      </c>
+      <c r="AB40" t="s">
         <v>539</v>
-      </c>
-      <c r="Y40" t="s">
-        <v>479</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>351</v>
-      </c>
-      <c r="AA40" t="s">
-        <v>514</v>
-      </c>
-      <c r="AB40" t="s">
-        <v>540</v>
       </c>
       <c r="AC40" t="s">
         <v>62</v>
       </c>
       <c r="AD40" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AE40" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AF40" t="s">
         <v>65</v>
@@ -8434,7 +8434,7 @@
         <v>49</v>
       </c>
       <c r="AP40" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="41" spans="1:42" x14ac:dyDescent="0.3">
@@ -8445,34 +8445,34 @@
         <v>43</v>
       </c>
       <c r="C41" t="s">
+        <v>485</v>
+      </c>
+      <c r="D41" t="s">
         <v>486</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>487</v>
-      </c>
-      <c r="E41" t="s">
-        <v>488</v>
       </c>
       <c r="F41" t="s">
         <v>89</v>
       </c>
       <c r="G41" t="s">
+        <v>475</v>
+      </c>
+      <c r="H41" t="s">
         <v>476</v>
       </c>
-      <c r="H41" t="s">
+      <c r="I41" t="s">
+        <v>476</v>
+      </c>
+      <c r="J41" t="s">
         <v>477</v>
       </c>
-      <c r="I41" t="s">
-        <v>477</v>
-      </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
+        <v>508</v>
+      </c>
+      <c r="L41" t="s">
         <v>478</v>
-      </c>
-      <c r="K41" t="s">
-        <v>509</v>
-      </c>
-      <c r="L41" t="s">
-        <v>479</v>
       </c>
       <c r="M41" t="s">
         <v>53</v>
@@ -8484,53 +8484,53 @@
         <v>55</v>
       </c>
       <c r="P41" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q41" t="s">
         <v>60</v>
       </c>
       <c r="R41" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="S41" t="s">
         <v>49</v>
       </c>
       <c r="T41" t="s">
+        <v>541</v>
+      </c>
+      <c r="U41" t="s">
+        <v>57</v>
+      </c>
+      <c r="V41" t="s">
+        <v>57</v>
+      </c>
+      <c r="W41" t="s">
+        <v>145</v>
+      </c>
+      <c r="X41" t="s">
+        <v>380</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>478</v>
+      </c>
+      <c r="Z41" t="s">
         <v>542</v>
       </c>
-      <c r="U41" t="s">
-        <v>57</v>
-      </c>
-      <c r="V41" t="s">
-        <v>57</v>
-      </c>
-      <c r="W41" t="s">
-        <v>146</v>
-      </c>
-      <c r="X41" t="s">
-        <v>381</v>
-      </c>
-      <c r="Y41" t="s">
-        <v>479</v>
-      </c>
-      <c r="Z41" t="s">
+      <c r="AA41" t="s">
+        <v>527</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>542</v>
+      </c>
+      <c r="AC41" t="s">
         <v>543</v>
       </c>
-      <c r="AA41" t="s">
-        <v>528</v>
-      </c>
-      <c r="AB41" t="s">
-        <v>543</v>
-      </c>
-      <c r="AC41" t="s">
-        <v>103</v>
-      </c>
       <c r="AD41" t="s">
+        <v>327</v>
+      </c>
+      <c r="AE41" t="s">
         <v>328</v>
       </c>
-      <c r="AE41" t="s">
-        <v>329</v>
-      </c>
       <c r="AF41" t="s">
         <v>65</v>
       </c>
@@ -8553,7 +8553,7 @@
         <v>49</v>
       </c>
       <c r="AM41" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AN41" t="s">
         <v>49</v>
@@ -8582,7 +8582,7 @@
         <v>547</v>
       </c>
       <c r="F42" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G42" t="s">
         <v>548</v>
@@ -8597,10 +8597,10 @@
         <v>550</v>
       </c>
       <c r="K42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L42" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M42" t="s">
         <v>53</v>
@@ -8609,10 +8609,10 @@
         <v>54</v>
       </c>
       <c r="O42" t="s">
+        <v>398</v>
+      </c>
+      <c r="P42" t="s">
         <v>399</v>
-      </c>
-      <c r="P42" t="s">
-        <v>400</v>
       </c>
       <c r="Q42" t="s">
         <v>76</v>
@@ -8633,19 +8633,19 @@
         <v>57</v>
       </c>
       <c r="W42" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X42" t="s">
         <v>553</v>
       </c>
       <c r="Y42" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Z42" t="s">
         <v>554</v>
       </c>
       <c r="AA42" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AB42" t="s">
         <v>555</v>
@@ -8654,10 +8654,10 @@
         <v>62</v>
       </c>
       <c r="AD42" t="s">
+        <v>310</v>
+      </c>
+      <c r="AE42" t="s">
         <v>311</v>
-      </c>
-      <c r="AE42" t="s">
-        <v>312</v>
       </c>
       <c r="AF42" t="s">
         <v>65</v>
@@ -8710,10 +8710,10 @@
         <v>559</v>
       </c>
       <c r="F43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G43" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H43" t="s">
         <v>560</v>
@@ -8725,10 +8725,10 @@
         <v>562</v>
       </c>
       <c r="K43" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L43" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M43" t="s">
         <v>53</v>
@@ -8737,13 +8737,13 @@
         <v>54</v>
       </c>
       <c r="O43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P43" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Q43" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R43" t="s">
         <v>563</v>
@@ -8761,13 +8761,13 @@
         <v>57</v>
       </c>
       <c r="W43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X43" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Y43" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Z43" t="s">
         <v>565</v>
@@ -8779,10 +8779,10 @@
         <v>566</v>
       </c>
       <c r="AC43" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="AD43" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AE43" t="s">
         <v>64</v>
@@ -8829,34 +8829,34 @@
         <v>43</v>
       </c>
       <c r="C44" t="s">
+        <v>458</v>
+      </c>
+      <c r="D44" t="s">
         <v>459</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>460</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
+        <v>156</v>
+      </c>
+      <c r="G44" t="s">
         <v>461</v>
       </c>
-      <c r="F44" t="s">
-        <v>157</v>
-      </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>462</v>
       </c>
-      <c r="H44" t="s">
+      <c r="I44" t="s">
+        <v>462</v>
+      </c>
+      <c r="J44" t="s">
         <v>463</v>
-      </c>
-      <c r="I44" t="s">
-        <v>463</v>
-      </c>
-      <c r="J44" t="s">
-        <v>464</v>
       </c>
       <c r="K44" t="s">
         <v>568</v>
       </c>
       <c r="L44" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="M44" t="s">
         <v>53</v>
@@ -8865,16 +8865,16 @@
         <v>54</v>
       </c>
       <c r="O44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P44" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Q44" t="s">
         <v>57</v>
       </c>
       <c r="R44" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="S44" t="s">
         <v>49</v>
@@ -8892,10 +8892,10 @@
         <v>60</v>
       </c>
       <c r="X44" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="Y44" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Z44" t="s">
         <v>49</v>
@@ -8904,16 +8904,16 @@
         <v>570</v>
       </c>
       <c r="AB44" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AC44" t="s">
         <v>62</v>
       </c>
       <c r="AD44" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AE44" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF44" t="s">
         <v>65</v>
@@ -8937,7 +8937,7 @@
         <v>49</v>
       </c>
       <c r="AM44" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AN44" t="s">
         <v>49</v>
@@ -8966,7 +8966,7 @@
         <v>574</v>
       </c>
       <c r="F45" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G45" t="s">
         <v>575</v>
@@ -8981,10 +8981,10 @@
         <v>577</v>
       </c>
       <c r="K45" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L45" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M45" t="s">
         <v>53</v>
@@ -8993,7 +8993,7 @@
         <v>54</v>
       </c>
       <c r="O45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P45" t="s">
         <v>578</v>
@@ -9017,19 +9017,19 @@
         <v>57</v>
       </c>
       <c r="W45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X45" t="s">
         <v>581</v>
       </c>
       <c r="Y45" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="Z45" t="s">
         <v>582</v>
       </c>
       <c r="AA45" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AB45" t="s">
         <v>583</v>
@@ -9038,10 +9038,10 @@
         <v>62</v>
       </c>
       <c r="AD45" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AE45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF45" t="s">
         <v>65</v>
@@ -9094,7 +9094,7 @@
         <v>587</v>
       </c>
       <c r="F46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G46" t="s">
         <v>588</v>
@@ -9127,7 +9127,7 @@
         <v>592</v>
       </c>
       <c r="Q46" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R46" t="s">
         <v>593</v>
@@ -9163,14 +9163,14 @@
         <v>598</v>
       </c>
       <c r="AC46" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="AD46" t="s">
+        <v>327</v>
+      </c>
+      <c r="AE46" t="s">
         <v>328</v>
       </c>
-      <c r="AE46" t="s">
-        <v>329</v>
-      </c>
       <c r="AF46" t="s">
         <v>65</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>49</v>
       </c>
       <c r="AM46" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AN46" t="s">
         <v>49</v>
@@ -9210,7 +9210,7 @@
         <v>42</v>
       </c>
       <c r="B47" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C47" t="s">
         <v>600</v>
@@ -9222,7 +9222,7 @@
         <v>602</v>
       </c>
       <c r="F47" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G47" t="s">
         <v>603</v>
@@ -9237,10 +9237,10 @@
         <v>605</v>
       </c>
       <c r="K47" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L47" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M47" t="s">
         <v>53</v>
@@ -9249,22 +9249,22 @@
         <v>54</v>
       </c>
       <c r="O47" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P47" t="s">
+        <v>524</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>57</v>
+      </c>
+      <c r="R47" t="s">
         <v>525</v>
       </c>
-      <c r="Q47" t="s">
-        <v>57</v>
-      </c>
-      <c r="R47" t="s">
+      <c r="S47" t="s">
+        <v>49</v>
+      </c>
+      <c r="T47" t="s">
         <v>526</v>
-      </c>
-      <c r="S47" t="s">
-        <v>49</v>
-      </c>
-      <c r="T47" t="s">
-        <v>527</v>
       </c>
       <c r="U47" t="s">
         <v>57</v>
@@ -9276,28 +9276,28 @@
         <v>60</v>
       </c>
       <c r="X47" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="Y47" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="Z47" t="s">
         <v>49</v>
       </c>
       <c r="AA47" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AB47" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AC47" t="s">
         <v>62</v>
       </c>
       <c r="AD47" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AE47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AF47" t="s">
         <v>65</v>
@@ -9350,7 +9350,7 @@
         <v>609</v>
       </c>
       <c r="F48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G48" t="s">
         <v>610</v>
@@ -9377,13 +9377,13 @@
         <v>54</v>
       </c>
       <c r="O48" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P48" t="s">
         <v>614</v>
       </c>
       <c r="Q48" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R48" t="s">
         <v>563</v>
@@ -9401,7 +9401,7 @@
         <v>57</v>
       </c>
       <c r="W48" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X48" t="s">
         <v>615</v>
@@ -9413,16 +9413,16 @@
         <v>616</v>
       </c>
       <c r="AA48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AB48" t="s">
         <v>617</v>
       </c>
       <c r="AC48" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="AD48" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AE48" t="s">
         <v>64</v>
@@ -9449,7 +9449,7 @@
         <v>49</v>
       </c>
       <c r="AM48" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AN48" t="s">
         <v>49</v>
@@ -9478,7 +9478,7 @@
         <v>621</v>
       </c>
       <c r="F49" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G49" t="s">
         <v>622</v>
@@ -9505,7 +9505,7 @@
         <v>54</v>
       </c>
       <c r="O49" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="P49" t="s">
         <v>626</v>
@@ -9514,14 +9514,14 @@
         <v>627</v>
       </c>
       <c r="R49" t="s">
+        <v>479</v>
+      </c>
+      <c r="S49" t="s">
+        <v>49</v>
+      </c>
+      <c r="T49" t="s">
         <v>480</v>
       </c>
-      <c r="S49" t="s">
-        <v>49</v>
-      </c>
-      <c r="T49" t="s">
-        <v>481</v>
-      </c>
       <c r="U49" t="s">
         <v>57</v>
       </c>
@@ -9529,10 +9529,10 @@
         <v>57</v>
       </c>
       <c r="W49" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="X49" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="Y49" t="s">
         <v>625</v>
@@ -9541,16 +9541,16 @@
         <v>628</v>
       </c>
       <c r="AA49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AB49" t="s">
         <v>629</v>
       </c>
       <c r="AC49" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD49" t="s">
         <v>103</v>
-      </c>
-      <c r="AD49" t="s">
-        <v>104</v>
       </c>
       <c r="AE49" t="s">
         <v>84</v>
@@ -9633,7 +9633,7 @@
         <v>54</v>
       </c>
       <c r="O50" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P50" t="s">
         <v>638</v>
@@ -9669,7 +9669,7 @@
         <v>49</v>
       </c>
       <c r="AA50" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AB50" t="s">
         <v>639</v>
@@ -9678,10 +9678,10 @@
         <v>62</v>
       </c>
       <c r="AD50" t="s">
+        <v>262</v>
+      </c>
+      <c r="AE50" t="s">
         <v>263</v>
-      </c>
-      <c r="AE50" t="s">
-        <v>264</v>
       </c>
       <c r="AF50" t="s">
         <v>65</v>
@@ -9734,7 +9734,7 @@
         <v>644</v>
       </c>
       <c r="F51" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G51" t="s">
         <v>645</v>
@@ -9749,7 +9749,7 @@
         <v>647</v>
       </c>
       <c r="K51" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L51" t="s">
         <v>568</v>
@@ -9791,7 +9791,7 @@
         <v>649</v>
       </c>
       <c r="Y51" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="Z51" t="s">
         <v>49</v>
@@ -9809,7 +9809,7 @@
         <v>652</v>
       </c>
       <c r="AE51" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AF51" t="s">
         <v>65</v>
@@ -9889,13 +9889,13 @@
         <v>54</v>
       </c>
       <c r="O52" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P52" t="s">
         <v>638</v>
       </c>
       <c r="Q52" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="R52" t="s">
         <v>661</v>
@@ -9925,19 +9925,19 @@
         <v>665</v>
       </c>
       <c r="AA52" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AB52" t="s">
         <v>666</v>
       </c>
       <c r="AC52" t="s">
-        <v>103</v>
+        <v>543</v>
       </c>
       <c r="AD52" t="s">
+        <v>262</v>
+      </c>
+      <c r="AE52" t="s">
         <v>263</v>
-      </c>
-      <c r="AE52" t="s">
-        <v>264</v>
       </c>
       <c r="AF52" t="s">
         <v>65</v>
@@ -9990,7 +9990,7 @@
         <v>670</v>
       </c>
       <c r="F53" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G53" t="s">
         <v>671</v>
@@ -10041,10 +10041,10 @@
         <v>57</v>
       </c>
       <c r="W53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X53" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Y53" t="s">
         <v>674</v>
@@ -10053,19 +10053,19 @@
         <v>565</v>
       </c>
       <c r="AA53" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB53" t="s">
         <v>676</v>
       </c>
       <c r="AC53" t="s">
-        <v>103</v>
+        <v>543</v>
       </c>
       <c r="AD53" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AE53" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AF53" t="s">
         <v>65</v>
@@ -10145,7 +10145,7 @@
         <v>54</v>
       </c>
       <c r="O54" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="P54" t="s">
         <v>686</v>
@@ -10154,13 +10154,13 @@
         <v>627</v>
       </c>
       <c r="R54" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="S54" t="s">
         <v>49</v>
       </c>
       <c r="T54" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="U54" t="s">
         <v>57</v>
@@ -10169,19 +10169,19 @@
         <v>57</v>
       </c>
       <c r="W54" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X54" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="Y54" t="s">
         <v>685</v>
       </c>
       <c r="Z54" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AA54" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AB54" t="s">
         <v>687</v>
@@ -10190,7 +10190,7 @@
         <v>62</v>
       </c>
       <c r="AD54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AE54" t="s">
         <v>84</v>
@@ -10276,49 +10276,49 @@
         <v>55</v>
       </c>
       <c r="P55" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="R55" t="s">
+        <v>479</v>
+      </c>
+      <c r="S55" t="s">
+        <v>49</v>
+      </c>
+      <c r="T55" t="s">
         <v>480</v>
       </c>
-      <c r="S55" t="s">
-        <v>49</v>
-      </c>
-      <c r="T55" t="s">
+      <c r="U55" t="s">
+        <v>57</v>
+      </c>
+      <c r="V55" t="s">
+        <v>57</v>
+      </c>
+      <c r="W55" t="s">
+        <v>163</v>
+      </c>
+      <c r="X55" t="s">
         <v>481</v>
-      </c>
-      <c r="U55" t="s">
-        <v>57</v>
-      </c>
-      <c r="V55" t="s">
-        <v>57</v>
-      </c>
-      <c r="W55" t="s">
-        <v>164</v>
-      </c>
-      <c r="X55" t="s">
-        <v>482</v>
       </c>
       <c r="Y55" t="s">
         <v>685</v>
       </c>
       <c r="Z55" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AA55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AB55" t="s">
         <v>695</v>
       </c>
       <c r="AC55" t="s">
+        <v>543</v>
+      </c>
+      <c r="AD55" t="s">
         <v>103</v>
-      </c>
-      <c r="AD55" t="s">
-        <v>104</v>
       </c>
       <c r="AE55" t="s">
         <v>84</v>
@@ -10404,49 +10404,49 @@
         <v>55</v>
       </c>
       <c r="P56" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="R56" t="s">
+        <v>479</v>
+      </c>
+      <c r="S56" t="s">
+        <v>49</v>
+      </c>
+      <c r="T56" t="s">
         <v>480</v>
       </c>
-      <c r="S56" t="s">
-        <v>49</v>
-      </c>
-      <c r="T56" t="s">
+      <c r="U56" t="s">
+        <v>57</v>
+      </c>
+      <c r="V56" t="s">
+        <v>57</v>
+      </c>
+      <c r="W56" t="s">
+        <v>163</v>
+      </c>
+      <c r="X56" t="s">
         <v>481</v>
-      </c>
-      <c r="U56" t="s">
-        <v>57</v>
-      </c>
-      <c r="V56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W56" t="s">
-        <v>164</v>
-      </c>
-      <c r="X56" t="s">
-        <v>482</v>
       </c>
       <c r="Y56" t="s">
         <v>685</v>
       </c>
       <c r="Z56" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AA56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AB56" t="s">
         <v>695</v>
       </c>
       <c r="AC56" t="s">
+        <v>543</v>
+      </c>
+      <c r="AD56" t="s">
         <v>103</v>
-      </c>
-      <c r="AD56" t="s">
-        <v>104</v>
       </c>
       <c r="AE56" t="s">
         <v>84</v>
@@ -10493,31 +10493,31 @@
         <v>43</v>
       </c>
       <c r="C57" t="s">
+        <v>330</v>
+      </c>
+      <c r="D57" t="s">
         <v>331</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>332</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>333</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>334</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
+        <v>49</v>
+      </c>
+      <c r="I57" t="s">
         <v>335</v>
       </c>
-      <c r="H57" t="s">
-        <v>49</v>
-      </c>
-      <c r="I57" t="s">
+      <c r="J57" t="s">
         <v>336</v>
       </c>
-      <c r="J57" t="s">
-        <v>337</v>
-      </c>
       <c r="K57" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L57" t="s">
         <v>685</v>
@@ -10529,23 +10529,23 @@
         <v>54</v>
       </c>
       <c r="O57" t="s">
+        <v>338</v>
+      </c>
+      <c r="P57" t="s">
         <v>339</v>
       </c>
-      <c r="P57" t="s">
-        <v>340</v>
-      </c>
       <c r="Q57" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R57" t="s">
+        <v>241</v>
+      </c>
+      <c r="S57" t="s">
+        <v>49</v>
+      </c>
+      <c r="T57" t="s">
         <v>242</v>
       </c>
-      <c r="S57" t="s">
-        <v>49</v>
-      </c>
-      <c r="T57" t="s">
-        <v>243</v>
-      </c>
       <c r="U57" t="s">
         <v>57</v>
       </c>
@@ -10553,7 +10553,7 @@
         <v>57</v>
       </c>
       <c r="W57" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X57" t="s">
         <v>698</v>
@@ -10565,7 +10565,7 @@
         <v>699</v>
       </c>
       <c r="AA57" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AB57" t="s">
         <v>700</v>
@@ -10574,10 +10574,10 @@
         <v>62</v>
       </c>
       <c r="AD57" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE57" t="s">
         <v>126</v>
-      </c>
-      <c r="AE57" t="s">
-        <v>127</v>
       </c>
       <c r="AF57" t="s">
         <v>65</v>
@@ -10630,7 +10630,7 @@
         <v>704</v>
       </c>
       <c r="F58" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G58" t="s">
         <v>705</v>
@@ -10693,7 +10693,7 @@
         <v>49</v>
       </c>
       <c r="AA58" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AB58" t="s">
         <v>708</v>
@@ -10702,10 +10702,10 @@
         <v>62</v>
       </c>
       <c r="AD58" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AE58" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF58" t="s">
         <v>65</v>
@@ -10758,7 +10758,7 @@
         <v>713</v>
       </c>
       <c r="F59" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G59" t="s">
         <v>714</v>
@@ -10788,7 +10788,7 @@
         <v>55</v>
       </c>
       <c r="P59" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q59" t="s">
         <v>76</v>
@@ -10809,7 +10809,7 @@
         <v>57</v>
       </c>
       <c r="W59" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X59" t="s">
         <v>615</v>
@@ -10821,16 +10821,16 @@
         <v>616</v>
       </c>
       <c r="AA59" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AB59" t="s">
         <v>718</v>
       </c>
       <c r="AC59" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="AD59" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AE59" t="s">
         <v>64</v>
@@ -10886,7 +10886,7 @@
         <v>713</v>
       </c>
       <c r="F60" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G60" t="s">
         <v>714</v>
@@ -10916,19 +10916,19 @@
         <v>55</v>
       </c>
       <c r="P60" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q60" t="s">
         <v>76</v>
       </c>
       <c r="R60" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="S60" t="s">
         <v>49</v>
       </c>
       <c r="T60" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="U60" t="s">
         <v>57</v>
@@ -10937,28 +10937,28 @@
         <v>57</v>
       </c>
       <c r="W60" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X60" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Y60" t="s">
         <v>717</v>
       </c>
       <c r="Z60" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AA60" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AB60" t="s">
         <v>720</v>
       </c>
       <c r="AC60" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD60" t="s">
         <v>103</v>
-      </c>
-      <c r="AD60" t="s">
-        <v>104</v>
       </c>
       <c r="AE60" t="s">
         <v>84</v>
@@ -11014,7 +11014,7 @@
         <v>724</v>
       </c>
       <c r="F61" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G61" t="s">
         <v>725</v>
@@ -11047,7 +11047,7 @@
         <v>648</v>
       </c>
       <c r="Q61" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="R61" t="s">
         <v>728</v>
@@ -11068,7 +11068,7 @@
         <v>730</v>
       </c>
       <c r="X61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y61" t="s">
         <v>717</v>
@@ -11077,19 +11077,19 @@
         <v>731</v>
       </c>
       <c r="AA61" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AB61" t="s">
         <v>732</v>
       </c>
       <c r="AC61" t="s">
-        <v>103</v>
+        <v>543</v>
       </c>
       <c r="AD61" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE61" t="s">
         <v>126</v>
-      </c>
-      <c r="AE61" t="s">
-        <v>127</v>
       </c>
       <c r="AF61" t="s">
         <v>65</v>
@@ -11169,7 +11169,7 @@
         <v>54</v>
       </c>
       <c r="O62" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="P62" t="s">
         <v>741</v>
@@ -11178,7 +11178,7 @@
         <v>627</v>
       </c>
       <c r="R62" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="S62" t="s">
         <v>49</v>
@@ -11193,7 +11193,7 @@
         <v>57</v>
       </c>
       <c r="W62" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="X62" t="s">
         <v>743</v>
@@ -11202,22 +11202,22 @@
         <v>660</v>
       </c>
       <c r="Z62" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AA62" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AB62" t="s">
         <v>744</v>
       </c>
       <c r="AC62" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="AD62" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AE62" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AF62" t="s">
         <v>65</v>
@@ -11270,7 +11270,7 @@
         <v>748</v>
       </c>
       <c r="F63" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G63" t="s">
         <v>749</v>
@@ -11297,7 +11297,7 @@
         <v>54</v>
       </c>
       <c r="O63" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="P63" t="s">
         <v>741</v>
@@ -11306,13 +11306,13 @@
         <v>627</v>
       </c>
       <c r="R63" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="S63" t="s">
         <v>49</v>
       </c>
       <c r="T63" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="U63" t="s">
         <v>57</v>
@@ -11324,7 +11324,7 @@
         <v>752</v>
       </c>
       <c r="X63" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y63" t="s">
         <v>717</v>
@@ -11339,13 +11339,13 @@
         <v>755</v>
       </c>
       <c r="AC63" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="AD63" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE63" t="s">
         <v>111</v>
-      </c>
-      <c r="AE63" t="s">
-        <v>112</v>
       </c>
       <c r="AF63" t="s">
         <v>65</v>
@@ -11398,7 +11398,7 @@
         <v>759</v>
       </c>
       <c r="F64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G64" t="s">
         <v>705</v>
@@ -11461,7 +11461,7 @@
         <v>49</v>
       </c>
       <c r="AA64" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AB64" t="s">
         <v>708</v>
@@ -11470,10 +11470,10 @@
         <v>62</v>
       </c>
       <c r="AD64" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AE64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF64" t="s">
         <v>65</v>
@@ -11526,7 +11526,7 @@
         <v>765</v>
       </c>
       <c r="F65" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G65" t="s">
         <v>766</v>
@@ -11553,13 +11553,13 @@
         <v>54</v>
       </c>
       <c r="O65" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P65" t="s">
         <v>769</v>
       </c>
       <c r="Q65" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R65" t="s">
         <v>770</v>
@@ -11577,7 +11577,7 @@
         <v>57</v>
       </c>
       <c r="W65" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X65" t="s">
         <v>772</v>
@@ -11589,19 +11589,19 @@
         <v>773</v>
       </c>
       <c r="AA65" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AB65" t="s">
         <v>774</v>
       </c>
       <c r="AC65" t="s">
-        <v>103</v>
+        <v>543</v>
       </c>
       <c r="AD65" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AE65" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF65" t="s">
         <v>65</v>
@@ -11681,13 +11681,13 @@
         <v>54</v>
       </c>
       <c r="O66" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q66" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R66" t="s">
         <v>593</v>
@@ -11705,7 +11705,7 @@
         <v>57</v>
       </c>
       <c r="W66" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X66" t="s">
         <v>783</v>
@@ -11717,19 +11717,19 @@
         <v>784</v>
       </c>
       <c r="AA66" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AB66" t="s">
         <v>785</v>
       </c>
       <c r="AC66" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="AD66" t="s">
+        <v>327</v>
+      </c>
+      <c r="AE66" t="s">
         <v>328</v>
-      </c>
-      <c r="AE66" t="s">
-        <v>329</v>
       </c>
       <c r="AF66" t="s">
         <v>65</v>
@@ -11770,7 +11770,7 @@
         <v>42</v>
       </c>
       <c r="B67" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C67" t="s">
         <v>787</v>
@@ -11797,7 +11797,7 @@
         <v>793</v>
       </c>
       <c r="K67" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="L67" t="s">
         <v>794</v>
@@ -11809,13 +11809,13 @@
         <v>54</v>
       </c>
       <c r="O67" t="s">
+        <v>338</v>
+      </c>
+      <c r="P67" t="s">
         <v>339</v>
       </c>
-      <c r="P67" t="s">
-        <v>340</v>
-      </c>
       <c r="Q67" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R67" t="s">
         <v>795</v>
@@ -11833,7 +11833,7 @@
         <v>57</v>
       </c>
       <c r="W67" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X67" t="s">
         <v>797</v>
@@ -11845,19 +11845,19 @@
         <v>798</v>
       </c>
       <c r="AA67" t="s">
-        <v>651</v>
+        <v>354</v>
       </c>
       <c r="AB67" t="s">
         <v>799</v>
       </c>
       <c r="AC67" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="AD67" t="s">
         <v>800</v>
       </c>
       <c r="AE67" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AF67" t="s">
         <v>65</v>
@@ -11910,7 +11910,7 @@
         <v>804</v>
       </c>
       <c r="F68" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G68" t="s">
         <v>805</v>
@@ -11946,7 +11946,7 @@
         <v>57</v>
       </c>
       <c r="R68" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="S68" t="s">
         <v>49</v>
@@ -11964,7 +11964,7 @@
         <v>60</v>
       </c>
       <c r="X68" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="Y68" t="s">
         <v>613</v>
@@ -11976,16 +11976,16 @@
         <v>808</v>
       </c>
       <c r="AB68" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AC68" t="s">
         <v>62</v>
       </c>
       <c r="AD68" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AE68" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AF68" t="s">
         <v>65</v>
